--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Constants" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Assets" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ProcessVariables" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -18,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <si>
     <t>Name</t>
   </si>
@@ -109,16 +110,10 @@
     <t>obligationDateStart</t>
   </si>
   <si>
-    <t>20/01/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data inicial do range de datas que deve abranger a data de vencimento da obrigação em questão, se não estiver definida nenhuma data nessa variável, o processo define o primeiro e o ultimo dia do mês como as datas de inicio e fim do range.</t>
   </si>
   <si>
     <t>obligationDateEnd</t>
-  </si>
-  <si>
-    <t>01/02/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Data final do range de datas que deve abranger a data de vencimento da obrigação em questão, se não estiver definida nenhuma data nessa variável, o processo define o primeiro e o ultimo dia do mês como as datas de inicio e fim do range.</t>
@@ -163,6 +158,9 @@
     <t>obligationDebugCompanyId</t>
   </si>
   <si>
+    <t>7a8d0889-71e5-4dab-9ec2-734bf7c46734</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -196,7 +194,7 @@
     <t>discordIntegrationWebhook</t>
   </si>
   <si>
-    <t>https://discord.com/api/webhooks/1480622360888348782/kdyzsfcL0x-dRAhSlVzLWuLgtZVv9F-nG_agjagkrFjNF1RSGt6oi5oVvIyV8dKBl_c7</t>
+    <t>https://discord.com/api/webhooks/1481613724102951093/SGz4BHIRTn3KXmhEQP1AgLaNKWGs4-LvW_bYP8tfs_xuurusg2LunnC13mx0I9LRq07B</t>
   </si>
   <si>
     <t xml:space="preserve">Webhook para integração e envio de mensagens e prints quando a automação falhar.</t>
@@ -214,7 +212,40 @@
     <t xml:space="preserve">O erro ocorreu na seguinte empresa:</t>
   </si>
   <si>
-    <t xml:space="preserve">PROCESS TIMEOUTS</t>
+    <t>MaxRetryNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must be 0 if working with Orchestrator queues. If &gt; 0, the robot will retry the same transaction which failed with a system exception. Must be an integer value.</t>
+  </si>
+  <si>
+    <t>MaxConsecutiveSystemExceptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of consecutive system exceptions allowed. If MaxConsecutiveSystemExceptions is reached, the job is stopped. To disable this feature, set the value to 0. </t>
+  </si>
+  <si>
+    <t>ExScreenshotsFolderPath</t>
+  </si>
+  <si>
+    <t>Exceptions_Screenshots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where to save exceptions screenshots - can be a full or a relative path.</t>
+  </si>
+  <si>
+    <t>RetryNumberGetTransactionItem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of times Get Transaction Item activity is retried in case of an exception. Must be an integer &gt;= 1.</t>
+  </si>
+  <si>
+    <t>RetryNumberSetTransactionStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of times Set transaction status activity is retried in case of an exception. Must be an integer &gt;= 1. </t>
+  </si>
+  <si>
+    <t>TIMEOUTS</t>
   </si>
   <si>
     <t>login_at_domonio_timeout</t>
@@ -241,40 +272,7 @@
     <t xml:space="preserve">Delay after padrão das atividades do processo</t>
   </si>
   <si>
-    <t>MaxRetryNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 0 if working with Orchestrator queues. If &gt; 0, the robot will retry the same transaction which failed with a system exception. Must be an integer value.</t>
-  </si>
-  <si>
-    <t>MaxConsecutiveSystemExceptions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The number of consecutive system exceptions allowed. If MaxConsecutiveSystemExceptions is reached, the job is stopped. To disable this feature, set the value to 0. </t>
-  </si>
-  <si>
-    <t>ExScreenshotsFolderPath</t>
-  </si>
-  <si>
-    <t>Exceptions_Screenshots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where to save exceptions screenshots - can be a full or a relative path.</t>
-  </si>
-  <si>
-    <t>RetryNumberGetTransactionItem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The number of times Get Transaction Item activity is retried in case of an exception. Must be an integer &gt;= 1.</t>
-  </si>
-  <si>
-    <t>RetryNumberSetTransactionStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The number of times Set transaction status activity is retried in case of an exception. Must be an integer &gt;= 1. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Success message</t>
+    <t xml:space="preserve">SUCCESS MESSAGE</t>
   </si>
   <si>
     <t>LogMessage_Success</t>
@@ -361,6 +359,15 @@
     <t xml:space="preserve">Faltam informações para a execução da automação na presente empresa. Favor verificar.</t>
   </si>
   <si>
+    <t>ExceptionMessage_AnyExpense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não existem despesas na empresa em questão para o periodo determinado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caso não existam despesas na empresa em questão.</t>
+  </si>
+  <si>
     <t>Asset</t>
   </si>
   <si>
@@ -404,6 +411,60 @@
   </si>
   <si>
     <t xml:space="preserve">Codigo do contador dentro do domínio</t>
+  </si>
+  <si>
+    <t>mainPath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\\192.168.8.8\Razonet\18- OPERAÇÃO RAZONET\01- ROTINAS AUTOMATICAS\04- LANÇAMENTOS CONTÁBEIS\AUTOMACAO\LANÇAMENTOS DESPESAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endereço onde serão alocados os arquivos de importação e relatórios de erros de importação do processo</t>
+  </si>
+  <si>
+    <t>GetExpensesSettings</t>
+  </si>
+  <si>
+    <t>expensesUrl</t>
+  </si>
+  <si>
+    <t>https://app.razonet.com.br/integration/v1/company_expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Url para requisição das despesas no backoffice.</t>
+  </si>
+  <si>
+    <t>getExpenses_timeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timeout do request.</t>
+  </si>
+  <si>
+    <t>getExpenses_perPage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numero de despesas apresentadas em cada página da paginação do json.</t>
+  </si>
+  <si>
+    <t>getExpenses_contentType</t>
+  </si>
+  <si>
+    <t>application/json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo de conteúdo que será aceitado no request</t>
+  </si>
+  <si>
+    <t>getExpenses_dateStart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inicio do range de datas que abrange a data de vencimento das despesas que irão ser importadas. Deve estar no formato "dd/MM/yyyy" e só deve existir caso o getExpenses_dateEnd existir também.</t>
+  </si>
+  <si>
+    <t>getExpenses_dateEnd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fim do range de datas que abrange a data de vencimento das despesas que irão ser importadas. Deve estar no formato "dd/MM/yyyy" e só deve existir caso o getExpenses_dateStart existir também. Deve ser posterior ao getExpenses_dateStart</t>
   </si>
 </sst>
 </file>
@@ -423,12 +484,12 @@
     </font>
     <font>
       <b/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -445,12 +506,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0"/>
+        <bgColor theme="1" tint="0"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -466,20 +533,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.099978637043366805"/>
+        <bgColor theme="2" tint="-0.099978637043366805"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor theme="8" tint="0.59999389629810485"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="0" tint="0"/>
+        <bgColor theme="0" tint="0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.099978637043366805"/>
-        <bgColor theme="2" tint="-0.099978637043366805"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor theme="9" tint="0.59999389629810485"/>
       </patternFill>
     </fill>
     <fill>
@@ -501,7 +574,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -524,11 +597,20 @@
       </bottom>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="53">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -540,58 +622,50 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf fontId="3" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="4" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="2" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -608,27 +682,71 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="5" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
     <xf fontId="5" fillId="9" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf fontId="5" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="11" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1143,7 +1261,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="9.140625"/>
     <col customWidth="1" min="2" max="2" width="45.140625"/>
-    <col customWidth="1" min="3" max="3" style="1" width="43.8515625"/>
+    <col customWidth="1" min="3" max="3" style="1" width="60.7109375"/>
     <col customWidth="1" min="4" max="4" width="84.57421875"/>
     <col customWidth="1" min="5" max="5" width="7.00390625"/>
     <col customWidth="1" min="6" max="27" width="8.7109375"/>
@@ -1194,245 +1312,214 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="28.5">
+    <row r="3" ht="17.399999999999999" customHeight="1">
+      <c r="A3" s="5"/>
       <c r="B3" s="5"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="11"/>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11"/>
     </row>
     <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="6"/>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="8" t="b">
+      <c r="C7" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="26.399999999999999" customHeight="1">
+    <row r="8" ht="17.399999999999999" customHeight="1">
+      <c r="A8" s="5"/>
       <c r="B8" s="5"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" ht="31.199999999999999" customHeight="1">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13" t="s">
+      <c r="C9" s="14"/>
+      <c r="D9" s="15" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" ht="33.600000000000001" customHeight="1">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="14" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" ht="43.200000000000003" customHeight="1">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12" t="s">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="16"/>
+      <c r="D11" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="13" t="s">
+    </row>
+    <row r="12" ht="61.200000000000003" customHeight="1">
+      <c r="A12" s="13"/>
+      <c r="B12" s="14" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" ht="61.200000000000003" customHeight="1">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12" t="s">
+      <c r="C12" s="17"/>
+      <c r="D12" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="15" t="s">
+    </row>
+    <row r="13" ht="28.800000000000001" customHeight="1">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="C13" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="14"/>
+    </row>
+    <row r="14" ht="28.800000000000001" customHeight="1">
+      <c r="A14" s="13"/>
+      <c r="B14" s="14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" ht="28.800000000000001" customHeight="1">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12" t="s">
+      <c r="C14" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="13"/>
+      <c r="B15" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="D13" s="12"/>
-    </row>
-    <row r="14" ht="28.800000000000001" customHeight="1">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="11"/>
-      <c r="B15" s="16" t="s">
+    </row>
+    <row r="16" ht="34.799999999999997" customHeight="1">
+      <c r="A16" s="13"/>
+      <c r="B16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18" t="s">
+      <c r="C16" s="14" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="16" ht="34.799999999999997" customHeight="1">
-      <c r="A16" s="11"/>
-      <c r="B16" s="16" t="s">
+      <c r="D16" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="18" t="s">
+    </row>
+    <row r="17" ht="17.399999999999999" customHeight="1">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" ht="46.799999999999997" customHeight="1">
+      <c r="A18" s="21" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18" ht="46.799999999999997" customHeight="1">
-      <c r="A18" s="19" t="s">
+      <c r="B18" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="C18" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="D18" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="20" t="s">
+    </row>
+    <row r="19" ht="46.799999999999997" customHeight="1">
+      <c r="A19" s="21"/>
+      <c r="B19" s="15" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="19" ht="46.799999999999997" customHeight="1">
-      <c r="A19" s="19"/>
-      <c r="B19" s="22" t="s">
+      <c r="C19" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" ht="43.200000000000003" customHeight="1">
+      <c r="A20" s="21"/>
+      <c r="B20" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="20"/>
-    </row>
-    <row r="20" ht="43.200000000000003" customHeight="1">
-      <c r="A20" s="19"/>
-      <c r="B20" s="22" t="s">
+      <c r="C20" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="20"/>
-    </row>
-    <row r="21" ht="28.800000000000001" customHeight="1"/>
-    <row r="22" ht="27.75" customHeight="1">
-      <c r="A22" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="26">
-        <v>30000</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" ht="29.399999999999999" customHeight="1">
-      <c r="A23" s="24"/>
-      <c r="B23" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="26">
-        <v>20000</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" ht="29.399999999999999" customHeight="1">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="26">
-        <v>0</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" ht="29.399999999999999" customHeight="1">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="26">
-        <v>0</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" ht="29.399999999999999" customHeight="1">
-      <c r="A26" s="24"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="25"/>
-    </row>
-    <row r="27" ht="28.800000000000001" customHeight="1">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="25"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="C26" s="1"/>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="C29" s="1"/>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="C34" s="1"/>
     </row>
   </sheetData>
-  <sortState ref="B11:C23" columnSort="0">
-    <sortCondition sortBy="value" descending="0" ref="A11:A23"/>
+  <sortState ref="B11:C20" columnSort="0">
+    <sortCondition sortBy="value" descending="0" ref="A11:A20"/>
   </sortState>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A9:A16"/>
     <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A22:A27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="C18"/>
@@ -1449,20 +1536,20 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8.00390625"/>
-    <col customWidth="1" min="2" max="2" style="28" width="52.140625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="29" width="63.11328125"/>
-    <col customWidth="1" min="4" max="4" style="29" width="75.42578125"/>
+    <col customWidth="1" min="2" max="2" style="24" width="52.140625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="25" width="63.11328125"/>
+    <col customWidth="1" min="4" max="4" style="25" width="84.140625"/>
     <col customWidth="1" min="5" max="27" width="8.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="27" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2"/>
@@ -1490,340 +1577,399 @@
       <c r="AA1" s="2"/>
     </row>
     <row r="2" ht="28.5">
-      <c r="A2" s="32"/>
-      <c r="B2" s="33" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="30">
+        <v>1</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" ht="42.75">
+      <c r="A3" s="28"/>
+      <c r="B3" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="30">
+        <v>3</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1">
+      <c r="A4" s="28"/>
+      <c r="B4" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="30">
+        <v>2</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5">
+      <c r="A6" s="28"/>
+      <c r="B6" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="30">
+        <v>2</v>
+      </c>
+      <c r="D6" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="34">
-        <v>1</v>
-      </c>
-      <c r="D2" s="34" t="s">
+    </row>
+    <row r="7" s="31" customFormat="1" ht="17.399999999999999" customHeight="1">
+      <c r="A7" s="5"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+    </row>
+    <row r="8" ht="39.75" customHeight="1">
+      <c r="A8" s="34" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="3" ht="42.75">
-      <c r="A3" s="32"/>
-      <c r="B3" s="33" t="s">
+      <c r="B8" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="34">
-        <v>3</v>
-      </c>
-      <c r="D3" s="34" t="s">
+      <c r="C8" s="35">
+        <v>30000</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="32"/>
-      <c r="B4" s="33" t="s">
+    <row r="9" ht="39.75" customHeight="1">
+      <c r="A9" s="36"/>
+      <c r="B9" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C9" s="35">
+        <v>20000</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="34" t="s">
+    </row>
+    <row r="10" ht="39.75" customHeight="1">
+      <c r="A10" s="36"/>
+      <c r="B10" s="14" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" ht="28.5">
-      <c r="A5" s="32"/>
-      <c r="B5" s="33" t="s">
+      <c r="C10" s="35">
+        <v>0</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="34">
-        <v>2</v>
-      </c>
-      <c r="D5" s="34" t="s">
+    </row>
+    <row r="11" ht="39.75" customHeight="1">
+      <c r="A11" s="36"/>
+      <c r="B11" s="14" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" ht="28.5">
-      <c r="A6" s="32"/>
-      <c r="B6" s="33" t="s">
+      <c r="C11" s="35">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="34">
-        <v>2</v>
-      </c>
-      <c r="D6" s="34" t="s">
+    </row>
+    <row r="12" ht="17.399999999999999" customHeight="1">
+      <c r="A12" s="5"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+    </row>
+    <row r="13" ht="22.800000000000001" customHeight="1">
+      <c r="A13" s="37" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="7" ht="39.75" customHeight="1">
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-    </row>
-    <row r="8" ht="28.5">
-      <c r="A8" s="35" t="s">
+      <c r="B13" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="C13" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="D13" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="34" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" ht="28.199999999999999" customHeight="1">
-      <c r="A9" s="35"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-    </row>
-    <row r="10" ht="28.199999999999999" customHeight="1">
-      <c r="A10" s="35"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="35"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="35"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="35"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-    </row>
-    <row r="14" ht="40.5" customHeight="1">
-      <c r="A14" s="36"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-    </row>
-    <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>62</v>
-      </c>
+    </row>
+    <row r="14" ht="28.199999999999999" customHeight="1">
+      <c r="A14" s="37"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+    </row>
+    <row r="15" ht="28.199999999999999" customHeight="1">
+      <c r="A15" s="37"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
     </row>
     <row r="16" ht="27" customHeight="1">
       <c r="A16" s="37"/>
-      <c r="B16" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" ht="33.75" customHeight="1">
+      <c r="B16" s="29"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+    </row>
+    <row r="17" ht="27" customHeight="1">
       <c r="A17" s="37"/>
-      <c r="B17" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="34"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="37"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-    </row>
-    <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="37"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+    </row>
+    <row r="19" ht="17.399999999999999" customHeight="1">
+      <c r="A19" s="38"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="37"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="34"/>
+      <c r="A20" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="37"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-    </row>
-    <row r="22" ht="27" customHeight="1">
-      <c r="A22" s="37"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" ht="33.75" customHeight="1">
+      <c r="A22" s="39"/>
+      <c r="B22" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="30"/>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="37"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-    </row>
-    <row r="24" ht="41.25" customHeight="1">
-      <c r="B24" s="28"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-    </row>
-    <row r="25" ht="27.75" customHeight="1">
-      <c r="A25" s="39" t="s">
+      <c r="A23" s="39"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="39"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+    </row>
+    <row r="25" ht="27" customHeight="1">
+      <c r="A25" s="39"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="30"/>
+    </row>
+    <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="39"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+    </row>
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="39"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+    </row>
+    <row r="28" ht="27" customHeight="1">
+      <c r="A28" s="39"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+    </row>
+    <row r="29" ht="17.399999999999999" customHeight="1">
+      <c r="A29" s="5"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+    </row>
+    <row r="30" ht="27.75" customHeight="1">
+      <c r="A30" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="33" t="s">
+      <c r="C30" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="D30" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="34" t="s">
+    </row>
+    <row r="31" ht="27.75" customHeight="1">
+      <c r="A31" s="40"/>
+      <c r="B31" s="29" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="26" ht="27.75" customHeight="1">
-      <c r="A26" s="39"/>
-      <c r="B26" s="33" t="s">
+      <c r="C31" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="D31" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="34" t="s">
+    </row>
+    <row r="32" ht="28.5">
+      <c r="A32" s="40"/>
+      <c r="B32" s="29" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="27" ht="28.5">
-      <c r="A27" s="39"/>
-      <c r="B27" s="33" t="s">
+      <c r="C32" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="D32" s="30"/>
+    </row>
+    <row r="33" ht="28.5">
+      <c r="A33" s="40"/>
+      <c r="B33" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="34"/>
-    </row>
-    <row r="28" ht="28.5">
-      <c r="A28" s="39"/>
-      <c r="B28" s="33" t="s">
+      <c r="C33" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="D33" s="30"/>
+    </row>
+    <row r="34" ht="27.75" customHeight="1">
+      <c r="A34" s="40"/>
+      <c r="B34" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="34"/>
-    </row>
-    <row r="29" ht="27.75" customHeight="1">
-      <c r="A29" s="39"/>
-      <c r="B29" s="33" t="s">
+      <c r="C34" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="D34" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="D29" s="34" t="s">
+    </row>
+    <row r="35" ht="31.199999999999999" customHeight="1">
+      <c r="A35" s="40"/>
+      <c r="B35" s="29" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="30" ht="31.199999999999999" customHeight="1">
-      <c r="A30" s="39"/>
-      <c r="B30" s="33" t="s">
+      <c r="C35" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="D35" s="30"/>
+    </row>
+    <row r="36" ht="28.800000000000001" customHeight="1">
+      <c r="A36" s="40"/>
+      <c r="B36" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="D30" s="34"/>
-    </row>
-    <row r="31" ht="28.800000000000001" customHeight="1">
-      <c r="A31" s="39"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-    </row>
-    <row r="32" ht="29.399999999999999" customHeight="1">
-      <c r="A32" s="39"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-    </row>
-    <row r="33" ht="26.25" customHeight="1">
-      <c r="A33" s="39"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-    </row>
-    <row r="34" ht="28.800000000000001" customHeight="1">
-      <c r="A34" s="39"/>
-      <c r="B34" s="33"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-    </row>
-    <row r="35" ht="28.800000000000001" customHeight="1">
-      <c r="A35" s="39"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-    </row>
-    <row r="36" ht="28.5" customHeight="1">
-      <c r="A36" s="39"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-    </row>
-    <row r="37" ht="28.5" customHeight="1">
-      <c r="A37" s="39"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-    </row>
-    <row r="38" ht="28.5" customHeight="1">
-      <c r="A38" s="39"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-    </row>
-    <row r="39" ht="28.5" customHeight="1">
-      <c r="A39" s="39"/>
-      <c r="B39" s="33"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-    </row>
-    <row r="40" ht="28.5" customHeight="1">
-      <c r="A40" s="39"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
+      <c r="C36" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" ht="29.399999999999999" customHeight="1">
+      <c r="A37" s="40"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+    </row>
+    <row r="38" ht="26.25" customHeight="1">
+      <c r="A38" s="40"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+    </row>
+    <row r="39" ht="28.800000000000001" customHeight="1">
+      <c r="A39" s="40"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+    </row>
+    <row r="40" ht="28.800000000000001" customHeight="1">
+      <c r="A40" s="40"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
     </row>
     <row r="41" ht="28.5" customHeight="1">
-      <c r="B41" s="28"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
+      <c r="A41" s="40"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
     </row>
     <row r="42" ht="28.5" customHeight="1">
-      <c r="B42" s="28"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-    </row>
-    <row r="43" ht="28.5" customHeight="1"/>
-    <row r="44" ht="28.5" customHeight="1"/>
-    <row r="45" ht="28.5" customHeight="1"/>
-    <row r="46" ht="28.5" customHeight="1"/>
-    <row r="47" ht="28.5" customHeight="1"/>
+      <c r="A42" s="40"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+    </row>
+    <row r="43" ht="28.5" customHeight="1">
+      <c r="A43" s="40"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+    </row>
+    <row r="44" ht="28.5" customHeight="1">
+      <c r="A44" s="40"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+    </row>
+    <row r="45" ht="28.5" customHeight="1">
+      <c r="A45" s="40"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+    </row>
+    <row r="46" ht="28.5" customHeight="1">
+      <c r="B46" s="24"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+    </row>
+    <row r="47" ht="28.5" customHeight="1">
+      <c r="B47" s="24"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+    </row>
     <row r="48" ht="28.5" customHeight="1"/>
     <row r="49" ht="28.5" customHeight="1"/>
     <row r="50" ht="28.5" customHeight="1"/>
@@ -1832,12 +1978,18 @@
     <row r="53" ht="28.5" customHeight="1"/>
     <row r="54" ht="28.5" customHeight="1"/>
     <row r="55" ht="28.5" customHeight="1"/>
+    <row r="56" ht="28.5" customHeight="1"/>
+    <row r="57" ht="28.5" customHeight="1"/>
+    <row r="58" ht="28.5" customHeight="1"/>
+    <row r="59" ht="28.5" customHeight="1"/>
+    <row r="60" ht="28.5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A15:A23"/>
-    <mergeCell ref="A25:A40"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="A20:A28"/>
+    <mergeCell ref="A30:A45"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1861,13 +2013,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -1894,58 +2046,58 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>89</v>
+        <v>96</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>89</v>
+        <v>99</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1"/>
@@ -2949,4 +3101,255 @@
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="5.57421875"/>
+    <col customWidth="1" min="2" max="2" style="45" width="24.421875"/>
+    <col customWidth="1" min="3" max="3" width="55.421875"/>
+    <col customWidth="1" min="4" max="4" width="75.8515625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75">
+      <c r="B1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" ht="42.75">
+      <c r="A2" s="46"/>
+      <c r="B2" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" ht="21.600000000000001" customHeight="1">
+      <c r="A3" s="46"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+    </row>
+    <row r="4" ht="21.600000000000001" customHeight="1">
+      <c r="A4" s="46"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+    </row>
+    <row r="5" ht="21.600000000000001" customHeight="1">
+      <c r="A5" s="46"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+    </row>
+    <row r="6" ht="21.600000000000001" customHeight="1">
+      <c r="A6" s="46"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+    </row>
+    <row r="7" ht="21.600000000000001" customHeight="1">
+      <c r="A7" s="46"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9" ht="41.25" customHeight="1">
+      <c r="A9" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" ht="39.75" customHeight="1">
+      <c r="A10" s="52"/>
+      <c r="B10" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="30">
+        <v>60000</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" ht="36.75" customHeight="1">
+      <c r="A11" s="52"/>
+      <c r="B11" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="30">
+        <v>3000</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" ht="36.75" customHeight="1">
+      <c r="A12" s="52"/>
+      <c r="B12" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="52"/>
+      <c r="B13" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" ht="63.600000000000001" customHeight="1">
+      <c r="A14" s="52"/>
+      <c r="B14" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" ht="30.600000000000001" customHeight="1"/>
+    <row r="17" ht="28.199999999999999" customHeight="1"/>
+    <row r="18" ht="28.199999999999999" customHeight="1"/>
+    <row r="19" ht="28.199999999999999" customHeight="1"/>
+    <row r="20" ht="28.199999999999999" customHeight="1"/>
+    <row r="21" ht="28.199999999999999" customHeight="1"/>
+    <row r="22" ht="28.199999999999999" customHeight="1"/>
+    <row r="23" ht="28.199999999999999" customHeight="1"/>
+    <row r="24" ht="28.199999999999999" customHeight="1"/>
+    <row r="25" ht="28.199999999999999" customHeight="1"/>
+    <row r="26" ht="28.199999999999999" customHeight="1"/>
+    <row r="27" ht="28.199999999999999" customHeight="1"/>
+    <row r="28" ht="28.199999999999999" customHeight="1"/>
+    <row r="29" ht="28.199999999999999" customHeight="1"/>
+    <row r="30" ht="28.199999999999999" customHeight="1"/>
+    <row r="31" ht="28.199999999999999" customHeight="1"/>
+    <row r="32" ht="28.199999999999999" customHeight="1"/>
+    <row r="33" ht="28.199999999999999" customHeight="1"/>
+    <row r="34" ht="28.199999999999999" customHeight="1"/>
+    <row r="35" ht="28.199999999999999" customHeight="1"/>
+    <row r="36" ht="28.199999999999999" customHeight="1"/>
+    <row r="37" ht="28.199999999999999" customHeight="1"/>
+    <row r="38" ht="28.199999999999999" customHeight="1"/>
+    <row r="39" ht="28.199999999999999" customHeight="1"/>
+    <row r="40" ht="28.199999999999999" customHeight="1"/>
+    <row r="41" ht="28.199999999999999" customHeight="1"/>
+    <row r="42" ht="28.199999999999999" customHeight="1"/>
+    <row r="43" ht="28.199999999999999" customHeight="1"/>
+    <row r="44" ht="28.199999999999999" customHeight="1"/>
+    <row r="45" ht="28.199999999999999" customHeight="1"/>
+    <row r="46" ht="28.199999999999999" customHeight="1"/>
+    <row r="47" ht="28.199999999999999" customHeight="1"/>
+    <row r="48" ht="28.199999999999999" customHeight="1"/>
+    <row r="49" ht="28.199999999999999" customHeight="1"/>
+    <row r="50" ht="28.199999999999999" customHeight="1"/>
+    <row r="51" ht="28.199999999999999" customHeight="1"/>
+    <row r="52" ht="28.199999999999999" customHeight="1"/>
+    <row r="53" ht="28.199999999999999" customHeight="1"/>
+    <row r="54" ht="28.199999999999999" customHeight="1"/>
+    <row r="55" ht="28.199999999999999" customHeight="1"/>
+    <row r="56" ht="28.199999999999999" customHeight="1"/>
+    <row r="57" ht="28.199999999999999" customHeight="1"/>
+    <row r="58" ht="28.199999999999999" customHeight="1"/>
+    <row r="59" ht="28.199999999999999" customHeight="1"/>
+    <row r="60" ht="28.199999999999999" customHeight="1"/>
+    <row r="61" ht="28.199999999999999" customHeight="1"/>
+    <row r="62" ht="28.199999999999999" customHeight="1"/>
+    <row r="63" ht="28.199999999999999" customHeight="1"/>
+    <row r="64" ht="28.199999999999999" customHeight="1"/>
+    <row r="65" ht="28.199999999999999" customHeight="1"/>
+    <row r="66" ht="28.199999999999999" customHeight="1"/>
+    <row r="67" ht="28.199999999999999" customHeight="1"/>
+    <row r="68" ht="28.199999999999999" customHeight="1"/>
+    <row r="69" ht="28.199999999999999" customHeight="1"/>
+    <row r="70" ht="28.199999999999999" customHeight="1"/>
+    <row r="71" ht="28.199999999999999" customHeight="1"/>
+    <row r="72" ht="28.199999999999999" customHeight="1"/>
+    <row r="73" ht="28.199999999999999" customHeight="1"/>
+    <row r="74" ht="28.199999999999999" customHeight="1"/>
+    <row r="75" ht="28.199999999999999" customHeight="1"/>
+    <row r="76" ht="28.199999999999999" customHeight="1"/>
+    <row r="77" ht="28.199999999999999" customHeight="1"/>
+    <row r="78" ht="28.199999999999999" customHeight="1"/>
+    <row r="79" ht="28.199999999999999" customHeight="1"/>
+    <row r="80" ht="28.199999999999999" customHeight="1"/>
+    <row r="81" ht="28.199999999999999" customHeight="1"/>
+    <row r="82" ht="28.199999999999999" customHeight="1"/>
+    <row r="83" ht="28.199999999999999" customHeight="1"/>
+    <row r="84" ht="28.199999999999999" customHeight="1"/>
+    <row r="85" ht="28.199999999999999" customHeight="1"/>
+    <row r="86" ht="28.199999999999999" customHeight="1"/>
+    <row r="87" ht="28.199999999999999" customHeight="1"/>
+    <row r="88" ht="28.199999999999999" customHeight="1"/>
+    <row r="89" ht="28.199999999999999" customHeight="1"/>
+    <row r="90" ht="28.199999999999999" customHeight="1"/>
+    <row r="91" ht="28.199999999999999" customHeight="1"/>
+    <row r="92" ht="28.199999999999999" customHeight="1"/>
+    <row r="93" ht="28.199999999999999" customHeight="1"/>
+    <row r="94" ht="28.199999999999999" customHeight="1"/>
+    <row r="95" ht="28.199999999999999" customHeight="1"/>
+    <row r="96" ht="28.199999999999999" customHeight="1"/>
+    <row r="97" ht="28.199999999999999" customHeight="1"/>
+    <row r="98" ht="28.199999999999999" customHeight="1"/>
+    <row r="99" ht="28.199999999999999" customHeight="1"/>
+    <row r="100" ht="28.199999999999999" customHeight="1"/>
+    <row r="101" ht="28.199999999999999" customHeight="1"/>
+    <row r="102" ht="28.199999999999999" customHeight="1"/>
+    <row r="103" ht="28.199999999999999" customHeight="1"/>
+    <row r="104" ht="28.199999999999999" customHeight="1"/>
+    <row r="105" ht="28.199999999999999" customHeight="1"/>
+    <row r="106" ht="28.199999999999999" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A9:A14"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="C9"/>
+  </hyperlinks>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -471,6 +471,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <sz val="11.000000"/>
@@ -714,12 +717,6 @@
     <xf fontId="5" fillId="11" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
@@ -747,6 +744,12 @@
     </xf>
     <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1588,7 +1591,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" ht="42.75">
+    <row r="3" ht="28.5">
       <c r="A3" s="28"/>
       <c r="B3" s="29" t="s">
         <v>36</v>
@@ -1896,13 +1899,13 @@
     </row>
     <row r="36" ht="28.800000000000001" customHeight="1">
       <c r="A36" s="40"/>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="C36" s="42" t="s">
+      <c r="C36" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="42" t="s">
+      <c r="D36" s="30" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2062,7 +2065,7 @@
       <c r="A3" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="41" t="s">
         <v>94</v>
       </c>
       <c r="C3" t="s">
@@ -2079,7 +2082,7 @@
       <c r="B4" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="42" t="s">
         <v>91</v>
       </c>
       <c r="D4" t="s">
@@ -2093,7 +2096,7 @@
       <c r="B5" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="42" t="s">
         <v>91</v>
       </c>
       <c r="D5" t="s">
@@ -3108,7 +3111,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="45" width="24.421875"/>
+    <col customWidth="1" min="2" max="2" style="43" width="24.421875"/>
     <col customWidth="1" min="3" max="3" width="55.421875"/>
     <col customWidth="1" min="4" max="4" width="75.8515625"/>
   </cols>
@@ -3125,61 +3128,61 @@
       </c>
     </row>
     <row r="2" ht="42.75">
-      <c r="A2" s="46"/>
-      <c r="B2" s="47" t="s">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="46" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="3" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
     </row>
     <row r="4" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
     </row>
     <row r="5" ht="21.600000000000001" customHeight="1">
-      <c r="A5" s="46"/>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
     </row>
     <row r="6" ht="21.600000000000001" customHeight="1">
-      <c r="A6" s="46"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
     </row>
     <row r="7" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="46"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="49"/>
+      <c r="B8" s="47"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
     <row r="9" ht="41.25" customHeight="1">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="48" t="s">
         <v>104</v>
       </c>
       <c r="B9" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="49" t="s">
         <v>106</v>
       </c>
       <c r="D9" s="30" t="s">
@@ -3187,7 +3190,7 @@
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="52"/>
+      <c r="A10" s="50"/>
       <c r="B10" s="29" t="s">
         <v>108</v>
       </c>
@@ -3199,7 +3202,7 @@
       </c>
     </row>
     <row r="11" ht="36.75" customHeight="1">
-      <c r="A11" s="52"/>
+      <c r="A11" s="50"/>
       <c r="B11" s="29" t="s">
         <v>110</v>
       </c>
@@ -3211,7 +3214,7 @@
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="52"/>
+      <c r="A12" s="50"/>
       <c r="B12" s="29" t="s">
         <v>112</v>
       </c>
@@ -3223,28 +3226,32 @@
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="52"/>
+      <c r="A13" s="50"/>
       <c r="B13" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="30"/>
+      <c r="C13" s="51">
+        <v>45778</v>
+      </c>
       <c r="D13" s="30" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="14" ht="63.600000000000001" customHeight="1">
-      <c r="A14" s="52"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="50"/>
+      <c r="B14" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="30"/>
+      <c r="C14" s="51">
+        <v>46023</v>
+      </c>
       <c r="D14" s="30" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="49"/>
+      <c r="B15" s="47"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
     </row>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
   <si>
     <t>Name</t>
   </si>
@@ -309,6 +309,12 @@
   </si>
   <si>
     <t xml:space="preserve">Opção 'enable_integration' está desabilitada, o processo não irá integrar as obrigações.</t>
+  </si>
+  <si>
+    <t>LogMessage_NoExpensesToEspecificatedDebitAccount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não existem despesas com a conta de débito especificada: </t>
   </si>
   <si>
     <t xml:space="preserve">EXCEPTION LOG MESSAGES</t>
@@ -613,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -714,6 +720,12 @@
     <xf fontId="5" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="5" fillId="11" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
@@ -747,9 +759,6 @@
     </xf>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1789,8 +1798,12 @@
     </row>
     <row r="23" ht="27" customHeight="1">
       <c r="A23" s="39"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="30"/>
+      <c r="B23" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>68</v>
+      </c>
       <c r="D23" s="30"/>
     </row>
     <row r="24" ht="27" customHeight="1">
@@ -1830,135 +1843,135 @@
       <c r="D29" s="33"/>
     </row>
     <row r="30" ht="27.75" customHeight="1">
-      <c r="A30" s="40" t="s">
-        <v>67</v>
+      <c r="A30" s="42" t="s">
+        <v>69</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" ht="27.75" customHeight="1">
-      <c r="A31" s="40"/>
+      <c r="A31" s="42"/>
       <c r="B31" s="29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" ht="28.5">
-      <c r="A32" s="40"/>
+      <c r="A32" s="42"/>
       <c r="B32" s="29" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D32" s="30"/>
     </row>
     <row r="33" ht="28.5">
-      <c r="A33" s="40"/>
+      <c r="A33" s="42"/>
       <c r="B33" s="29" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D33" s="30"/>
     </row>
     <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="40"/>
+      <c r="A34" s="42"/>
       <c r="B34" s="29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" ht="31.199999999999999" customHeight="1">
-      <c r="A35" s="40"/>
+      <c r="A35" s="42"/>
       <c r="B35" s="29" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D35" s="30"/>
     </row>
     <row r="36" ht="28.800000000000001" customHeight="1">
-      <c r="A36" s="40"/>
+      <c r="A36" s="42"/>
       <c r="B36" s="29" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D36" s="30" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" ht="29.399999999999999" customHeight="1">
-      <c r="A37" s="40"/>
+      <c r="A37" s="42"/>
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="30"/>
     </row>
     <row r="38" ht="26.25" customHeight="1">
-      <c r="A38" s="40"/>
+      <c r="A38" s="42"/>
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="30"/>
     </row>
     <row r="39" ht="28.800000000000001" customHeight="1">
-      <c r="A39" s="40"/>
+      <c r="A39" s="42"/>
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="30"/>
     </row>
     <row r="40" ht="28.800000000000001" customHeight="1">
-      <c r="A40" s="40"/>
+      <c r="A40" s="42"/>
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="30"/>
     </row>
     <row r="41" ht="28.5" customHeight="1">
-      <c r="A41" s="40"/>
+      <c r="A41" s="42"/>
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="30"/>
     </row>
     <row r="42" ht="28.5" customHeight="1">
-      <c r="A42" s="40"/>
+      <c r="A42" s="42"/>
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="30"/>
     </row>
     <row r="43" ht="28.5" customHeight="1">
-      <c r="A43" s="40"/>
+      <c r="A43" s="42"/>
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="30"/>
     </row>
     <row r="44" ht="28.5" customHeight="1">
-      <c r="A44" s="40"/>
+      <c r="A44" s="42"/>
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="30"/>
     </row>
     <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" s="40"/>
+      <c r="A45" s="42"/>
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="30"/>
@@ -2016,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2049,58 +2062,58 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" t="s">
-        <v>91</v>
-      </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>91</v>
+        <v>98</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>91</v>
+        <v>101</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1"/>
@@ -3111,7 +3124,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="43" width="24.421875"/>
+    <col customWidth="1" min="2" max="2" style="45" width="24.421875"/>
     <col customWidth="1" min="3" max="3" width="55.421875"/>
     <col customWidth="1" min="4" max="4" width="75.8515625"/>
   </cols>
@@ -3128,130 +3141,130 @@
       </c>
     </row>
     <row r="2" ht="42.75">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="46" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="46" t="s">
+      <c r="A2" s="46"/>
+      <c r="B2" s="47" t="s">
         <v>103</v>
       </c>
+      <c r="C2" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="3" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="44"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
     </row>
     <row r="4" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
     </row>
     <row r="5" ht="21.600000000000001" customHeight="1">
-      <c r="A5" s="44"/>
-      <c r="B5" s="45"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
+      <c r="A5" s="46"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
     </row>
     <row r="6" ht="21.600000000000001" customHeight="1">
-      <c r="A6" s="44"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
+      <c r="A6" s="46"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
     </row>
     <row r="7" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="44"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
+      <c r="A7" s="46"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="47"/>
+      <c r="B8" s="49"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
     <row r="9" ht="41.25" customHeight="1">
-      <c r="A9" s="48" t="s">
-        <v>104</v>
+      <c r="A9" s="50" t="s">
+        <v>106</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>108</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="50"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="30">
         <v>60000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" ht="36.75" customHeight="1">
-      <c r="A11" s="50"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="29" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C11" s="30">
         <v>3000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="50"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="29" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="50"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="C13" s="51">
+        <v>117</v>
+      </c>
+      <c r="C13" s="53">
         <v>45778</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" ht="63.600000000000001" customHeight="1">
-      <c r="A14" s="50"/>
-      <c r="B14" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" s="51">
+      <c r="A14" s="52"/>
+      <c r="B14" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="53">
         <v>46023</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="47"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
     </row>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>Name</t>
   </si>
@@ -426,6 +426,18 @@
   </si>
   <si>
     <t xml:space="preserve">Endereço onde serão alocados os arquivos de importação e relatórios de erros de importação do processo</t>
+  </si>
+  <si>
+    <t>allDebitAccountImportationArchiveName</t>
+  </si>
+  <si>
+    <t>ContasDeDebitoGeral</t>
+  </si>
+  <si>
+    <t>especificDebitCount</t>
+  </si>
+  <si>
+    <t>2055,1055,2074,5572</t>
   </si>
   <si>
     <t>GetExpensesSettings</t>
@@ -619,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -719,12 +731,6 @@
     <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="5" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="11" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
@@ -1798,10 +1804,10 @@
     </row>
     <row r="23" ht="27" customHeight="1">
       <c r="A23" s="39"/>
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="30" t="s">
         <v>68</v>
       </c>
       <c r="D23" s="30"/>
@@ -1843,7 +1849,7 @@
       <c r="D29" s="33"/>
     </row>
     <row r="30" ht="27.75" customHeight="1">
-      <c r="A30" s="42" t="s">
+      <c r="A30" s="40" t="s">
         <v>69</v>
       </c>
       <c r="B30" s="29" t="s">
@@ -1857,7 +1863,7 @@
       </c>
     </row>
     <row r="31" ht="27.75" customHeight="1">
-      <c r="A31" s="42"/>
+      <c r="A31" s="40"/>
       <c r="B31" s="29" t="s">
         <v>73</v>
       </c>
@@ -1869,7 +1875,7 @@
       </c>
     </row>
     <row r="32" ht="28.5">
-      <c r="A32" s="42"/>
+      <c r="A32" s="40"/>
       <c r="B32" s="29" t="s">
         <v>76</v>
       </c>
@@ -1879,7 +1885,7 @@
       <c r="D32" s="30"/>
     </row>
     <row r="33" ht="28.5">
-      <c r="A33" s="42"/>
+      <c r="A33" s="40"/>
       <c r="B33" s="29" t="s">
         <v>78</v>
       </c>
@@ -1889,7 +1895,7 @@
       <c r="D33" s="30"/>
     </row>
     <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="42"/>
+      <c r="A34" s="40"/>
       <c r="B34" s="29" t="s">
         <v>80</v>
       </c>
@@ -1901,7 +1907,7 @@
       </c>
     </row>
     <row r="35" ht="31.199999999999999" customHeight="1">
-      <c r="A35" s="42"/>
+      <c r="A35" s="40"/>
       <c r="B35" s="29" t="s">
         <v>83</v>
       </c>
@@ -1911,7 +1917,7 @@
       <c r="D35" s="30"/>
     </row>
     <row r="36" ht="28.800000000000001" customHeight="1">
-      <c r="A36" s="42"/>
+      <c r="A36" s="40"/>
       <c r="B36" s="29" t="s">
         <v>85</v>
       </c>
@@ -1923,55 +1929,55 @@
       </c>
     </row>
     <row r="37" ht="29.399999999999999" customHeight="1">
-      <c r="A37" s="42"/>
+      <c r="A37" s="40"/>
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="30"/>
     </row>
     <row r="38" ht="26.25" customHeight="1">
-      <c r="A38" s="42"/>
+      <c r="A38" s="40"/>
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="30"/>
     </row>
     <row r="39" ht="28.800000000000001" customHeight="1">
-      <c r="A39" s="42"/>
+      <c r="A39" s="40"/>
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="30"/>
     </row>
     <row r="40" ht="28.800000000000001" customHeight="1">
-      <c r="A40" s="42"/>
+      <c r="A40" s="40"/>
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="30"/>
     </row>
     <row r="41" ht="28.5" customHeight="1">
-      <c r="A41" s="42"/>
+      <c r="A41" s="40"/>
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="30"/>
     </row>
     <row r="42" ht="28.5" customHeight="1">
-      <c r="A42" s="42"/>
+      <c r="A42" s="40"/>
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="30"/>
     </row>
     <row r="43" ht="28.5" customHeight="1">
-      <c r="A43" s="42"/>
+      <c r="A43" s="40"/>
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="30"/>
     </row>
     <row r="44" ht="28.5" customHeight="1">
-      <c r="A44" s="42"/>
+      <c r="A44" s="40"/>
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="30"/>
     </row>
     <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" s="42"/>
+      <c r="A45" s="40"/>
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="30"/>
@@ -2078,7 +2084,7 @@
       <c r="A3" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="41" t="s">
         <v>96</v>
       </c>
       <c r="C3" t="s">
@@ -2095,7 +2101,7 @@
       <c r="B4" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="42" t="s">
         <v>93</v>
       </c>
       <c r="D4" t="s">
@@ -2109,7 +2115,7 @@
       <c r="B5" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="42" t="s">
         <v>93</v>
       </c>
       <c r="D5" t="s">
@@ -3124,7 +3130,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="45" width="24.421875"/>
+    <col customWidth="1" min="2" max="2" style="43" width="38.421875"/>
     <col customWidth="1" min="3" max="3" width="55.421875"/>
     <col customWidth="1" min="4" max="4" width="75.8515625"/>
   </cols>
@@ -3141,130 +3147,138 @@
       </c>
     </row>
     <row r="2" ht="42.75">
-      <c r="A2" s="46"/>
-      <c r="B2" s="47" t="s">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="46" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="3" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="46"/>
     </row>
     <row r="4" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
     </row>
     <row r="5" ht="21.600000000000001" customHeight="1">
-      <c r="A5" s="46"/>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="6" ht="21.600000000000001" customHeight="1">
-      <c r="A6" s="46"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
     </row>
     <row r="7" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="46"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="49"/>
+      <c r="B8" s="47"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
     <row r="9" ht="41.25" customHeight="1">
-      <c r="A9" s="50" t="s">
-        <v>106</v>
+      <c r="A9" s="48" t="s">
+        <v>110</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>108</v>
+        <v>111</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>112</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="52"/>
+      <c r="A10" s="50"/>
       <c r="B10" s="29" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C10" s="30">
         <v>60000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" ht="36.75" customHeight="1">
-      <c r="A11" s="52"/>
+      <c r="A11" s="50"/>
       <c r="B11" s="29" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C11" s="30">
         <v>3000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="52"/>
+      <c r="A12" s="50"/>
       <c r="B12" s="29" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="52"/>
+      <c r="A13" s="50"/>
       <c r="B13" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" s="53">
+        <v>121</v>
+      </c>
+      <c r="C13" s="51">
         <v>45778</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" ht="63.600000000000001" customHeight="1">
-      <c r="A14" s="52"/>
+      <c r="A14" s="50"/>
       <c r="B14" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="53">
-        <v>46023</v>
+        <v>123</v>
+      </c>
+      <c r="C14" s="51">
+        <v>46022</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="49"/>
+      <c r="B15" s="47"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
     </row>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t>Name</t>
   </si>
@@ -128,6 +128,9 @@
     <t>obligationDebugCnpj</t>
   </si>
   <si>
+    <t>25385913000102</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -158,9 +161,6 @@
     <t>obligationDebugCompanyId</t>
   </si>
   <si>
-    <t>7a8d0889-71e5-4dab-9ec2-734bf7c46734</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -374,6 +374,24 @@
     <t xml:space="preserve">Caso não existam despesas na empresa em questão.</t>
   </si>
   <si>
+    <t>ExceptionMessage_ExpenseRequest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erro no processo de requisição das despesas - Get Expenses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caso haja um erro no processo de Get Expenses</t>
+  </si>
+  <si>
+    <t>ExceptionMessage_ExpenseDatesDefinition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erro ao definir as datas de inicio e final do Get Exepenses. As datas devem estar com o tipo "texto" na planilha "Config.xlsx". Verifique também se as datas estão de acordo com a realidade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caso haja um erro durante o processo de definição de datas do request das despesas. </t>
+  </si>
+  <si>
     <t>Asset</t>
   </si>
   <si>
@@ -476,10 +494,16 @@
     <t>getExpenses_dateStart</t>
   </si>
   <si>
+    <t>01/05/2025</t>
+  </si>
+  <si>
     <t xml:space="preserve">Inicio do range de datas que abrange a data de vencimento das despesas que irão ser importadas. Deve estar no formato "dd/MM/yyyy" e só deve existir caso o getExpenses_dateEnd existir também.</t>
   </si>
   <si>
     <t>getExpenses_dateEnd</t>
+  </si>
+  <si>
+    <t>31/12/2025</t>
   </si>
   <si>
     <t xml:space="preserve">Fim do range de datas que abrange a data de vencimento das despesas que irão ser importadas. Deve estar no formato "dd/MM/yyyy" e só deve existir caso o getExpenses_dateStart existir também. Deve ser posterior ao getExpenses_dateStart</t>
@@ -489,9 +513,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-  </numFmts>
   <fonts count="6">
     <font>
       <sz val="11.000000"/>
@@ -631,7 +652,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -763,7 +784,10 @@
     <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1443,19 +1467,19 @@
       <c r="B15" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="19"/>
+      <c r="C15" s="19" t="s">
+        <v>22</v>
+      </c>
       <c r="D15" s="20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="34.799999999999997" customHeight="1">
       <c r="A16" s="13"/>
       <c r="B16" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="14" t="s">
         <v>24</v>
       </c>
+      <c r="C16" s="14"/>
       <c r="D16" s="20" t="s">
         <v>25</v>
       </c>
@@ -1930,15 +1954,27 @@
     </row>
     <row r="37" ht="29.399999999999999" customHeight="1">
       <c r="A37" s="40"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-    </row>
-    <row r="38" ht="26.25" customHeight="1">
+      <c r="B37" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" ht="42.75">
       <c r="A38" s="40"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
+      <c r="B38" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="39" ht="28.800000000000001" customHeight="1">
       <c r="A39" s="40"/>
@@ -2035,13 +2071,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2068,58 +2104,58 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1"/>
@@ -3149,22 +3185,22 @@
     <row r="2" ht="42.75">
       <c r="A2" s="44"/>
       <c r="B2" s="45" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" ht="21.600000000000001" customHeight="1">
       <c r="A3" s="44"/>
       <c r="B3" s="45" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D3" s="46"/>
     </row>
@@ -3178,10 +3214,10 @@
       <c r="A5" s="44"/>
       <c r="B5" s="45"/>
       <c r="C5" s="46" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" ht="21.600000000000001" customHeight="1">
@@ -3204,76 +3240,76 @@
     </row>
     <row r="9" ht="41.25" customHeight="1">
       <c r="A9" s="48" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
       <c r="A10" s="50"/>
       <c r="B10" s="29" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C10" s="30">
         <v>60000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" ht="36.75" customHeight="1">
       <c r="A11" s="50"/>
       <c r="B11" s="29" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C11" s="30">
         <v>3000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
       <c r="A12" s="50"/>
       <c r="B12" s="29" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="50"/>
       <c r="B13" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="C13" s="51">
-        <v>45778</v>
+        <v>127</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>128</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" ht="63.600000000000001" customHeight="1">
       <c r="A14" s="50"/>
       <c r="B14" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="51">
-        <v>46022</v>
+        <v>130</v>
+      </c>
+      <c r="C14" s="52" t="s">
+        <v>131</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" ht="14.25">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t>Name</t>
   </si>
@@ -452,10 +452,13 @@
     <t>ContasDeDebitoGeral</t>
   </si>
   <si>
-    <t>especificDebitCount</t>
+    <t>especificDebitAccount</t>
   </si>
   <si>
     <t>2055,1055,2074,5572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Domínio pode apresentar erro de acordo com a quantidade de despesas inseridas em um determinado arquivo de importação. Por isso, existem as contas de débito específicas que devem estar separadas por arquivo de importação.Deve estar no fomraco "contaDeDebito,contaDeDebito,contaDeDebito"</t>
   </si>
   <si>
     <t>GetExpensesSettings</t>
@@ -652,7 +655,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -764,13 +767,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -783,9 +792,6 @@
     </xf>
     <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3182,7 +3188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="42.75">
+    <row r="2" s="43" customFormat="1" ht="42.75">
       <c r="A2" s="44"/>
       <c r="B2" s="45" t="s">
         <v>109</v>
@@ -3194,7 +3200,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" ht="21.600000000000001" customHeight="1">
+    <row r="3" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
       <c r="A3" s="44"/>
       <c r="B3" s="45" t="s">
         <v>112</v>
@@ -3204,29 +3210,31 @@
       </c>
       <c r="D3" s="46"/>
     </row>
-    <row r="4" ht="21.600000000000001" customHeight="1">
+    <row r="4" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
       <c r="A4" s="44"/>
       <c r="B4" s="45"/>
       <c r="C4" s="46"/>
       <c r="D4" s="46"/>
     </row>
-    <row r="5" ht="21.600000000000001" customHeight="1">
+    <row r="5" s="43" customFormat="1" ht="57">
       <c r="A5" s="44"/>
-      <c r="B5" s="45"/>
+      <c r="B5" s="47" t="s">
+        <v>114</v>
+      </c>
       <c r="C5" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="46" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="6" ht="21.600000000000001" customHeight="1">
+      <c r="D5" s="48" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
       <c r="A6" s="44"/>
       <c r="B6" s="45"/>
       <c r="C6" s="46"/>
       <c r="D6" s="46"/>
     </row>
-    <row r="7" ht="21.600000000000001" customHeight="1">
+    <row r="7" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
       <c r="A7" s="44"/>
       <c r="B7" s="45"/>
       <c r="C7" s="46"/>
@@ -3234,87 +3242,87 @@
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="47"/>
+      <c r="B8" s="49"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
     <row r="9" ht="41.25" customHeight="1">
-      <c r="A9" s="48" t="s">
-        <v>116</v>
+      <c r="A9" s="50" t="s">
+        <v>117</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="49" t="s">
         <v>118</v>
       </c>
+      <c r="C9" s="51" t="s">
+        <v>119</v>
+      </c>
       <c r="D9" s="30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="50"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C10" s="30">
         <v>60000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" ht="36.75" customHeight="1">
-      <c r="A11" s="50"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C11" s="30">
         <v>3000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="50"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="50"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="51" t="s">
         <v>128</v>
       </c>
+      <c r="C13" s="53" t="s">
+        <v>129</v>
+      </c>
       <c r="D13" s="30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" ht="63.600000000000001" customHeight="1">
-      <c r="A14" s="50"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" s="52" t="s">
         <v>131</v>
       </c>
+      <c r="C14" s="53" t="s">
+        <v>132</v>
+      </c>
       <c r="D14" s="30" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="47"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
     </row>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t>Name</t>
   </si>
@@ -128,9 +128,6 @@
     <t>obligationDebugCnpj</t>
   </si>
   <si>
-    <t>25385913000102</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -161,6 +158,9 @@
     <t>obligationDebugCompanyId</t>
   </si>
   <si>
+    <t>7a8d0889-71e5-4dab-9ec2-734bf7c46734</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -435,6 +435,24 @@
   </si>
   <si>
     <t xml:space="preserve">Codigo do contador dentro do domínio</t>
+  </si>
+  <si>
+    <t>databaseConnectionString</t>
+  </si>
+  <si>
+    <t>database_connection_string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">String de conexão com o banco de dados do Domínio</t>
+  </si>
+  <si>
+    <t>databaseProviderName</t>
+  </si>
+  <si>
+    <t>database_provider_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provider name para conexão no banco de dados do Domínio</t>
   </si>
   <si>
     <t>mainPath</t>
@@ -703,6 +721,7 @@
     <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="2" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
@@ -771,9 +790,6 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1473,19 +1489,19 @@
       <c r="B15" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="20" t="s">
         <v>22</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="16" ht="34.799999999999997" customHeight="1">
       <c r="A16" s="13"/>
       <c r="B16" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="14"/>
       <c r="D16" s="20" t="s">
         <v>25</v>
       </c>
@@ -1497,13 +1513,13 @@
       <c r="D17" s="5"/>
     </row>
     <row r="18" ht="46.799999999999997" customHeight="1">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="22" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="23" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="14" t="s">
@@ -1511,21 +1527,21 @@
       </c>
     </row>
     <row r="19" ht="46.799999999999997" customHeight="1">
-      <c r="A19" s="21"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="24" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="14"/>
     </row>
     <row r="20" ht="43.200000000000003" customHeight="1">
-      <c r="A20" s="21"/>
+      <c r="A20" s="22"/>
       <c r="B20" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="14"/>
@@ -1584,20 +1600,20 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8.00390625"/>
-    <col customWidth="1" min="2" max="2" style="24" width="52.140625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="25" width="63.11328125"/>
-    <col customWidth="1" min="4" max="4" style="25" width="84.140625"/>
+    <col customWidth="1" min="2" max="2" style="25" width="52.140625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="26" width="63.11328125"/>
+    <col customWidth="1" min="4" max="4" style="26" width="84.140625"/>
     <col customWidth="1" min="5" max="27" width="8.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2"/>
@@ -1625,79 +1641,79 @@
       <c r="AA1" s="2"/>
     </row>
     <row r="2" ht="28.5">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="29"/>
+      <c r="B2" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="30">
+      <c r="C2" s="31">
         <v>1</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="31" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3" ht="28.5">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29" t="s">
+      <c r="A3" s="29"/>
+      <c r="B3" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3" s="31">
         <v>3</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="31" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29" t="s">
+      <c r="A4" s="29"/>
+      <c r="B4" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="31" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" ht="28.5">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29" t="s">
+      <c r="A5" s="29"/>
+      <c r="B5" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>2</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="31" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" ht="28.5">
-      <c r="A6" s="28"/>
-      <c r="B6" s="29" t="s">
+      <c r="A6" s="29"/>
+      <c r="B6" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>2</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="31" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" s="31" customFormat="1" ht="17.399999999999999" customHeight="1">
+    <row r="7" s="32" customFormat="1" ht="17.399999999999999" customHeight="1">
       <c r="A7" s="5"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
     </row>
     <row r="8" ht="39.75" customHeight="1">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="35" t="s">
         <v>45</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="36">
         <v>30000</v>
       </c>
       <c r="D8" s="15" t="s">
@@ -1705,11 +1721,11 @@
       </c>
     </row>
     <row r="9" ht="39.75" customHeight="1">
-      <c r="A9" s="36"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="36">
         <v>20000</v>
       </c>
       <c r="D9" s="15" t="s">
@@ -1717,11 +1733,11 @@
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="36"/>
+      <c r="A10" s="37"/>
       <c r="B10" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="36">
         <v>0</v>
       </c>
       <c r="D10" s="15" t="s">
@@ -1729,11 +1745,11 @@
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="36"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="36">
         <v>0</v>
       </c>
       <c r="D11" s="15" t="s">
@@ -1742,297 +1758,297 @@
     </row>
     <row r="12" ht="17.399999999999999" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
     </row>
     <row r="13" ht="22.800000000000001" customHeight="1">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="31" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" ht="28.199999999999999" customHeight="1">
-      <c r="A14" s="37"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
     </row>
     <row r="15" ht="28.199999999999999" customHeight="1">
-      <c r="A15" s="37"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="37"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="37"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
     </row>
     <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="37"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
     </row>
     <row r="19" ht="17.399999999999999" customHeight="1">
-      <c r="A19" s="38"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="31" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="39"/>
-      <c r="B21" s="29" t="s">
+      <c r="A21" s="40"/>
+      <c r="B21" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="31" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="22" ht="33.75" customHeight="1">
-      <c r="A22" s="39"/>
-      <c r="B22" s="30" t="s">
+      <c r="A22" s="40"/>
+      <c r="B22" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="30"/>
+      <c r="D22" s="31"/>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="39"/>
-      <c r="B23" s="29" t="s">
+      <c r="A23" s="40"/>
+      <c r="B23" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C23" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="30"/>
+      <c r="D23" s="31"/>
     </row>
     <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="39"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
+      <c r="A24" s="40"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
     </row>
     <row r="25" ht="27" customHeight="1">
-      <c r="A25" s="39"/>
-      <c r="B25" s="29"/>
+      <c r="A25" s="40"/>
+      <c r="B25" s="30"/>
       <c r="C25" s="20"/>
-      <c r="D25" s="30"/>
+      <c r="D25" s="31"/>
     </row>
     <row r="26" ht="27" customHeight="1">
-      <c r="A26" s="39"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
+      <c r="A26" s="40"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
     </row>
     <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="39"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
+      <c r="A27" s="40"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
     </row>
     <row r="28" ht="27" customHeight="1">
-      <c r="A28" s="39"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
+      <c r="A28" s="40"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
     </row>
     <row r="29" ht="17.399999999999999" customHeight="1">
       <c r="A29" s="5"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
     </row>
     <row r="30" ht="27.75" customHeight="1">
-      <c r="A30" s="40" t="s">
+      <c r="A30" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="30" t="s">
+      <c r="D30" s="31" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="31" ht="27.75" customHeight="1">
-      <c r="A31" s="40"/>
-      <c r="B31" s="29" t="s">
+      <c r="A31" s="41"/>
+      <c r="B31" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="30" t="s">
+      <c r="C31" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D31" s="30" t="s">
+      <c r="D31" s="31" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="32" ht="28.5">
-      <c r="A32" s="40"/>
-      <c r="B32" s="29" t="s">
+      <c r="A32" s="41"/>
+      <c r="B32" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="30"/>
+      <c r="D32" s="31"/>
     </row>
     <row r="33" ht="28.5">
-      <c r="A33" s="40"/>
-      <c r="B33" s="29" t="s">
+      <c r="A33" s="41"/>
+      <c r="B33" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="30" t="s">
+      <c r="C33" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="D33" s="30"/>
+      <c r="D33" s="31"/>
     </row>
     <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="40"/>
-      <c r="B34" s="29" t="s">
+      <c r="A34" s="41"/>
+      <c r="B34" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="C34" s="30" t="s">
+      <c r="C34" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="31" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="35" ht="31.199999999999999" customHeight="1">
-      <c r="A35" s="40"/>
-      <c r="B35" s="29" t="s">
+      <c r="A35" s="41"/>
+      <c r="B35" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="30"/>
+      <c r="D35" s="31"/>
     </row>
     <row r="36" ht="28.800000000000001" customHeight="1">
-      <c r="A36" s="40"/>
-      <c r="B36" s="29" t="s">
+      <c r="A36" s="41"/>
+      <c r="B36" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C36" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="D36" s="30" t="s">
+      <c r="D36" s="31" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="37" ht="29.399999999999999" customHeight="1">
-      <c r="A37" s="40"/>
-      <c r="B37" s="29" t="s">
+      <c r="A37" s="41"/>
+      <c r="B37" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="30" t="s">
+      <c r="C37" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="D37" s="30" t="s">
+      <c r="D37" s="31" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="38" ht="42.75">
-      <c r="A38" s="40"/>
-      <c r="B38" s="29" t="s">
+      <c r="A38" s="41"/>
+      <c r="B38" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="30" t="s">
+      <c r="D38" s="31" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="39" ht="28.800000000000001" customHeight="1">
-      <c r="A39" s="40"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
+      <c r="A39" s="41"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
     </row>
     <row r="40" ht="28.800000000000001" customHeight="1">
-      <c r="A40" s="40"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
+      <c r="A40" s="41"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
     </row>
     <row r="41" ht="28.5" customHeight="1">
-      <c r="A41" s="40"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
+      <c r="A41" s="41"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
     </row>
     <row r="42" ht="28.5" customHeight="1">
-      <c r="A42" s="40"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
+      <c r="A42" s="41"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
     </row>
     <row r="43" ht="28.5" customHeight="1">
-      <c r="A43" s="40"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
+      <c r="A43" s="41"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
     </row>
     <row r="44" ht="28.5" customHeight="1">
-      <c r="A44" s="40"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
+      <c r="A44" s="41"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
     </row>
     <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" s="40"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
+      <c r="A45" s="41"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
     </row>
     <row r="46" ht="28.5" customHeight="1">
-      <c r="B46" s="24"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
     </row>
     <row r="47" ht="28.5" customHeight="1">
-      <c r="B47" s="24"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="25"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
     </row>
     <row r="48" ht="28.5" customHeight="1"/>
     <row r="49" ht="28.5" customHeight="1"/>
@@ -2126,7 +2142,7 @@
       <c r="A3" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="42" t="s">
         <v>102</v>
       </c>
       <c r="C3" t="s">
@@ -2143,7 +2159,7 @@
       <c r="B4" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="43" t="s">
         <v>99</v>
       </c>
       <c r="D4" t="s">
@@ -2157,15 +2173,41 @@
       <c r="B5" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="43" t="s">
         <v>99</v>
       </c>
       <c r="D5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1"/>
-    <row r="7" ht="14.25" customHeight="1"/>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" t="s">
+        <v>114</v>
+      </c>
+    </row>
     <row r="8" ht="14.25" customHeight="1"/>
     <row r="9" ht="14.25" customHeight="1"/>
     <row r="10" ht="14.25" customHeight="1"/>
@@ -3172,73 +3214,73 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="43" width="38.421875"/>
+    <col customWidth="1" min="2" max="2" style="44" width="38.421875"/>
     <col customWidth="1" min="3" max="3" width="55.421875"/>
     <col customWidth="1" min="4" max="4" width="75.8515625"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="43" customFormat="1" ht="42.75">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="46" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="46" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="44"/>
-      <c r="B3" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="46"/>
-    </row>
-    <row r="4" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-    </row>
-    <row r="5" s="43" customFormat="1" ht="57">
-      <c r="A5" s="44"/>
+    <row r="2" s="44" customFormat="1" ht="42.75">
+      <c r="A2" s="45"/>
+      <c r="B2" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="47" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A3" s="45"/>
+      <c r="B3" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="47"/>
+    </row>
+    <row r="4" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A4" s="45"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+    </row>
+    <row r="5" s="44" customFormat="1" ht="57">
+      <c r="A5" s="45"/>
       <c r="B5" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>115</v>
+        <v>120</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>121</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A6" s="44"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-    </row>
-    <row r="7" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="44"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A6" s="45"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+    </row>
+    <row r="7" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A7" s="45"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="5"/>
@@ -3248,76 +3290,76 @@
     </row>
     <row r="9" ht="41.25" customHeight="1">
       <c r="A9" s="50" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>118</v>
+        <v>123</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>124</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>120</v>
+        <v>125</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
       <c r="A10" s="52"/>
-      <c r="B10" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="C10" s="30">
+      <c r="B10" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="31">
         <v>60000</v>
       </c>
-      <c r="D10" s="30" t="s">
-        <v>122</v>
+      <c r="D10" s="31" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="11" ht="36.75" customHeight="1">
       <c r="A11" s="52"/>
-      <c r="B11" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="30">
+      <c r="B11" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" s="31">
         <v>3000</v>
       </c>
-      <c r="D11" s="30" t="s">
-        <v>124</v>
+      <c r="D11" s="31" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
       <c r="A12" s="52"/>
-      <c r="B12" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>127</v>
+      <c r="B12" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="52"/>
-      <c r="B13" s="29" t="s">
-        <v>128</v>
+      <c r="B13" s="30" t="s">
+        <v>134</v>
       </c>
       <c r="C13" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="14" ht="63.600000000000001" customHeight="1">
       <c r="A14" s="52"/>
-      <c r="B14" s="29" t="s">
-        <v>131</v>
+      <c r="B14" s="30" t="s">
+        <v>137</v>
       </c>
       <c r="C14" s="53" t="s">
-        <v>132</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>133</v>
+        <v>138</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="15" ht="14.25">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t>Name</t>
   </si>
@@ -284,6 +284,12 @@
     <t xml:space="preserve">Mensagem de integração da obrigação no backoffice quando o processo for bem sucedido.</t>
   </si>
   <si>
+    <t>LogMessage_SuccessOpenWorkPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Periodo de trabalho aberto com sucesso!</t>
+  </si>
+  <si>
     <t xml:space="preserve">INFORMATION MESSAGES</t>
   </si>
   <si>
@@ -317,6 +323,18 @@
     <t xml:space="preserve">Não existem despesas com a conta de débito especificada: </t>
   </si>
   <si>
+    <t>LogMessage_OpenWorkPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abrindo periodo de trabalho...</t>
+  </si>
+  <si>
+    <t>LogMessage_OpenClosing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abrindo periodo de fechamento...</t>
+  </si>
+  <si>
     <t xml:space="preserve">EXCEPTION LOG MESSAGES</t>
   </si>
   <si>
@@ -477,6 +495,15 @@
   </si>
   <si>
     <t xml:space="preserve">O Domínio pode apresentar erro de acordo com a quantidade de despesas inseridas em um determinado arquivo de importação. Por isso, existem as contas de débito específicas que devem estar separadas por arquivo de importação.Deve estar no fomraco "contaDeDebito,contaDeDebito,contaDeDebito"</t>
+  </si>
+  <si>
+    <t>dateEndWorkPeriod</t>
+  </si>
+  <si>
+    <t>01/01/2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data final do periodo de trabalho cadastrado no sistema Domínio.</t>
   </si>
   <si>
     <t>GetExpensesSettings</t>
@@ -673,7 +700,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -795,6 +822,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1778,8 +1808,12 @@
     </row>
     <row r="14" ht="28.199999999999999" customHeight="1">
       <c r="A14" s="38"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="31"/>
+      <c r="B14" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>59</v>
+      </c>
       <c r="D14" s="31"/>
     </row>
     <row r="15" ht="28.199999999999999" customHeight="1">
@@ -1814,60 +1848,68 @@
     </row>
     <row r="20" ht="27" customHeight="1">
       <c r="A20" s="40" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" ht="27" customHeight="1">
       <c r="A21" s="40"/>
       <c r="B21" s="30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" ht="33.75" customHeight="1">
       <c r="A22" s="40"/>
       <c r="B22" s="31" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D22" s="31"/>
     </row>
     <row r="23" ht="27" customHeight="1">
       <c r="A23" s="40"/>
       <c r="B23" s="30" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D23" s="31"/>
     </row>
     <row r="24" ht="27" customHeight="1">
       <c r="A24" s="40"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="31"/>
+      <c r="B24" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>72</v>
+      </c>
       <c r="D24" s="31"/>
     </row>
     <row r="25" ht="27" customHeight="1">
       <c r="A25" s="40"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="20"/>
+      <c r="B25" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>74</v>
+      </c>
       <c r="D25" s="31"/>
     </row>
     <row r="26" ht="27" customHeight="1">
@@ -1896,111 +1938,111 @@
     </row>
     <row r="30" ht="27.75" customHeight="1">
       <c r="A30" s="41" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" ht="27.75" customHeight="1">
       <c r="A31" s="41"/>
       <c r="B31" s="30" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" ht="28.5">
       <c r="A32" s="41"/>
       <c r="B32" s="30" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D32" s="31"/>
     </row>
     <row r="33" ht="28.5">
       <c r="A33" s="41"/>
       <c r="B33" s="30" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D33" s="31"/>
     </row>
     <row r="34" ht="27.75" customHeight="1">
       <c r="A34" s="41"/>
       <c r="B34" s="30" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" ht="31.199999999999999" customHeight="1">
       <c r="A35" s="41"/>
       <c r="B35" s="30" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D35" s="31"/>
     </row>
     <row r="36" ht="28.800000000000001" customHeight="1">
       <c r="A36" s="41"/>
       <c r="B36" s="30" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" ht="29.399999999999999" customHeight="1">
       <c r="A37" s="41"/>
       <c r="B37" s="30" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" ht="42.75">
       <c r="A38" s="41"/>
       <c r="B38" s="30" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" ht="28.800000000000001" customHeight="1">
       <c r="A39" s="41"/>
-      <c r="B39" s="30"/>
+      <c r="B39" s="31"/>
       <c r="C39" s="31"/>
       <c r="D39" s="31"/>
     </row>
@@ -2093,13 +2135,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2126,86 +2168,86 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="42" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="42" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1"/>
@@ -3233,22 +3275,22 @@
     <row r="2" s="44" customFormat="1" ht="42.75">
       <c r="A2" s="45"/>
       <c r="B2" s="46" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
       <c r="A3" s="45"/>
       <c r="B3" s="46" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D3" s="47"/>
     </row>
@@ -3261,20 +3303,26 @@
     <row r="5" s="44" customFormat="1" ht="57">
       <c r="A5" s="45"/>
       <c r="B5" s="47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
       <c r="A6" s="45"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
+      <c r="B6" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="7" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
       <c r="A7" s="45"/>
@@ -3284,87 +3332,87 @@
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="49"/>
+      <c r="B8" s="50"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
     <row r="9" ht="41.25" customHeight="1">
-      <c r="A9" s="50" t="s">
-        <v>123</v>
+      <c r="A9" s="51" t="s">
+        <v>132</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>125</v>
+        <v>133</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>134</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="52"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="30" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C10" s="31">
         <v>60000</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" ht="36.75" customHeight="1">
-      <c r="A11" s="52"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="30" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C11" s="31">
         <v>3000</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="52"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="30" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="52"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="53" t="s">
-        <v>135</v>
+        <v>143</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>144</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" ht="63.600000000000001" customHeight="1">
-      <c r="A14" s="52"/>
+      <c r="A14" s="53"/>
       <c r="B14" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="C14" s="53" t="s">
-        <v>138</v>
+        <v>146</v>
+      </c>
+      <c r="C14" s="54" t="s">
+        <v>147</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="49"/>
+      <c r="B15" s="50"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
     </row>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <si>
     <t>Name</t>
   </si>
@@ -110,10 +110,16 @@
     <t>obligationDateStart</t>
   </si>
   <si>
+    <t>01/03/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data inicial do range de datas que deve abranger a data de vencimento da obrigação em questão, se não estiver definida nenhuma data nessa variável, o processo define o primeiro e o ultimo dia do mês como as datas de inicio e fim do range.</t>
   </si>
   <si>
     <t>obligationDateEnd</t>
+  </si>
+  <si>
+    <t>05/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Data final do range de datas que deve abranger a data de vencimento da obrigação em questão, se não estiver definida nenhuma data nessa variável, o processo define o primeiro e o ultimo dia do mês como as datas de inicio e fim do range.</t>
@@ -700,7 +706,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -742,6 +748,9 @@
     </xf>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1479,25 +1488,29 @@
       <c r="B11" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="16"/>
+      <c r="C11" s="16" t="s">
+        <v>16</v>
+      </c>
       <c r="D11" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" ht="61.200000000000003" customHeight="1">
       <c r="A12" s="13"/>
       <c r="B12" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="15" t="s">
         <v>18</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" ht="28.800000000000001" customHeight="1">
       <c r="A13" s="13"/>
       <c r="B13" s="14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C13" s="14" t="b">
         <v>1</v>
@@ -1507,7 +1520,7 @@
     <row r="14" ht="28.800000000000001" customHeight="1">
       <c r="A14" s="13"/>
       <c r="B14" s="14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C14" s="14" t="b">
         <v>0</v>
@@ -1516,24 +1529,24 @@
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="13"/>
-      <c r="B15" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="20" t="s">
-        <v>22</v>
+      <c r="B15" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" ht="34.799999999999997" customHeight="1">
       <c r="A16" s="13"/>
-      <c r="B16" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="20" t="s">
+      <c r="B16" s="19" t="s">
         <v>25</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" ht="17.399999999999999" customHeight="1">
@@ -1543,36 +1556,36 @@
       <c r="D17" s="5"/>
     </row>
     <row r="18" ht="46.799999999999997" customHeight="1">
-      <c r="A18" s="22" t="s">
-        <v>26</v>
+      <c r="A18" s="23" t="s">
+        <v>28</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>30</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" ht="46.799999999999997" customHeight="1">
-      <c r="A19" s="22"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>33</v>
       </c>
       <c r="D19" s="14"/>
     </row>
     <row r="20" ht="43.200000000000003" customHeight="1">
-      <c r="A20" s="22"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>35</v>
       </c>
       <c r="D20" s="14"/>
     </row>
@@ -1630,20 +1643,20 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8.00390625"/>
-    <col customWidth="1" min="2" max="2" style="25" width="52.140625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="26" width="63.11328125"/>
-    <col customWidth="1" min="4" max="4" style="26" width="84.140625"/>
+    <col customWidth="1" min="2" max="2" style="26" width="52.140625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="27" width="63.11328125"/>
+    <col customWidth="1" min="4" max="4" style="27" width="84.140625"/>
     <col customWidth="1" min="5" max="27" width="8.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2"/>
@@ -1671,426 +1684,426 @@
       <c r="AA1" s="2"/>
     </row>
     <row r="2" ht="28.5">
-      <c r="A2" s="29"/>
-      <c r="B2" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="31">
+      <c r="A2" s="30"/>
+      <c r="B2" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="32">
         <v>1</v>
       </c>
-      <c r="D2" s="31" t="s">
-        <v>35</v>
+      <c r="D2" s="32" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3" ht="28.5">
-      <c r="A3" s="29"/>
-      <c r="B3" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="31">
+      <c r="A3" s="30"/>
+      <c r="B3" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="32">
         <v>3</v>
       </c>
-      <c r="D3" s="31" t="s">
-        <v>37</v>
+      <c r="D3" s="32" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="29"/>
-      <c r="B4" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="31" t="s">
+      <c r="A4" s="30"/>
+      <c r="B4" s="31" t="s">
         <v>40</v>
       </c>
+      <c r="C4" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="5" ht="28.5">
-      <c r="A5" s="29"/>
-      <c r="B5" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="31">
+      <c r="A5" s="30"/>
+      <c r="B5" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="32">
         <v>2</v>
       </c>
-      <c r="D5" s="31" t="s">
-        <v>42</v>
+      <c r="D5" s="32" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6" ht="28.5">
-      <c r="A6" s="29"/>
-      <c r="B6" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="31">
+      <c r="A6" s="30"/>
+      <c r="B6" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="32">
         <v>2</v>
       </c>
-      <c r="D6" s="31" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" s="32" customFormat="1" ht="17.399999999999999" customHeight="1">
+      <c r="D6" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" s="33" customFormat="1" ht="17.399999999999999" customHeight="1">
       <c r="A7" s="5"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
     </row>
     <row r="8" ht="39.75" customHeight="1">
-      <c r="A8" s="35" t="s">
-        <v>45</v>
+      <c r="A8" s="36" t="s">
+        <v>47</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="36">
+        <v>48</v>
+      </c>
+      <c r="C8" s="37">
         <v>30000</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" ht="39.75" customHeight="1">
-      <c r="A9" s="37"/>
+      <c r="A9" s="38"/>
       <c r="B9" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="36">
+        <v>50</v>
+      </c>
+      <c r="C9" s="37">
         <v>20000</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="37"/>
+      <c r="A10" s="38"/>
       <c r="B10" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="36">
+        <v>52</v>
+      </c>
+      <c r="C10" s="37">
         <v>0</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="37"/>
+      <c r="A11" s="38"/>
       <c r="B11" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="36">
+        <v>54</v>
+      </c>
+      <c r="C11" s="37">
         <v>0</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" ht="17.399999999999999" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
     </row>
     <row r="13" ht="22.800000000000001" customHeight="1">
-      <c r="A13" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="31" t="s">
+      <c r="A13" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="B13" s="31" t="s">
         <v>57</v>
       </c>
+      <c r="C13" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="14" ht="28.199999999999999" customHeight="1">
-      <c r="A14" s="38"/>
-      <c r="B14" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="31"/>
+      <c r="A14" s="39"/>
+      <c r="B14" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="32"/>
     </row>
     <row r="15" ht="28.199999999999999" customHeight="1">
-      <c r="A15" s="38"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
+      <c r="A15" s="39"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="38"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
+      <c r="A16" s="39"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="38"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
     </row>
     <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="38"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
+      <c r="A18" s="39"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
     </row>
     <row r="19" ht="17.399999999999999" customHeight="1">
-      <c r="A19" s="39"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
+      <c r="A19" s="40"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="31" t="s">
+      <c r="A20" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="B20" s="31" t="s">
         <v>63</v>
       </c>
+      <c r="C20" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="40"/>
-      <c r="B21" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="31" t="s">
+      <c r="A21" s="41"/>
+      <c r="B21" s="31" t="s">
         <v>66</v>
       </c>
+      <c r="C21" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="22" ht="33.75" customHeight="1">
-      <c r="A22" s="40"/>
-      <c r="B22" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="31"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="32"/>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="40"/>
-      <c r="B23" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="31"/>
+      <c r="A23" s="41"/>
+      <c r="B23" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="32"/>
     </row>
     <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="40"/>
-      <c r="B24" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" s="31"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="32"/>
     </row>
     <row r="25" ht="27" customHeight="1">
-      <c r="A25" s="40"/>
-      <c r="B25" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" s="31"/>
+      <c r="A25" s="41"/>
+      <c r="B25" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="32"/>
     </row>
     <row r="26" ht="27" customHeight="1">
-      <c r="A26" s="40"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
+      <c r="A26" s="41"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
     </row>
     <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="40"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
+      <c r="A27" s="41"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
     </row>
     <row r="28" ht="27" customHeight="1">
-      <c r="A28" s="40"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
+      <c r="A28" s="41"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
     </row>
     <row r="29" ht="17.399999999999999" customHeight="1">
       <c r="A29" s="5"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
     </row>
     <row r="30" ht="27.75" customHeight="1">
-      <c r="A30" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="31" t="s">
+      <c r="A30" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="D30" s="31" t="s">
+      <c r="B30" s="31" t="s">
         <v>78</v>
       </c>
+      <c r="C30" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="31" ht="27.75" customHeight="1">
-      <c r="A31" s="41"/>
-      <c r="B31" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="31" t="s">
+      <c r="A31" s="42"/>
+      <c r="B31" s="31" t="s">
         <v>81</v>
       </c>
+      <c r="C31" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" s="32" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="32" ht="28.5">
-      <c r="A32" s="41"/>
-      <c r="B32" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32" s="31"/>
+      <c r="A32" s="42"/>
+      <c r="B32" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="32"/>
     </row>
     <row r="33" ht="28.5">
-      <c r="A33" s="41"/>
-      <c r="B33" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33" s="31"/>
+      <c r="A33" s="42"/>
+      <c r="B33" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="D33" s="32"/>
     </row>
     <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="41"/>
-      <c r="B34" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="D34" s="31" t="s">
+      <c r="A34" s="42"/>
+      <c r="B34" s="31" t="s">
         <v>88</v>
       </c>
+      <c r="C34" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="32" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="35" ht="31.199999999999999" customHeight="1">
-      <c r="A35" s="41"/>
-      <c r="B35" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" s="31"/>
+      <c r="A35" s="42"/>
+      <c r="B35" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="32"/>
     </row>
     <row r="36" ht="28.800000000000001" customHeight="1">
-      <c r="A36" s="41"/>
-      <c r="B36" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" s="31" t="s">
+      <c r="A36" s="42"/>
+      <c r="B36" s="31" t="s">
         <v>93</v>
       </c>
+      <c r="C36" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="32" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="37" ht="29.399999999999999" customHeight="1">
-      <c r="A37" s="41"/>
-      <c r="B37" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" s="31" t="s">
+      <c r="A37" s="42"/>
+      <c r="B37" s="31" t="s">
         <v>96</v>
       </c>
+      <c r="C37" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" s="32" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="38" ht="42.75">
-      <c r="A38" s="41"/>
-      <c r="B38" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="D38" s="31" t="s">
+      <c r="A38" s="42"/>
+      <c r="B38" s="31" t="s">
         <v>99</v>
       </c>
+      <c r="C38" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="39" ht="28.800000000000001" customHeight="1">
-      <c r="A39" s="41"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
+      <c r="A39" s="42"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
     </row>
     <row r="40" ht="28.800000000000001" customHeight="1">
-      <c r="A40" s="41"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
+      <c r="A40" s="42"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
     </row>
     <row r="41" ht="28.5" customHeight="1">
-      <c r="A41" s="41"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
+      <c r="A41" s="42"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
     </row>
     <row r="42" ht="28.5" customHeight="1">
-      <c r="A42" s="41"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
+      <c r="A42" s="42"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
     </row>
     <row r="43" ht="28.5" customHeight="1">
-      <c r="A43" s="41"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
+      <c r="A43" s="42"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
     </row>
     <row r="44" ht="28.5" customHeight="1">
-      <c r="A44" s="41"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
+      <c r="A44" s="42"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
     </row>
     <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" s="41"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
+      <c r="A45" s="42"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
     </row>
     <row r="46" ht="28.5" customHeight="1">
-      <c r="B46" s="25"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
     </row>
     <row r="47" ht="28.5" customHeight="1">
-      <c r="B47" s="25"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
     </row>
     <row r="48" ht="28.5" customHeight="1"/>
     <row r="49" ht="28.5" customHeight="1"/>
@@ -2135,13 +2148,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2168,86 +2181,86 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" t="s">
-        <v>105</v>
-      </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>105</v>
+        <v>112</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>105</v>
+        <v>115</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="42" t="s">
-        <v>115</v>
+      <c r="A6" s="43" t="s">
+        <v>117</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>105</v>
+        <v>118</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="42" t="s">
-        <v>118</v>
+      <c r="A7" s="43" t="s">
+        <v>120</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>105</v>
+        <v>121</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1"/>
@@ -3256,163 +3269,163 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="44" width="38.421875"/>
+    <col customWidth="1" min="2" max="2" style="45" width="38.421875"/>
     <col customWidth="1" min="3" max="3" width="55.421875"/>
     <col customWidth="1" min="4" max="4" width="75.8515625"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="44" customFormat="1" ht="42.75">
-      <c r="A2" s="45"/>
-      <c r="B2" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="D2" s="47" t="s">
+    <row r="2" s="45" customFormat="1" ht="42.75">
+      <c r="A2" s="46"/>
+      <c r="B2" s="47" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="3" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="46" t="s">
+      <c r="C2" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="D2" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="47"/>
-    </row>
-    <row r="4" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="45"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-    </row>
-    <row r="5" s="44" customFormat="1" ht="57">
-      <c r="A5" s="45"/>
-      <c r="B5" s="47" t="s">
+    </row>
+    <row r="3" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A3" s="46"/>
+      <c r="B3" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C3" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D3" s="48"/>
+    </row>
+    <row r="4" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A4" s="46"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+    </row>
+    <row r="5" s="45" customFormat="1" ht="57">
+      <c r="A5" s="46"/>
+      <c r="B5" s="48" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="6" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A6" s="45"/>
-      <c r="B6" s="46" t="s">
+      <c r="C5" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="D5" s="49" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="47" t="s">
+    </row>
+    <row r="6" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A6" s="46"/>
+      <c r="B6" s="47" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="7" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="45"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
+      <c r="C6" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A7" s="46"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="50"/>
+      <c r="B8" s="51"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
     <row r="9" ht="41.25" customHeight="1">
-      <c r="A9" s="51" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="52" t="s">
+      <c r="A9" s="52" t="s">
         <v>134</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="B9" s="31" t="s">
         <v>135</v>
       </c>
+      <c r="C9" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="31">
+      <c r="A10" s="54"/>
+      <c r="B10" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="32">
         <v>60000</v>
       </c>
-      <c r="D10" s="31" t="s">
-        <v>137</v>
+      <c r="D10" s="32" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="11" ht="36.75" customHeight="1">
-      <c r="A11" s="53"/>
-      <c r="B11" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" s="31">
+      <c r="A11" s="54"/>
+      <c r="B11" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="32">
         <v>3000</v>
       </c>
-      <c r="D11" s="31" t="s">
-        <v>139</v>
+      <c r="D11" s="32" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="D12" s="31" t="s">
+      <c r="A12" s="54"/>
+      <c r="B12" s="31" t="s">
         <v>142</v>
       </c>
+      <c r="C12" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="C13" s="54" t="s">
-        <v>144</v>
-      </c>
-      <c r="D13" s="31" t="s">
+      <c r="A13" s="54"/>
+      <c r="B13" s="31" t="s">
         <v>145</v>
       </c>
+      <c r="C13" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="14" ht="63.600000000000001" customHeight="1">
-      <c r="A14" s="53"/>
-      <c r="B14" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="D14" s="31" t="s">
+      <c r="A14" s="54"/>
+      <c r="B14" s="31" t="s">
         <v>148</v>
+      </c>
+      <c r="C14" s="55" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="50"/>
+      <c r="B15" s="51"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
     </row>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -482,7 +482,7 @@
     <t>mainPath</t>
   </si>
   <si>
-    <t xml:space="preserve">\\192.168.8.8\Razonet\18- OPERAÇÃO RAZONET\01- ROTINAS AUTOMATICAS\04- LANÇAMENTOS CONTÁBEIS\AUTOMACAO\LANÇAMENTOS DESPESAS</t>
+    <t xml:space="preserve">\\192.168.8.8\Razonet\18- OPERAÇÃO RAZONET\Robo de despesas</t>
   </si>
   <si>
     <t xml:space="preserve">Endereço onde serão alocados os arquivos de importação e relatórios de erros de importação do processo</t>
@@ -706,7 +706,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -748,16 +748,12 @@
     </xf>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="2" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
@@ -826,6 +822,9 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1503,7 +1502,7 @@
       <c r="C12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="15" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1529,23 +1528,23 @@
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="13"/>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="21" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="20" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" ht="34.799999999999997" customHeight="1">
       <c r="A16" s="13"/>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="20" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1556,13 +1555,13 @@
       <c r="D17" s="5"/>
     </row>
     <row r="18" ht="46.799999999999997" customHeight="1">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="21" t="s">
         <v>28</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="22" t="s">
         <v>30</v>
       </c>
       <c r="D18" s="14" t="s">
@@ -1570,21 +1569,21 @@
       </c>
     </row>
     <row r="19" ht="46.799999999999997" customHeight="1">
-      <c r="A19" s="23"/>
+      <c r="A19" s="21"/>
       <c r="B19" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="23" t="s">
         <v>33</v>
       </c>
       <c r="D19" s="14"/>
     </row>
     <row r="20" ht="43.200000000000003" customHeight="1">
-      <c r="A20" s="23"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="23" t="s">
         <v>35</v>
       </c>
       <c r="D20" s="14"/>
@@ -1643,20 +1642,20 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8.00390625"/>
-    <col customWidth="1" min="2" max="2" style="26" width="52.140625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="27" width="63.11328125"/>
-    <col customWidth="1" min="4" max="4" style="27" width="84.140625"/>
+    <col customWidth="1" min="2" max="2" style="24" width="52.140625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="25" width="63.11328125"/>
+    <col customWidth="1" min="4" max="4" style="25" width="84.140625"/>
     <col customWidth="1" min="5" max="27" width="8.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="27" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2"/>
@@ -1684,79 +1683,79 @@
       <c r="AA1" s="2"/>
     </row>
     <row r="2" ht="28.5">
-      <c r="A2" s="30"/>
-      <c r="B2" s="31" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="32">
+      <c r="C2" s="30">
         <v>1</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="30" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" ht="28.5">
-      <c r="A3" s="30"/>
-      <c r="B3" s="31" t="s">
+      <c r="A3" s="28"/>
+      <c r="B3" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="30">
         <v>3</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="30" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31" t="s">
+      <c r="A4" s="28"/>
+      <c r="B4" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="30" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" ht="28.5">
-      <c r="A5" s="30"/>
-      <c r="B5" s="31" t="s">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="30">
         <v>2</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="30" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" ht="28.5">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31" t="s">
+      <c r="A6" s="28"/>
+      <c r="B6" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="30">
         <v>2</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="30" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" s="33" customFormat="1" ht="17.399999999999999" customHeight="1">
+    <row r="7" s="31" customFormat="1" ht="17.399999999999999" customHeight="1">
       <c r="A7" s="5"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
     </row>
     <row r="8" ht="39.75" customHeight="1">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="35">
         <v>30000</v>
       </c>
       <c r="D8" s="15" t="s">
@@ -1764,11 +1763,11 @@
       </c>
     </row>
     <row r="9" ht="39.75" customHeight="1">
-      <c r="A9" s="38"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="35">
         <v>20000</v>
       </c>
       <c r="D9" s="15" t="s">
@@ -1776,11 +1775,11 @@
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="38"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="35">
         <v>0</v>
       </c>
       <c r="D10" s="15" t="s">
@@ -1788,11 +1787,11 @@
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="38"/>
+      <c r="A11" s="36"/>
       <c r="B11" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="35">
         <v>0</v>
       </c>
       <c r="D11" s="15" t="s">
@@ -1801,309 +1800,309 @@
     </row>
     <row r="12" ht="17.399999999999999" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
     </row>
     <row r="13" ht="22.800000000000001" customHeight="1">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="30" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="14" ht="28.199999999999999" customHeight="1">
-      <c r="A14" s="39"/>
-      <c r="B14" s="31" t="s">
+      <c r="A14" s="37"/>
+      <c r="B14" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="32"/>
+      <c r="D14" s="30"/>
     </row>
     <row r="15" ht="28.199999999999999" customHeight="1">
-      <c r="A15" s="39"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="39"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="39"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
     </row>
     <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="39"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
     </row>
     <row r="19" ht="17.399999999999999" customHeight="1">
-      <c r="A19" s="40"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="30" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="41"/>
-      <c r="B21" s="31" t="s">
+      <c r="A21" s="39"/>
+      <c r="B21" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="30" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="22" ht="33.75" customHeight="1">
-      <c r="A22" s="41"/>
-      <c r="B22" s="32" t="s">
+      <c r="A22" s="39"/>
+      <c r="B22" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="32"/>
+      <c r="D22" s="30"/>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="41"/>
-      <c r="B23" s="31" t="s">
+      <c r="A23" s="39"/>
+      <c r="B23" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="32"/>
+      <c r="D23" s="30"/>
     </row>
     <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="41"/>
-      <c r="B24" s="31" t="s">
+      <c r="A24" s="39"/>
+      <c r="B24" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="32"/>
+      <c r="D24" s="30"/>
     </row>
     <row r="25" ht="27" customHeight="1">
-      <c r="A25" s="41"/>
-      <c r="B25" s="31" t="s">
+      <c r="A25" s="39"/>
+      <c r="B25" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="32"/>
+      <c r="D25" s="30"/>
     </row>
     <row r="26" ht="27" customHeight="1">
-      <c r="A26" s="41"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
+      <c r="A26" s="39"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
     </row>
     <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="41"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
+      <c r="A27" s="39"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
     </row>
     <row r="28" ht="27" customHeight="1">
-      <c r="A28" s="41"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
+      <c r="A28" s="39"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
     </row>
     <row r="29" ht="17.399999999999999" customHeight="1">
       <c r="A29" s="5"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
     </row>
     <row r="30" ht="27.75" customHeight="1">
-      <c r="A30" s="42" t="s">
+      <c r="A30" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="30" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="31" ht="27.75" customHeight="1">
-      <c r="A31" s="42"/>
-      <c r="B31" s="31" t="s">
+      <c r="A31" s="40"/>
+      <c r="B31" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="30" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="32" ht="28.5">
-      <c r="A32" s="42"/>
-      <c r="B32" s="31" t="s">
+      <c r="A32" s="40"/>
+      <c r="B32" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D32" s="32"/>
+      <c r="D32" s="30"/>
     </row>
     <row r="33" ht="28.5">
-      <c r="A33" s="42"/>
-      <c r="B33" s="31" t="s">
+      <c r="A33" s="40"/>
+      <c r="B33" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="32" t="s">
+      <c r="C33" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="D33" s="32"/>
+      <c r="D33" s="30"/>
     </row>
     <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="42"/>
-      <c r="B34" s="31" t="s">
+      <c r="A34" s="40"/>
+      <c r="B34" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="30" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="35" ht="31.199999999999999" customHeight="1">
-      <c r="A35" s="42"/>
-      <c r="B35" s="31" t="s">
+      <c r="A35" s="40"/>
+      <c r="B35" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="32" t="s">
+      <c r="C35" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="32"/>
+      <c r="D35" s="30"/>
     </row>
     <row r="36" ht="28.800000000000001" customHeight="1">
-      <c r="A36" s="42"/>
-      <c r="B36" s="31" t="s">
+      <c r="A36" s="40"/>
+      <c r="B36" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="30" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="37" ht="29.399999999999999" customHeight="1">
-      <c r="A37" s="42"/>
-      <c r="B37" s="31" t="s">
+      <c r="A37" s="40"/>
+      <c r="B37" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="32" t="s">
+      <c r="C37" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="30" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="38" ht="42.75">
-      <c r="A38" s="42"/>
-      <c r="B38" s="31" t="s">
+      <c r="A38" s="40"/>
+      <c r="B38" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="C38" s="32" t="s">
+      <c r="C38" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="30" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="39" ht="28.800000000000001" customHeight="1">
-      <c r="A39" s="42"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
+      <c r="A39" s="40"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
     </row>
     <row r="40" ht="28.800000000000001" customHeight="1">
-      <c r="A40" s="42"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
+      <c r="A40" s="40"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
     </row>
     <row r="41" ht="28.5" customHeight="1">
-      <c r="A41" s="42"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
+      <c r="A41" s="40"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
     </row>
     <row r="42" ht="28.5" customHeight="1">
-      <c r="A42" s="42"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
+      <c r="A42" s="40"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
     </row>
     <row r="43" ht="28.5" customHeight="1">
-      <c r="A43" s="42"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
+      <c r="A43" s="40"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
     </row>
     <row r="44" ht="28.5" customHeight="1">
-      <c r="A44" s="42"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
+      <c r="A44" s="40"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
     </row>
     <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" s="42"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="32"/>
+      <c r="A45" s="40"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
     </row>
     <row r="46" ht="28.5" customHeight="1">
-      <c r="B46" s="26"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
     </row>
     <row r="47" ht="28.5" customHeight="1">
-      <c r="B47" s="26"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
     </row>
     <row r="48" ht="28.5" customHeight="1"/>
     <row r="49" ht="28.5" customHeight="1"/>
@@ -2197,7 +2196,7 @@
       <c r="A3" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="41" t="s">
         <v>110</v>
       </c>
       <c r="C3" t="s">
@@ -2214,7 +2213,7 @@
       <c r="B4" t="s">
         <v>112</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="42" t="s">
         <v>107</v>
       </c>
       <c r="D4" t="s">
@@ -2228,7 +2227,7 @@
       <c r="B5" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="42" t="s">
         <v>107</v>
       </c>
       <c r="D5" t="s">
@@ -2236,13 +2235,13 @@
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="41" t="s">
         <v>117</v>
       </c>
       <c r="B6" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="42" t="s">
         <v>107</v>
       </c>
       <c r="D6" t="s">
@@ -2250,13 +2249,13 @@
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="41" t="s">
         <v>120</v>
       </c>
       <c r="B7" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="42" t="s">
         <v>107</v>
       </c>
       <c r="D7" t="s">
@@ -3269,163 +3268,163 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="45" width="38.421875"/>
+    <col customWidth="1" min="2" max="2" style="43" width="38.421875"/>
     <col customWidth="1" min="3" max="3" width="55.421875"/>
     <col customWidth="1" min="4" max="4" width="75.8515625"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="27" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="45" customFormat="1" ht="42.75">
-      <c r="A2" s="46"/>
-      <c r="B2" s="47" t="s">
+    <row r="2" s="43" customFormat="1" ht="42.75">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="47" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="47" t="s">
+    <row r="3" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A3" s="44"/>
+      <c r="B3" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="47" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="48"/>
-    </row>
-    <row r="4" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-    </row>
-    <row r="5" s="45" customFormat="1" ht="57">
-      <c r="A5" s="46"/>
-      <c r="B5" s="48" t="s">
+      <c r="D3" s="47"/>
+    </row>
+    <row r="4" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A4" s="44"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+    </row>
+    <row r="5" s="43" customFormat="1" ht="57">
+      <c r="A5" s="44"/>
+      <c r="B5" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="48" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="6" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A6" s="46"/>
-      <c r="B6" s="47" t="s">
+    <row r="6" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A6" s="44"/>
+      <c r="B6" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="49" t="s">
         <v>132</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="47" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="7" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="46"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
+    <row r="7" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A7" s="44"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="51"/>
+      <c r="B8" s="50"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
     <row r="9" ht="41.25" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="30" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="54"/>
-      <c r="B10" s="31" t="s">
+      <c r="A10" s="53"/>
+      <c r="B10" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="30">
         <v>60000</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="30" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="11" ht="36.75" customHeight="1">
-      <c r="A11" s="54"/>
-      <c r="B11" s="31" t="s">
+      <c r="A11" s="53"/>
+      <c r="B11" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="30">
         <v>3000</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="30" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="54"/>
-      <c r="B12" s="31" t="s">
+      <c r="A12" s="53"/>
+      <c r="B12" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="30" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="54"/>
-      <c r="B13" s="31" t="s">
+      <c r="A13" s="53"/>
+      <c r="B13" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="30" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="14" ht="63.600000000000001" customHeight="1">
-      <c r="A14" s="54"/>
-      <c r="B14" s="31" t="s">
+      <c r="A14" s="53"/>
+      <c r="B14" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="30" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="51"/>
+      <c r="B15" s="50"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
     </row>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
   <si>
     <t>Name</t>
   </si>
@@ -414,6 +414,12 @@
   </si>
   <si>
     <t xml:space="preserve">Caso haja um erro durante o processo de definição de datas do request das despesas. </t>
+  </si>
+  <si>
+    <t>ExceptionMessage_CriticasDeEstruturasAosTxtsDeImportacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foram exibidas criticas de estruturas aos txts de importação no processo de importação. Favor verificar</t>
   </si>
   <si>
     <t>Asset</t>
@@ -706,7 +712,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -810,6 +816,12 @@
     <xf fontId="5" fillId="11" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
@@ -822,9 +834,6 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2042,7 +2051,7 @@
     </row>
     <row r="38" ht="42.75">
       <c r="A38" s="40"/>
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="41" t="s">
         <v>99</v>
       </c>
       <c r="C38" s="30" t="s">
@@ -2054,8 +2063,12 @@
     </row>
     <row r="39" ht="28.800000000000001" customHeight="1">
       <c r="A39" s="40"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
+      <c r="B39" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C39" s="42" t="s">
+        <v>103</v>
+      </c>
       <c r="D39" s="30"/>
     </row>
     <row r="40" ht="28.800000000000001" customHeight="1">
@@ -2147,13 +2160,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2180,86 +2193,86 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="C3" t="s">
-        <v>107</v>
-      </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>107</v>
+        <v>114</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>107</v>
+        <v>117</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="41" t="s">
-        <v>117</v>
+      <c r="A6" s="43" t="s">
+        <v>119</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>107</v>
+        <v>120</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="41" t="s">
-        <v>120</v>
+      <c r="A7" s="43" t="s">
+        <v>122</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>107</v>
+        <v>123</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1"/>
@@ -3268,7 +3281,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="43" width="38.421875"/>
+    <col customWidth="1" min="2" max="2" style="45" width="38.421875"/>
     <col customWidth="1" min="3" max="3" width="55.421875"/>
     <col customWidth="1" min="4" max="4" width="75.8515625"/>
   </cols>
@@ -3284,147 +3297,147 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="43" customFormat="1" ht="42.75">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="C2" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="D2" s="47" t="s">
+    <row r="2" s="45" customFormat="1" ht="28.5">
+      <c r="A2" s="46"/>
+      <c r="B2" s="47" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="3" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="44"/>
-      <c r="B3" s="45" t="s">
+      <c r="C2" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="D2" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="47"/>
-    </row>
-    <row r="4" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-    </row>
-    <row r="5" s="43" customFormat="1" ht="57">
-      <c r="A5" s="44"/>
-      <c r="B5" s="47" t="s">
+    </row>
+    <row r="3" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A3" s="46"/>
+      <c r="B3" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C3" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D3" s="48"/>
+    </row>
+    <row r="4" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A4" s="46"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+    </row>
+    <row r="5" s="45" customFormat="1" ht="57">
+      <c r="A5" s="46"/>
+      <c r="B5" s="48" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="6" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A6" s="44"/>
-      <c r="B6" s="45" t="s">
+      <c r="C5" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="D5" s="49" t="s">
         <v>132</v>
       </c>
-      <c r="D6" s="47" t="s">
+    </row>
+    <row r="6" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A6" s="46"/>
+      <c r="B6" s="47" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="7" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="44"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
+      <c r="C6" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A7" s="46"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="50"/>
+      <c r="B8" s="51"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
     <row r="9" ht="41.25" customHeight="1">
-      <c r="A9" s="51" t="s">
-        <v>134</v>
+      <c r="A9" s="52" t="s">
+        <v>136</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="52" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>138</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="53"/>
+      <c r="A10" s="54"/>
       <c r="B10" s="29" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C10" s="30">
         <v>60000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" ht="36.75" customHeight="1">
-      <c r="A11" s="53"/>
+      <c r="A11" s="54"/>
       <c r="B11" s="29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C11" s="30">
         <v>3000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="53"/>
+      <c r="A12" s="54"/>
       <c r="B12" s="29" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="53"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="C13" s="54" t="s">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="C13" s="55" t="s">
+        <v>148</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" ht="63.600000000000001" customHeight="1">
-      <c r="A14" s="53"/>
+      <c r="A14" s="54"/>
       <c r="B14" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="C14" s="54" t="s">
-        <v>149</v>
+        <v>150</v>
+      </c>
+      <c r="C14" s="55" t="s">
+        <v>151</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="50"/>
+      <c r="B15" s="51"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
     </row>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
   <si>
     <t>Name</t>
   </si>
@@ -110,7 +110,7 @@
     <t>obligationDateStart</t>
   </si>
   <si>
-    <t>01/03/2026</t>
+    <t>20/01/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Data inicial do range de datas que deve abranger a data de vencimento da obrigação em questão, se não estiver definida nenhuma data nessa variável, o processo define o primeiro e o ultimo dia do mês como as datas de inicio e fim do range.</t>
@@ -119,7 +119,7 @@
     <t>obligationDateEnd</t>
   </si>
   <si>
-    <t>05/03/2026</t>
+    <t>05/02/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Data final do range de datas que deve abranger a data de vencimento da obrigação em questão, se não estiver definida nenhuma data nessa variável, o processo define o primeiro e o ultimo dia do mês como as datas de inicio e fim do range.</t>
@@ -485,6 +485,9 @@
     <t xml:space="preserve">Provider name para conexão no banco de dados do Domínio</t>
   </si>
   <si>
+    <t>s</t>
+  </si>
+  <si>
     <t>mainPath</t>
   </si>
   <si>
@@ -554,7 +557,7 @@
     <t>getExpenses_dateStart</t>
   </si>
   <si>
-    <t>01/05/2025</t>
+    <t>01/01/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Inicio do range de datas que abrange a data de vencimento das despesas que irão ser importadas. Deve estar no formato "dd/MM/yyyy" e só deve existir caso o getExpenses_dateEnd existir também.</t>
@@ -563,7 +566,7 @@
     <t>getExpenses_dateEnd</t>
   </si>
   <si>
-    <t>31/12/2025</t>
+    <t>01/02/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Fim do range de datas que abrange a data de vencimento das despesas que irão ser importadas. Deve estar no formato "dd/MM/yyyy" e só deve existir caso o getExpenses_dateStart existir também. Deve ser posterior ao getExpenses_dateStart</t>
@@ -712,7 +715,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -815,12 +818,6 @@
     </xf>
     <xf fontId="5" fillId="11" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
@@ -2051,7 +2048,7 @@
     </row>
     <row r="38" ht="42.75">
       <c r="A38" s="40"/>
-      <c r="B38" s="41" t="s">
+      <c r="B38" s="29" t="s">
         <v>99</v>
       </c>
       <c r="C38" s="30" t="s">
@@ -2063,10 +2060,10 @@
     </row>
     <row r="39" ht="28.800000000000001" customHeight="1">
       <c r="A39" s="40"/>
-      <c r="B39" s="42" t="s">
+      <c r="B39" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="C39" s="42" t="s">
+      <c r="C39" s="30" t="s">
         <v>103</v>
       </c>
       <c r="D39" s="30"/>
@@ -2209,7 +2206,7 @@
       <c r="A3" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="41" t="s">
         <v>112</v>
       </c>
       <c r="C3" t="s">
@@ -2226,7 +2223,7 @@
       <c r="B4" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="42" t="s">
         <v>109</v>
       </c>
       <c r="D4" t="s">
@@ -2240,7 +2237,7 @@
       <c r="B5" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="42" t="s">
         <v>109</v>
       </c>
       <c r="D5" t="s">
@@ -2248,13 +2245,13 @@
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="41" t="s">
         <v>119</v>
       </c>
       <c r="B6" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="42" t="s">
         <v>109</v>
       </c>
       <c r="D6" t="s">
@@ -2262,13 +2259,13 @@
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="41" t="s">
         <v>122</v>
       </c>
       <c r="B7" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="42" t="s">
         <v>109</v>
       </c>
       <c r="D7" t="s">
@@ -3281,12 +3278,15 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="45" width="38.421875"/>
+    <col customWidth="1" min="2" max="2" style="43" width="38.421875"/>
     <col customWidth="1" min="3" max="3" width="55.421875"/>
     <col customWidth="1" min="4" max="4" width="75.8515625"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
+      <c r="A1" t="s">
+        <v>125</v>
+      </c>
       <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
@@ -3297,147 +3297,147 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="45" customFormat="1" ht="28.5">
-      <c r="A2" s="46"/>
-      <c r="B2" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="C2" s="48" t="s">
+    <row r="2" s="43" customFormat="1" ht="28.5">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="46" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="3" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="47" t="s">
+      <c r="D2" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="48" t="s">
+    </row>
+    <row r="3" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A3" s="44"/>
+      <c r="B3" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="48"/>
-    </row>
-    <row r="4" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-    </row>
-    <row r="5" s="45" customFormat="1" ht="57">
-      <c r="A5" s="46"/>
-      <c r="B5" s="48" t="s">
+      <c r="C3" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="D3" s="46"/>
+    </row>
+    <row r="4" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A4" s="44"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+    </row>
+    <row r="5" s="43" customFormat="1" ht="57">
+      <c r="A5" s="44"/>
+      <c r="B5" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="C5" s="46" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="6" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A6" s="46"/>
-      <c r="B6" s="47" t="s">
+      <c r="D5" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="50" t="s">
+    </row>
+    <row r="6" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A6" s="44"/>
+      <c r="B6" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="C6" s="48" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="7" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="46"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
+      <c r="D6" s="46" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A7" s="44"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="51"/>
+      <c r="B8" s="49"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
     <row r="9" ht="41.25" customHeight="1">
-      <c r="A9" s="52" t="s">
-        <v>136</v>
+      <c r="A9" s="50" t="s">
+        <v>137</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="53" t="s">
         <v>138</v>
       </c>
+      <c r="C9" s="51" t="s">
+        <v>139</v>
+      </c>
       <c r="D9" s="30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="54"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C10" s="30">
         <v>60000</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" ht="36.75" customHeight="1">
-      <c r="A11" s="54"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C11" s="30">
         <v>3000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="54"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="54"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="C13" s="55" t="s">
         <v>148</v>
       </c>
+      <c r="C13" s="53" t="s">
+        <v>149</v>
+      </c>
       <c r="D13" s="30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" ht="63.600000000000001" customHeight="1">
-      <c r="A14" s="54"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="C14" s="55" t="s">
         <v>151</v>
       </c>
+      <c r="C14" s="53" t="s">
+        <v>152</v>
+      </c>
       <c r="D14" s="30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="51"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
     </row>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -715,7 +715,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -846,6 +846,9 @@
     </xf>
     <xf fontId="2" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="4" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3365,10 +3368,10 @@
       <c r="A9" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="51" t="s">
         <v>138</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="52" t="s">
         <v>139</v>
       </c>
       <c r="D9" s="30" t="s">
@@ -3376,7 +3379,7 @@
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="52"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="29" t="s">
         <v>141</v>
       </c>
@@ -3388,7 +3391,7 @@
       </c>
     </row>
     <row r="11" ht="36.75" customHeight="1">
-      <c r="A11" s="52"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="29" t="s">
         <v>143</v>
       </c>
@@ -3400,7 +3403,7 @@
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="52"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="29" t="s">
         <v>145</v>
       </c>
@@ -3412,11 +3415,11 @@
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="52"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="54" t="s">
         <v>149</v>
       </c>
       <c r="D13" s="30" t="s">
@@ -3424,11 +3427,11 @@
       </c>
     </row>
     <row r="14" ht="63.600000000000001" customHeight="1">
-      <c r="A14" s="52"/>
+      <c r="A14" s="53"/>
       <c r="B14" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="54" t="s">
         <v>152</v>
       </c>
       <c r="D14" s="30" t="s">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <si>
     <t>Name</t>
   </si>
@@ -566,10 +566,34 @@
     <t>getExpenses_dateEnd</t>
   </si>
   <si>
-    <t>01/02/2026</t>
+    <t>01/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Fim do range de datas que abrange a data de vencimento das despesas que irão ser importadas. Deve estar no formato "dd/MM/yyyy" e só deve existir caso o getExpenses_dateStart existir também. Deve ser posterior ao getExpenses_dateStart</t>
+  </si>
+  <si>
+    <t>PostExpensesSettings</t>
+  </si>
+  <si>
+    <t>postExpenses_endPoint</t>
+  </si>
+  <si>
+    <t>set_as_integrated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endpoint para request post para integrar as obrigações, o formato final do endpoint fica "expensesUrl + /:id/set_as_integrated</t>
+  </si>
+  <si>
+    <t>postExpenses_timeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timeout do request</t>
+  </si>
+  <si>
+    <t>postExpenses_contentType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content-type do post expenses</t>
   </si>
 </sst>
 </file>
@@ -611,7 +635,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -678,6 +702,12 @@
         <bgColor indexed="2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -715,7 +745,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -847,9 +877,6 @@
     <xf fontId="2" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf fontId="4" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -858,6 +885,18 @@
     </xf>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="12" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="12" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="12" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3368,10 +3407,10 @@
       <c r="A9" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="51" t="s">
         <v>139</v>
       </c>
       <c r="D9" s="30" t="s">
@@ -3379,7 +3418,7 @@
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="53"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="29" t="s">
         <v>141</v>
       </c>
@@ -3391,7 +3430,7 @@
       </c>
     </row>
     <row r="11" ht="36.75" customHeight="1">
-      <c r="A11" s="53"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="29" t="s">
         <v>143</v>
       </c>
@@ -3403,7 +3442,7 @@
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="53"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="29" t="s">
         <v>145</v>
       </c>
@@ -3415,11 +3454,11 @@
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="53"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C13" s="54" t="s">
+      <c r="C13" s="53" t="s">
         <v>149</v>
       </c>
       <c r="D13" s="30" t="s">
@@ -3427,11 +3466,11 @@
       </c>
     </row>
     <row r="14" ht="63.600000000000001" customHeight="1">
-      <c r="A14" s="53"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="C14" s="54" t="s">
+      <c r="C14" s="53" t="s">
         <v>152</v>
       </c>
       <c r="D14" s="30" t="s">
@@ -3444,9 +3483,44 @@
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
     </row>
-    <row r="16" ht="30.600000000000001" customHeight="1"/>
-    <row r="17" ht="28.199999999999999" customHeight="1"/>
-    <row r="18" ht="28.199999999999999" customHeight="1"/>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="D16" s="57" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="54"/>
+      <c r="B17" s="55" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="56">
+        <v>5000</v>
+      </c>
+      <c r="D17" s="56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="54"/>
+      <c r="B18" s="55" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="56" t="s">
+        <v>161</v>
+      </c>
+    </row>
     <row r="19" ht="28.199999999999999" customHeight="1"/>
     <row r="20" ht="28.199999999999999" customHeight="1"/>
     <row r="21" ht="28.199999999999999" customHeight="1"/>
@@ -3536,9 +3610,10 @@
     <row r="105" ht="28.199999999999999" customHeight="1"/>
     <row r="106" ht="28.199999999999999" customHeight="1"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="A9:A14"/>
+    <mergeCell ref="A16:A18"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="C9"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
   <si>
     <t>Name</t>
   </si>
@@ -512,6 +512,15 @@
     <t xml:space="preserve">O Domínio pode apresentar erro de acordo com a quantidade de despesas inseridas em um determinado arquivo de importação. Por isso, existem as contas de débito específicas que devem estar separadas por arquivo de importação.Deve estar no fomraco "contaDeDebito,contaDeDebito,contaDeDebito"</t>
   </si>
   <si>
+    <t>especificExceptDebitAccounts</t>
+  </si>
+  <si>
+    <t>2110,2074,1204,2103,2112,2055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contas de débito que não devem ser importadas para o Domínio.</t>
+  </si>
+  <si>
     <t>dateEndWorkPeriod</t>
   </si>
   <si>
@@ -557,7 +566,7 @@
     <t>getExpenses_dateStart</t>
   </si>
   <si>
-    <t>01/01/2026</t>
+    <t>01/01/2025</t>
   </si>
   <si>
     <t xml:space="preserve">Inicio do range de datas que abrange a data de vencimento das despesas que irão ser importadas. Deve estar no formato "dd/MM/yyyy" e só deve existir caso o getExpenses_dateEnd existir também.</t>
@@ -865,7 +874,7 @@
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3375,16 +3384,16 @@
       <c r="C5" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="46" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="6" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
+    <row r="6" s="43" customFormat="1" ht="36" customHeight="1">
       <c r="A6" s="44"/>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="46" t="s">
         <v>135</v>
       </c>
       <c r="D6" s="46" t="s">
@@ -3393,79 +3402,79 @@
     </row>
     <row r="7" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
       <c r="A7" s="44"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-    </row>
-    <row r="8" ht="14.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9" ht="41.25" customHeight="1">
-      <c r="A9" s="50" t="s">
+      <c r="B7" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="C7" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="D7" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="30" t="s">
+    </row>
+    <row r="8" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A8" s="44"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10" ht="41.25" customHeight="1">
+      <c r="A10" s="50" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="52"/>
       <c r="B10" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="C10" s="30">
-        <v>60000</v>
+      <c r="C10" s="51" t="s">
+        <v>142</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="11" ht="36.75" customHeight="1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" ht="39.75" customHeight="1">
       <c r="A11" s="52"/>
       <c r="B11" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="30">
-        <v>3000</v>
+        <v>60000</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
       <c r="A12" s="52"/>
       <c r="B12" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="C12" s="30" t="s">
         <v>146</v>
+      </c>
+      <c r="C12" s="30">
+        <v>3000</v>
       </c>
       <c r="D12" s="30" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1">
+    <row r="13" ht="36.75" customHeight="1">
       <c r="A13" s="52"/>
       <c r="B13" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="30" t="s">
         <v>149</v>
       </c>
       <c r="D13" s="30" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="14" ht="63.600000000000001" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="52"/>
       <c r="B14" s="29" t="s">
         <v>151</v>
@@ -3477,51 +3486,62 @@
         <v>153</v>
       </c>
     </row>
-    <row r="15" ht="14.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="54" t="s">
+    <row r="15" ht="63.600000000000001" customHeight="1">
+      <c r="A15" s="52"/>
+      <c r="B15" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="B16" s="55" t="s">
+      <c r="C15" s="53" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="D15" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="D16" s="57" t="s">
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="54" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="54"/>
       <c r="B17" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="C17" s="56">
-        <v>5000</v>
-      </c>
-      <c r="D17" s="56" t="s">
+      <c r="C17" s="56" t="s">
         <v>159</v>
+      </c>
+      <c r="D17" s="57" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="54"/>
       <c r="B18" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="C18" s="56" t="s">
-        <v>146</v>
+        <v>161</v>
+      </c>
+      <c r="C18" s="56">
+        <v>5000</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="19" ht="28.199999999999999" customHeight="1"/>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="54"/>
+      <c r="B19" s="55" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="56" t="s">
+        <v>164</v>
+      </c>
+    </row>
     <row r="20" ht="28.199999999999999" customHeight="1"/>
     <row r="21" ht="28.199999999999999" customHeight="1"/>
     <row r="22" ht="28.199999999999999" customHeight="1"/>
@@ -3609,14 +3629,15 @@
     <row r="104" ht="28.199999999999999" customHeight="1"/>
     <row r="105" ht="28.199999999999999" customHeight="1"/>
     <row r="106" ht="28.199999999999999" customHeight="1"/>
+    <row r="107" ht="28.199999999999999" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="A17:A19"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="C9"/>
+    <hyperlink r:id="rId1" ref="C10"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -89,6 +89,9 @@
     </r>
   </si>
   <si>
+    <t>enableExpensesIntegration</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBLIGATION SETTINGS</t>
   </si>
   <si>
@@ -110,7 +113,7 @@
     <t>obligationDateStart</t>
   </si>
   <si>
-    <t>20/01/2026</t>
+    <t>20/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Data inicial do range de datas que deve abranger a data de vencimento da obrigação em questão, se não estiver definida nenhuma data nessa variável, o processo define o primeiro e o ultimo dia do mês como as datas de inicio e fim do range.</t>
@@ -119,7 +122,7 @@
     <t>obligationDateEnd</t>
   </si>
   <si>
-    <t>05/02/2026</t>
+    <t>05/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Data final do range de datas que deve abranger a data de vencimento da obrigação em questão, se não estiver definida nenhuma data nessa variável, o processo define o primeiro e o ultimo dia do mês como as datas de inicio e fim do range.</t>
@@ -164,9 +167,6 @@
     <t>obligationDebugCompanyId</t>
   </si>
   <si>
-    <t>7a8d0889-71e5-4dab-9ec2-734bf7c46734</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -566,7 +566,7 @@
     <t>getExpenses_dateStart</t>
   </si>
   <si>
-    <t>01/01/2025</t>
+    <t>01/01/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Inicio do range de datas que abrange a data de vencimento das despesas que irão ser importadas. Deve estar no formato "dd/MM/yyyy" e só deve existir caso o getExpenses_dateEnd existir também.</t>
@@ -575,7 +575,7 @@
     <t>getExpenses_dateEnd</t>
   </si>
   <si>
-    <t>01/03/2026</t>
+    <t>01/02/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Fim do range de datas que abrange a data de vencimento das despesas que irão ser importadas. Deve estar no formato "dd/MM/yyyy" e só deve existir caso o getExpenses_dateStart existir também. Deve ser posterior ao getExpenses_dateStart</t>
@@ -632,15 +632,15 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <sz val="14.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <u/>
       <sz val="11.000000"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14.000000"/>
-      <color theme="1"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -754,7 +754,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="56">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -776,14 +776,17 @@
     <xf fontId="2" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
+    <xf fontId="3" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="3" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="2" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
@@ -805,12 +808,6 @@
     <xf fontId="2" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -839,7 +836,7 @@
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -848,14 +845,14 @@
     <xf fontId="2" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
-    <xf fontId="5" fillId="9" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="9" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
     <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="5" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="11" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="11" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
@@ -874,9 +871,6 @@
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -886,7 +880,7 @@
     <xf fontId="2" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="5" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1481,33 +1475,37 @@
       <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
+      <c r="B4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5" ht="27" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10"/>
+      <c r="B5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="13" t="b">
+        <v>0</v>
+      </c>
       <c r="D5" s="11"/>
     </row>
     <row r="6" ht="27" customHeight="1">
       <c r="A6" s="8"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="13"/>
       <c r="D6" s="11"/>
     </row>
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="8"/>
-      <c r="B7" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>8</v>
-      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="11"/>
     </row>
     <row r="8" ht="17.399999999999999" customHeight="1">
       <c r="A8" s="5"/>
@@ -1516,92 +1514,90 @@
       <c r="D8" s="7"/>
     </row>
     <row r="9" ht="31.199999999999999" customHeight="1">
-      <c r="A9" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="14" t="s">
+      <c r="A9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="15" t="s">
+      <c r="B9" s="12" t="s">
         <v>11</v>
       </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" ht="33.600000000000001" customHeight="1">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="14"/>
+      <c r="B10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="C10" s="15" t="s">
         <v>14</v>
       </c>
+      <c r="D10" s="15" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" ht="43.200000000000003" customHeight="1">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="16" t="s">
+      <c r="A11" s="14"/>
+      <c r="B11" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="C11" s="17" t="s">
         <v>17</v>
       </c>
+      <c r="D11" s="16" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="12" ht="61.200000000000003" customHeight="1">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="17" t="s">
+      <c r="A12" s="14"/>
+      <c r="B12" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="C12" s="18" t="s">
         <v>20</v>
       </c>
+      <c r="D12" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="13" ht="28.800000000000001" customHeight="1">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="14" t="b">
+      <c r="A13" s="14"/>
+      <c r="B13" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="D13" s="14"/>
+      <c r="D13" s="15"/>
     </row>
     <row r="14" ht="28.800000000000001" customHeight="1">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="14" t="b">
+      <c r="A14" s="14"/>
+      <c r="B14" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="D14" s="14"/>
+      <c r="D14" s="15"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="13"/>
-      <c r="B15" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="20" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="19" t="s">
         <v>24</v>
       </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="16" ht="34.799999999999997" customHeight="1">
-      <c r="A16" s="13"/>
-      <c r="B16" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="14" t="s">
+      <c r="A16" s="14"/>
+      <c r="B16" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="C16" s="15"/>
+      <c r="D16" s="21" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1612,38 +1608,38 @@
       <c r="D17" s="5"/>
     </row>
     <row r="18" ht="46.799999999999997" customHeight="1">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="16" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" ht="46.799999999999997" customHeight="1">
-      <c r="A19" s="21"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="14"/>
+      <c r="D19" s="15"/>
     </row>
     <row r="20" ht="43.200000000000003" customHeight="1">
-      <c r="A20" s="21"/>
+      <c r="A20" s="22"/>
       <c r="B20" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="14"/>
+      <c r="D20" s="16"/>
     </row>
     <row r="21" ht="14.25">
       <c r="C21" s="1"/>
@@ -1699,20 +1695,20 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8.00390625"/>
-    <col customWidth="1" min="2" max="2" style="24" width="52.140625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="25" width="63.11328125"/>
-    <col customWidth="1" min="4" max="4" style="25" width="84.140625"/>
+    <col customWidth="1" min="2" max="2" style="23" width="52.140625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="24" width="63.11328125"/>
+    <col customWidth="1" min="4" max="4" style="24" width="84.140625"/>
     <col customWidth="1" min="5" max="27" width="8.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2"/>
@@ -1740,430 +1736,430 @@
       <c r="AA1" s="2"/>
     </row>
     <row r="2" ht="28.5">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="30">
+      <c r="C2" s="29">
         <v>1</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="29" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" ht="28.5">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29" t="s">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3" s="29">
         <v>3</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="29" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29" t="s">
+      <c r="A4" s="27"/>
+      <c r="B4" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="29" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" ht="28.5">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29" t="s">
+      <c r="A5" s="27"/>
+      <c r="B5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
+        <v>15</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5">
+      <c r="A6" s="27"/>
+      <c r="B6" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="29">
         <v>2</v>
       </c>
-      <c r="D5" s="30" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" ht="28.5">
-      <c r="A6" s="28"/>
-      <c r="B6" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="30">
-        <v>2</v>
-      </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="29" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" s="31" customFormat="1" ht="17.399999999999999" customHeight="1">
+    <row r="7" s="30" customFormat="1" ht="17.399999999999999" customHeight="1">
       <c r="A7" s="5"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
     </row>
     <row r="8" ht="39.75" customHeight="1">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="34">
         <v>30000</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="16" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="9" ht="39.75" customHeight="1">
-      <c r="A9" s="36"/>
-      <c r="B9" s="14" t="s">
+      <c r="A9" s="35"/>
+      <c r="B9" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="34">
         <v>20000</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="36"/>
-      <c r="B10" s="14" t="s">
+      <c r="A10" s="35"/>
+      <c r="B10" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="34">
         <v>0</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="16" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="36"/>
-      <c r="B11" s="14" t="s">
+      <c r="A11" s="35"/>
+      <c r="B11" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="34">
         <v>0</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="16" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" ht="17.399999999999999" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
     </row>
     <row r="13" ht="22.800000000000001" customHeight="1">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="29" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="14" ht="28.199999999999999" customHeight="1">
-      <c r="A14" s="37"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="36"/>
+      <c r="B14" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="30"/>
+      <c r="D14" s="29"/>
     </row>
     <row r="15" ht="28.199999999999999" customHeight="1">
-      <c r="A15" s="37"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
+      <c r="A15" s="36"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="37"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
+      <c r="A16" s="36"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="37"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
     </row>
     <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="37"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
+      <c r="A18" s="36"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
     </row>
     <row r="19" ht="17.399999999999999" customHeight="1">
-      <c r="A19" s="38"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="29" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="39"/>
-      <c r="B21" s="29" t="s">
+      <c r="A21" s="38"/>
+      <c r="B21" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="29" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="22" ht="33.75" customHeight="1">
-      <c r="A22" s="39"/>
-      <c r="B22" s="30" t="s">
+      <c r="A22" s="38"/>
+      <c r="B22" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="30"/>
+      <c r="D22" s="29"/>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="39"/>
-      <c r="B23" s="29" t="s">
+      <c r="A23" s="38"/>
+      <c r="B23" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C23" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="30"/>
+      <c r="D23" s="29"/>
     </row>
     <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="39"/>
-      <c r="B24" s="29" t="s">
+      <c r="A24" s="38"/>
+      <c r="B24" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="30"/>
+      <c r="D24" s="29"/>
     </row>
     <row r="25" ht="27" customHeight="1">
-      <c r="A25" s="39"/>
-      <c r="B25" s="29" t="s">
+      <c r="A25" s="38"/>
+      <c r="B25" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="30"/>
+      <c r="D25" s="29"/>
     </row>
     <row r="26" ht="27" customHeight="1">
-      <c r="A26" s="39"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
     </row>
     <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="39"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
     </row>
     <row r="28" ht="27" customHeight="1">
-      <c r="A28" s="39"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
+      <c r="A28" s="38"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
     </row>
     <row r="29" ht="17.399999999999999" customHeight="1">
       <c r="A29" s="5"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
     </row>
     <row r="30" ht="27.75" customHeight="1">
-      <c r="A30" s="40" t="s">
+      <c r="A30" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="30" t="s">
+      <c r="D30" s="29" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="31" ht="27.75" customHeight="1">
-      <c r="A31" s="40"/>
-      <c r="B31" s="29" t="s">
+      <c r="A31" s="39"/>
+      <c r="B31" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="30" t="s">
+      <c r="C31" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="30" t="s">
+      <c r="D31" s="29" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="32" ht="28.5">
-      <c r="A32" s="40"/>
-      <c r="B32" s="29" t="s">
+      <c r="A32" s="39"/>
+      <c r="B32" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="D32" s="30"/>
+      <c r="D32" s="29"/>
     </row>
     <row r="33" ht="28.5">
-      <c r="A33" s="40"/>
-      <c r="B33" s="29" t="s">
+      <c r="A33" s="39"/>
+      <c r="B33" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="30" t="s">
+      <c r="C33" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="D33" s="30"/>
+      <c r="D33" s="29"/>
     </row>
     <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="40"/>
-      <c r="B34" s="29" t="s">
+      <c r="A34" s="39"/>
+      <c r="B34" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="30" t="s">
+      <c r="C34" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="29" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="35" ht="31.199999999999999" customHeight="1">
-      <c r="A35" s="40"/>
-      <c r="B35" s="29" t="s">
+      <c r="A35" s="39"/>
+      <c r="B35" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="30"/>
+      <c r="D35" s="29"/>
     </row>
     <row r="36" ht="28.800000000000001" customHeight="1">
-      <c r="A36" s="40"/>
-      <c r="B36" s="29" t="s">
+      <c r="A36" s="39"/>
+      <c r="B36" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C36" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="D36" s="30" t="s">
+      <c r="D36" s="29" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="37" ht="29.399999999999999" customHeight="1">
-      <c r="A37" s="40"/>
-      <c r="B37" s="29" t="s">
+      <c r="A37" s="39"/>
+      <c r="B37" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="30" t="s">
+      <c r="C37" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D37" s="30" t="s">
+      <c r="D37" s="29" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="38" ht="42.75">
-      <c r="A38" s="40"/>
-      <c r="B38" s="29" t="s">
+      <c r="A38" s="39"/>
+      <c r="B38" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="D38" s="30" t="s">
+      <c r="D38" s="29" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="39" ht="28.800000000000001" customHeight="1">
-      <c r="A39" s="40"/>
-      <c r="B39" s="30" t="s">
+      <c r="A39" s="39"/>
+      <c r="B39" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="30"/>
+      <c r="D39" s="29"/>
     </row>
     <row r="40" ht="28.800000000000001" customHeight="1">
-      <c r="A40" s="40"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
+      <c r="A40" s="39"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
     </row>
     <row r="41" ht="28.5" customHeight="1">
-      <c r="A41" s="40"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
+      <c r="A41" s="39"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
     </row>
     <row r="42" ht="28.5" customHeight="1">
-      <c r="A42" s="40"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
+      <c r="A42" s="39"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
     </row>
     <row r="43" ht="28.5" customHeight="1">
-      <c r="A43" s="40"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
+      <c r="A43" s="39"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
     </row>
     <row r="44" ht="28.5" customHeight="1">
-      <c r="A44" s="40"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
+      <c r="A44" s="39"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
     </row>
     <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" s="40"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
+      <c r="A45" s="39"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
     </row>
     <row r="46" ht="28.5" customHeight="1">
-      <c r="B46" s="24"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
     </row>
     <row r="47" ht="28.5" customHeight="1">
-      <c r="B47" s="24"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="25"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
     </row>
     <row r="48" ht="28.5" customHeight="1"/>
     <row r="49" ht="28.5" customHeight="1"/>
@@ -2257,7 +2253,7 @@
       <c r="A3" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>112</v>
       </c>
       <c r="C3" t="s">
@@ -2274,7 +2270,7 @@
       <c r="B4" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="41" t="s">
         <v>109</v>
       </c>
       <c r="D4" t="s">
@@ -2288,7 +2284,7 @@
       <c r="B5" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="41" t="s">
         <v>109</v>
       </c>
       <c r="D5" t="s">
@@ -2296,13 +2292,13 @@
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="40" t="s">
         <v>119</v>
       </c>
       <c r="B6" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="41" t="s">
         <v>109</v>
       </c>
       <c r="D6" t="s">
@@ -2310,13 +2306,13 @@
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="40" t="s">
         <v>122</v>
       </c>
       <c r="B7" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="41" t="s">
         <v>109</v>
       </c>
       <c r="D7" t="s">
@@ -3329,7 +3325,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="43" width="38.421875"/>
+    <col customWidth="1" min="2" max="2" style="42" width="38.421875"/>
     <col customWidth="1" min="3" max="3" width="55.421875"/>
     <col customWidth="1" min="4" max="4" width="75.8515625"/>
   </cols>
@@ -3338,207 +3334,208 @@
       <c r="A1" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="43" customFormat="1" ht="28.5">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45" t="s">
+    <row r="2" s="42" customFormat="1" ht="28.5">
+      <c r="A2" s="43"/>
+      <c r="B2" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="45" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="3" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="44"/>
-      <c r="B3" s="45" t="s">
+    <row r="3" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A3" s="43"/>
+      <c r="B3" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="46"/>
-    </row>
-    <row r="4" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-    </row>
-    <row r="5" s="43" customFormat="1" ht="57">
-      <c r="A5" s="44"/>
-      <c r="B5" s="46" t="s">
+      <c r="D3" s="45"/>
+    </row>
+    <row r="4" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+    </row>
+    <row r="5" s="42" customFormat="1" ht="57">
+      <c r="A5" s="43"/>
+      <c r="B5" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="45" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="6" s="43" customFormat="1" ht="36" customHeight="1">
-      <c r="A6" s="44"/>
-      <c r="B6" s="47" t="s">
+    <row r="6" s="42" customFormat="1" ht="36" customHeight="1">
+      <c r="A6" s="43"/>
+      <c r="B6" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="45" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="45" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="7" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="44"/>
-      <c r="B7" s="45" t="s">
+      <c r="G6" s="42"/>
+    </row>
+    <row r="7" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A7" s="43"/>
+      <c r="B7" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="45" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="8" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A8" s="44"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
+    <row r="8" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A8" s="43"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="49"/>
+      <c r="B9" s="47"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
     </row>
     <row r="10" ht="41.25" customHeight="1">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="49" t="s">
         <v>142</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="29" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="52"/>
-      <c r="B11" s="29" t="s">
+      <c r="A11" s="50"/>
+      <c r="B11" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>60000</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="29" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="52"/>
-      <c r="B12" s="29" t="s">
+      <c r="A12" s="50"/>
+      <c r="B12" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="29">
         <v>3000</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="29" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="13" ht="36.75" customHeight="1">
-      <c r="A13" s="52"/>
-      <c r="B13" s="29" t="s">
+      <c r="A13" s="50"/>
+      <c r="B13" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="29" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="52"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="50"/>
+      <c r="B14" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="51" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="29" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="15" ht="63.600000000000001" customHeight="1">
-      <c r="A15" s="52"/>
-      <c r="B15" s="29" t="s">
+      <c r="A15" s="50"/>
+      <c r="B15" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="29" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="49"/>
+      <c r="B16" s="47"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="52" t="s">
         <v>157</v>
       </c>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="53" t="s">
         <v>158</v>
       </c>
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="54" t="s">
         <v>159</v>
       </c>
-      <c r="D17" s="57" t="s">
+      <c r="D17" s="55" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="54"/>
-      <c r="B18" s="55" t="s">
+      <c r="A18" s="52"/>
+      <c r="B18" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="C18" s="56">
+      <c r="C18" s="54">
         <v>5000</v>
       </c>
-      <c r="D18" s="56" t="s">
+      <c r="D18" s="54" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="54"/>
-      <c r="B19" s="55" t="s">
+      <c r="A19" s="52"/>
+      <c r="B19" s="53" t="s">
         <v>163</v>
       </c>
-      <c r="C19" s="56" t="s">
+      <c r="C19" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="D19" s="56" t="s">
+      <c r="D19" s="54" t="s">
         <v>164</v>
       </c>
     </row>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
   <si>
     <t>Name</t>
   </si>
@@ -296,6 +296,12 @@
     <t xml:space="preserve">Periodo de trabalho aberto com sucesso!</t>
   </si>
   <si>
+    <t>LogMessage_SuccessArcriveRead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arquivo de importação lido com sucesso!</t>
+  </si>
+  <si>
     <t xml:space="preserve">INFORMATION MESSAGES</t>
   </si>
   <si>
@@ -341,6 +347,36 @@
     <t xml:space="preserve">Abrindo periodo de fechamento...</t>
   </si>
   <si>
+    <t>LogMessage_ImportationError</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houve um erro no momento da importação!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quando, no momento de apresentação dos relatórios, após ler os arquivos de importação, é apresentado um erro.</t>
+  </si>
+  <si>
+    <t>LogMessage_ImportationStructuralCritiques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foram apresentadas criticas às estruturas dos arquivos txt de importação.</t>
+  </si>
+  <si>
+    <t>LogMessage_ImportationAdvertencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existem advertências relativas aos arquivos de importação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quando, no momento de apresentação dos relatórios, após ler os arquivos de importação, é apresentada a tela de advertências. É necessário selecionar todos os registros à serem importados.</t>
+  </si>
+  <si>
+    <t>LogMessage_EnableExpensesIntegration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opção 'enableExpensesIntegration' está desabilitada, o processo não irá integrar as obrigações.</t>
+  </si>
+  <si>
     <t xml:space="preserve">EXCEPTION LOG MESSAGES</t>
   </si>
   <si>
@@ -416,12 +452,18 @@
     <t xml:space="preserve">Caso haja um erro durante o processo de definição de datas do request das despesas. </t>
   </si>
   <si>
-    <t>ExceptionMessage_CriticasDeEstruturasAosTxtsDeImportacao</t>
+    <t>ExceptionMessage_StructuralCritiquesToImportationArchives</t>
   </si>
   <si>
     <t xml:space="preserve">Foram exibidas criticas de estruturas aos txts de importação no processo de importação. Favor verificar</t>
   </si>
   <si>
+    <t>ExceptionMessage_ImportationReportDoNotExist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O relatorio de importações do Domínio não foi apresentado.</t>
+  </si>
+  <si>
     <t>Asset</t>
   </si>
   <si>
@@ -528,6 +570,15 @@
   </si>
   <si>
     <t xml:space="preserve">Data final do periodo de trabalho cadastrado no sistema Domínio.</t>
+  </si>
+  <si>
+    <t>attribute_invisibleElement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">não disponível</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atributo que é apresentado quando um determinado elemento é apresentado na tela, mas não está disponivel para iteração. </t>
   </si>
   <si>
     <t>GetExpensesSettings</t>
@@ -754,7 +805,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="63">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -787,6 +838,7 @@
     <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="2" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
@@ -848,6 +900,12 @@
     <xf fontId="4" fillId="9" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="4" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
@@ -874,6 +932,12 @@
     <xf fontId="0" fillId="0" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -900,6 +964,12 @@
     </xf>
     <xf fontId="0" fillId="12" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="12" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="12" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1497,13 +1567,13 @@
     </row>
     <row r="6" ht="27" customHeight="1">
       <c r="A6" s="8"/>
-      <c r="B6" s="12"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="13"/>
       <c r="D6" s="11"/>
     </row>
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="8"/>
-      <c r="B7" s="12"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="13"/>
       <c r="D7" s="11"/>
     </row>
@@ -1514,90 +1584,90 @@
       <c r="D8" s="7"/>
     </row>
     <row r="9" ht="31.199999999999999" customHeight="1">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16" t="s">
+      <c r="C9" s="16"/>
+      <c r="D9" s="17" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" ht="33.600000000000001" customHeight="1">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15" t="s">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" ht="43.200000000000003" customHeight="1">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15" t="s">
+      <c r="A11" s="15"/>
+      <c r="B11" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="17" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" ht="61.200000000000003" customHeight="1">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15" t="s">
+      <c r="A12" s="15"/>
+      <c r="B12" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="17" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" ht="28.800000000000001" customHeight="1">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15" t="s">
+      <c r="A13" s="15"/>
+      <c r="B13" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="15" t="b">
+      <c r="C13" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="D13" s="15"/>
+      <c r="D13" s="16"/>
     </row>
     <row r="14" ht="28.800000000000001" customHeight="1">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15" t="s">
+      <c r="A14" s="15"/>
+      <c r="B14" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="15" t="b">
+      <c r="C14" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="D14" s="15"/>
+      <c r="D14" s="16"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="14"/>
-      <c r="B15" s="19" t="s">
+      <c r="A15" s="15"/>
+      <c r="B15" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="21" t="s">
+      <c r="C15" s="21"/>
+      <c r="D15" s="22" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" ht="34.799999999999997" customHeight="1">
-      <c r="A16" s="14"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="15"/>
+      <c r="B16" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="21" t="s">
+      <c r="C16" s="16"/>
+      <c r="D16" s="22" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1608,38 +1678,38 @@
       <c r="D17" s="5"/>
     </row>
     <row r="18" ht="46.799999999999997" customHeight="1">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="17" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" ht="46.799999999999997" customHeight="1">
-      <c r="A19" s="22"/>
-      <c r="B19" s="15" t="s">
+      <c r="A19" s="23"/>
+      <c r="B19" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="15"/>
+      <c r="D19" s="16"/>
     </row>
     <row r="20" ht="43.200000000000003" customHeight="1">
-      <c r="A20" s="22"/>
-      <c r="B20" s="15" t="s">
+      <c r="A20" s="23"/>
+      <c r="B20" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="16"/>
+      <c r="D20" s="17"/>
     </row>
     <row r="21" ht="14.25">
       <c r="C21" s="1"/>
@@ -1695,20 +1765,20 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8.00390625"/>
-    <col customWidth="1" min="2" max="2" style="23" width="52.140625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="24" width="63.11328125"/>
-    <col customWidth="1" min="4" max="4" style="24" width="84.140625"/>
+    <col customWidth="1" min="2" max="2" style="24" width="53.8515625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="25" width="63.11328125"/>
+    <col customWidth="1" min="4" max="4" style="25" width="84.140625"/>
     <col customWidth="1" min="5" max="27" width="8.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="27" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2"/>
@@ -1736,435 +1806,485 @@
       <c r="AA1" s="2"/>
     </row>
     <row r="2" ht="28.5">
-      <c r="A2" s="27"/>
-      <c r="B2" s="28" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="30">
         <v>1</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="30" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" ht="28.5">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28" t="s">
+      <c r="A3" s="28"/>
+      <c r="B3" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="30">
         <v>3</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="30" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="27"/>
-      <c r="B4" s="28" t="s">
+      <c r="A4" s="28"/>
+      <c r="B4" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="30" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" ht="28.5">
-      <c r="A5" s="27"/>
-      <c r="B5" s="28" t="s">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>15</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="30" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" ht="28.5">
-      <c r="A6" s="27"/>
-      <c r="B6" s="28" t="s">
+      <c r="A6" s="28"/>
+      <c r="B6" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>2</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="30" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" s="30" customFormat="1" ht="17.399999999999999" customHeight="1">
+    <row r="7" s="31" customFormat="1" ht="17.399999999999999" customHeight="1">
       <c r="A7" s="5"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
     </row>
     <row r="8" ht="39.75" customHeight="1">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="35">
         <v>30000</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="17" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="9" ht="39.75" customHeight="1">
-      <c r="A9" s="35"/>
-      <c r="B9" s="15" t="s">
+      <c r="A9" s="36"/>
+      <c r="B9" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="35">
         <v>20000</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="17" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="35"/>
-      <c r="B10" s="15" t="s">
+      <c r="A10" s="36"/>
+      <c r="B10" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <v>0</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="17" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="35"/>
-      <c r="B11" s="15" t="s">
+      <c r="A11" s="36"/>
+      <c r="B11" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="35">
         <v>0</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" ht="17.399999999999999" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
     </row>
     <row r="13" ht="22.800000000000001" customHeight="1">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="30" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="14" ht="28.199999999999999" customHeight="1">
-      <c r="A14" s="36"/>
-      <c r="B14" s="28" t="s">
+      <c r="A14" s="37"/>
+      <c r="B14" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="29"/>
+      <c r="D14" s="30"/>
     </row>
     <row r="15" ht="28.199999999999999" customHeight="1">
-      <c r="A15" s="36"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="30"/>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="36"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="36"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
     </row>
     <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="36"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
     </row>
     <row r="19" ht="17.399999999999999" customHeight="1">
-      <c r="A19" s="37"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
+      <c r="A19" s="40"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="29" t="s">
+      <c r="A20" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="B20" s="29" t="s">
         <v>65</v>
       </c>
+      <c r="C20" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="38"/>
-      <c r="B21" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="29" t="s">
+      <c r="A21" s="41"/>
+      <c r="B21" s="29" t="s">
         <v>68</v>
       </c>
+      <c r="C21" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="22" ht="33.75" customHeight="1">
-      <c r="A22" s="38"/>
-      <c r="B22" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="29"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="30"/>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="38"/>
-      <c r="B23" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="29"/>
+      <c r="A23" s="41"/>
+      <c r="B23" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="30"/>
     </row>
     <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="38"/>
-      <c r="B24" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" s="29"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="30"/>
     </row>
     <row r="25" ht="27" customHeight="1">
-      <c r="A25" s="38"/>
-      <c r="B25" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" s="29"/>
-    </row>
-    <row r="26" ht="27" customHeight="1">
-      <c r="A26" s="38"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-    </row>
-    <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="38"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-    </row>
-    <row r="28" ht="27" customHeight="1">
-      <c r="A28" s="38"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-    </row>
-    <row r="29" ht="17.399999999999999" customHeight="1">
-      <c r="A29" s="5"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-    </row>
-    <row r="30" ht="27.75" customHeight="1">
-      <c r="A30" s="39" t="s">
+      <c r="A25" s="41"/>
+      <c r="B25" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="C25" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="D25" s="30"/>
+    </row>
+    <row r="26" ht="28.5">
+      <c r="A26" s="41"/>
+      <c r="B26" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="29" t="s">
+      <c r="C26" s="39" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="31" ht="27.75" customHeight="1">
-      <c r="A31" s="39"/>
-      <c r="B31" s="28" t="s">
+      <c r="D26" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="29" t="s">
+    </row>
+    <row r="27" ht="28.5">
+      <c r="A27" s="41"/>
+      <c r="B27" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="29" t="s">
+      <c r="C27" s="39" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="32" ht="28.5">
-      <c r="A32" s="39"/>
-      <c r="B32" s="28" t="s">
+      <c r="D27" s="39" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" ht="42.75">
+      <c r="A28" s="41"/>
+      <c r="B28" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C28" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="D32" s="29"/>
-    </row>
-    <row r="33" ht="28.5">
-      <c r="A33" s="39"/>
-      <c r="B33" s="28" t="s">
+      <c r="D28" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="29" t="s">
+    </row>
+    <row r="29" ht="28.800000000000001" customHeight="1">
+      <c r="A29" s="41"/>
+      <c r="B29" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="D33" s="29"/>
+      <c r="C29" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="39"/>
+    </row>
+    <row r="30" ht="27.600000000000001" customHeight="1">
+      <c r="A30" s="41"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+    </row>
+    <row r="31" ht="26.399999999999999" customHeight="1">
+      <c r="A31" s="41"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+    </row>
+    <row r="32" ht="27" customHeight="1">
+      <c r="A32" s="41"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+    </row>
+    <row r="33" ht="17.399999999999999" customHeight="1">
+      <c r="A33" s="5"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
     </row>
     <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="39"/>
-      <c r="B34" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="29" t="s">
+      <c r="A34" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="B34" s="29" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="35" ht="31.199999999999999" customHeight="1">
-      <c r="A35" s="39"/>
-      <c r="B35" s="28" t="s">
+      <c r="C34" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="D34" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="29"/>
-    </row>
-    <row r="36" ht="28.800000000000001" customHeight="1">
-      <c r="A36" s="39"/>
-      <c r="B36" s="28" t="s">
+    </row>
+    <row r="35" ht="27.75" customHeight="1">
+      <c r="A35" s="42"/>
+      <c r="B35" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C35" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D35" s="30" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="37" ht="29.399999999999999" customHeight="1">
-      <c r="A37" s="39"/>
-      <c r="B37" s="28" t="s">
+    <row r="36" ht="28.5">
+      <c r="A36" s="42"/>
+      <c r="B36" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C36" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="D37" s="29" t="s">
+      <c r="D36" s="30"/>
+    </row>
+    <row r="37" ht="28.5">
+      <c r="A37" s="42"/>
+      <c r="B37" s="29" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="38" ht="42.75">
-      <c r="A38" s="39"/>
-      <c r="B38" s="28" t="s">
+      <c r="C37" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="D37" s="30"/>
+    </row>
+    <row r="38" ht="27.75" customHeight="1">
+      <c r="A38" s="42"/>
+      <c r="B38" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="D38" s="29" t="s">
+      <c r="C38" s="30" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="39" ht="28.800000000000001" customHeight="1">
-      <c r="A39" s="39"/>
+      <c r="D38" s="30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" ht="31.199999999999999" customHeight="1">
+      <c r="A39" s="42"/>
       <c r="B39" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="C39" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="29"/>
+      <c r="C39" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="30"/>
     </row>
     <row r="40" ht="28.800000000000001" customHeight="1">
-      <c r="A40" s="39"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-    </row>
-    <row r="41" ht="28.5" customHeight="1">
-      <c r="A41" s="39"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-    </row>
-    <row r="42" ht="28.5" customHeight="1">
-      <c r="A42" s="39"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-    </row>
-    <row r="43" ht="28.5" customHeight="1">
-      <c r="A43" s="39"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-    </row>
-    <row r="44" ht="28.5" customHeight="1">
-      <c r="A44" s="39"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
+      <c r="A40" s="42"/>
+      <c r="B40" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" s="30" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" ht="29.399999999999999" customHeight="1">
+      <c r="A41" s="42"/>
+      <c r="B41" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" s="30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" ht="42.75">
+      <c r="A42" s="42"/>
+      <c r="B42" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="D42" s="30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" ht="28.800000000000001" customHeight="1">
+      <c r="A43" s="42"/>
+      <c r="B43" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" s="30"/>
+    </row>
+    <row r="44" ht="28.800000000000001" customHeight="1">
+      <c r="A44" s="42"/>
+      <c r="B44" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="D44" s="30"/>
     </row>
     <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" s="39"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
+      <c r="A45" s="42"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
     </row>
     <row r="46" ht="28.5" customHeight="1">
-      <c r="B46" s="23"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
+      <c r="A46" s="42"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
     </row>
     <row r="47" ht="28.5" customHeight="1">
-      <c r="B47" s="23"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-    </row>
-    <row r="48" ht="28.5" customHeight="1"/>
-    <row r="49" ht="28.5" customHeight="1"/>
-    <row r="50" ht="28.5" customHeight="1"/>
-    <row r="51" ht="28.5" customHeight="1"/>
+      <c r="A47" s="42"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+    </row>
+    <row r="48" ht="28.5" customHeight="1">
+      <c r="A48" s="42"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+    </row>
+    <row r="49" ht="28.5" customHeight="1">
+      <c r="A49" s="42"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+    </row>
+    <row r="50" ht="28.5" customHeight="1">
+      <c r="B50" s="24"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+    </row>
+    <row r="51" ht="28.5" customHeight="1">
+      <c r="B51" s="24"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+    </row>
     <row r="52" ht="28.5" customHeight="1"/>
     <row r="53" ht="28.5" customHeight="1"/>
     <row r="54" ht="28.5" customHeight="1"/>
@@ -2174,13 +2294,17 @@
     <row r="58" ht="28.5" customHeight="1"/>
     <row r="59" ht="28.5" customHeight="1"/>
     <row r="60" ht="28.5" customHeight="1"/>
+    <row r="61" ht="28.5" customHeight="1"/>
+    <row r="62" ht="28.5" customHeight="1"/>
+    <row r="63" ht="28.5" customHeight="1"/>
+    <row r="64" ht="28.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A13:A18"/>
-    <mergeCell ref="A20:A28"/>
-    <mergeCell ref="A30:A45"/>
+    <mergeCell ref="A20:A32"/>
+    <mergeCell ref="A34:A49"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -2204,13 +2328,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2237,86 +2361,86 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" s="40" t="s">
-        <v>112</v>
+        <v>125</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>126</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="41" t="s">
-        <v>109</v>
+        <v>128</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>123</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>109</v>
+        <v>131</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="40" t="s">
-        <v>119</v>
+      <c r="A6" s="43" t="s">
+        <v>133</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>109</v>
+        <v>134</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>123</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="40" t="s">
-        <v>122</v>
+      <c r="A7" s="43" t="s">
+        <v>136</v>
       </c>
       <c r="B7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="41" t="s">
-        <v>109</v>
-      </c>
       <c r="D7" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1"/>
@@ -3325,221 +3449,229 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="42" width="38.421875"/>
+    <col customWidth="1" min="2" max="2" style="45" width="38.421875"/>
     <col customWidth="1" min="3" max="3" width="55.421875"/>
     <col customWidth="1" min="4" max="4" width="75.8515625"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
       <c r="A1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="27" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="42" customFormat="1" ht="28.5">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" s="45" t="s">
-        <v>127</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="3" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="43"/>
-      <c r="B3" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="D3" s="45"/>
-    </row>
-    <row r="4" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="43"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-    </row>
-    <row r="5" s="42" customFormat="1" ht="57">
-      <c r="A5" s="43"/>
-      <c r="B5" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" s="42" customFormat="1" ht="36" customHeight="1">
-      <c r="A6" s="43"/>
-      <c r="B6" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="G6" s="42"/>
-    </row>
-    <row r="7" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="43"/>
-      <c r="B7" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="C7" s="46" t="s">
-        <v>138</v>
-      </c>
-      <c r="D7" s="45" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="8" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A8" s="43"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
+    <row r="2" s="45" customFormat="1" ht="28.5">
+      <c r="A2" s="46"/>
+      <c r="B2" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A3" s="46"/>
+      <c r="B3" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="48"/>
+    </row>
+    <row r="4" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A4" s="46"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+    </row>
+    <row r="5" s="45" customFormat="1" ht="57">
+      <c r="A5" s="46"/>
+      <c r="B5" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="48" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" s="45" customFormat="1" ht="36" customHeight="1">
+      <c r="A6" s="46"/>
+      <c r="B6" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>150</v>
+      </c>
+      <c r="G6" s="45"/>
+    </row>
+    <row r="7" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A7" s="46"/>
+      <c r="B7" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="48" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" s="45" customFormat="1" ht="28.5">
+      <c r="A8" s="46"/>
+      <c r="B8" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="47"/>
+      <c r="B9" s="52"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
     </row>
     <row r="10" ht="41.25" customHeight="1">
-      <c r="A10" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>143</v>
+      <c r="A10" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="50"/>
-      <c r="B11" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="C11" s="29">
+      <c r="A11" s="55"/>
+      <c r="B11" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="30">
         <v>60000</v>
       </c>
-      <c r="D11" s="29" t="s">
-        <v>145</v>
+      <c r="D11" s="30" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="50"/>
-      <c r="B12" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="C12" s="29">
+      <c r="A12" s="55"/>
+      <c r="B12" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="30">
         <v>3000</v>
       </c>
-      <c r="D12" s="29" t="s">
-        <v>147</v>
+      <c r="D12" s="30" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="13" ht="36.75" customHeight="1">
-      <c r="A13" s="50"/>
-      <c r="B13" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>150</v>
+      <c r="A13" s="55"/>
+      <c r="B13" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="50"/>
-      <c r="B14" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>153</v>
+      <c r="A14" s="55"/>
+      <c r="B14" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>169</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="15" ht="63.600000000000001" customHeight="1">
-      <c r="A15" s="50"/>
-      <c r="B15" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>156</v>
+      <c r="A15" s="55"/>
+      <c r="B15" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" s="56" t="s">
+        <v>172</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="47"/>
+      <c r="B16" s="52"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="B17" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="C17" s="54" t="s">
-        <v>159</v>
-      </c>
-      <c r="D17" s="55" t="s">
-        <v>160</v>
+      <c r="A17" s="57" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="D17" s="60" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="52"/>
-      <c r="B18" s="53" t="s">
-        <v>161</v>
-      </c>
-      <c r="C18" s="54">
+      <c r="A18" s="57"/>
+      <c r="B18" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="C18" s="62">
         <v>5000</v>
       </c>
-      <c r="D18" s="54" t="s">
-        <v>162</v>
+      <c r="D18" s="62" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="52"/>
-      <c r="B19" s="53" t="s">
-        <v>163</v>
-      </c>
-      <c r="C19" s="54" t="s">
-        <v>149</v>
-      </c>
-      <c r="D19" s="54" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="20" ht="28.199999999999999" customHeight="1"/>
+      <c r="A19" s="57"/>
+      <c r="B19" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="C19" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" s="62" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" ht="28.199999999999999" customHeight="1">
+      <c r="B20" s="45"/>
+    </row>
     <row r="21" ht="28.199999999999999" customHeight="1"/>
     <row r="22" ht="28.199999999999999" customHeight="1"/>
     <row r="23" ht="28.199999999999999" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -383,7 +383,7 @@
     <t>ExceptionMessage_GetTransactionData</t>
   </si>
   <si>
-    <t xml:space="preserve">Error getting transaction data for Transaction Number: </t>
+    <t xml:space="preserve">Error no get company para a empresa: </t>
   </si>
   <si>
     <t xml:space="preserve">Static part of logging message. Error retrieving Transaction Data.</t>
@@ -805,7 +805,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="58">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -838,7 +838,6 @@
     <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="2" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
@@ -900,12 +899,6 @@
     <xf fontId="4" fillId="9" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="4" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
@@ -913,6 +906,12 @@
     <xf fontId="4" fillId="11" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
@@ -932,12 +931,6 @@
     <xf fontId="0" fillId="0" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -964,12 +957,6 @@
     </xf>
     <xf fontId="0" fillId="12" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="12" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="12" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1567,13 +1554,13 @@
     </row>
     <row r="6" ht="27" customHeight="1">
       <c r="A6" s="8"/>
-      <c r="B6" s="14"/>
+      <c r="B6" s="12"/>
       <c r="C6" s="13"/>
       <c r="D6" s="11"/>
     </row>
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="8"/>
-      <c r="B7" s="14"/>
+      <c r="B7" s="12"/>
       <c r="C7" s="13"/>
       <c r="D7" s="11"/>
     </row>
@@ -1584,90 +1571,90 @@
       <c r="D8" s="7"/>
     </row>
     <row r="9" ht="31.199999999999999" customHeight="1">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17" t="s">
+      <c r="C9" s="15"/>
+      <c r="D9" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" ht="33.600000000000001" customHeight="1">
-      <c r="A10" s="15"/>
-      <c r="B10" s="16" t="s">
+      <c r="A10" s="14"/>
+      <c r="B10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" ht="43.200000000000003" customHeight="1">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16" t="s">
+      <c r="A11" s="14"/>
+      <c r="B11" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" ht="61.200000000000003" customHeight="1">
-      <c r="A12" s="15"/>
-      <c r="B12" s="16" t="s">
+      <c r="A12" s="14"/>
+      <c r="B12" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="16" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" ht="28.800000000000001" customHeight="1">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16" t="s">
+      <c r="A13" s="14"/>
+      <c r="B13" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="16" t="b">
+      <c r="C13" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="D13" s="16"/>
+      <c r="D13" s="15"/>
     </row>
     <row r="14" ht="28.800000000000001" customHeight="1">
-      <c r="A14" s="15"/>
-      <c r="B14" s="16" t="s">
+      <c r="A14" s="14"/>
+      <c r="B14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="16" t="b">
+      <c r="C14" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="D14" s="16"/>
+      <c r="D14" s="15"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="15"/>
-      <c r="B15" s="20" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="22" t="s">
+      <c r="C15" s="20"/>
+      <c r="D15" s="21" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" ht="34.799999999999997" customHeight="1">
-      <c r="A16" s="15"/>
-      <c r="B16" s="20" t="s">
+      <c r="A16" s="14"/>
+      <c r="B16" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="22" t="s">
+      <c r="C16" s="15"/>
+      <c r="D16" s="21" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1678,38 +1665,38 @@
       <c r="D17" s="5"/>
     </row>
     <row r="18" ht="46.799999999999997" customHeight="1">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="16" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" ht="46.799999999999997" customHeight="1">
-      <c r="A19" s="23"/>
-      <c r="B19" s="16" t="s">
+      <c r="A19" s="22"/>
+      <c r="B19" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="16"/>
+      <c r="D19" s="15"/>
     </row>
     <row r="20" ht="43.200000000000003" customHeight="1">
-      <c r="A20" s="23"/>
-      <c r="B20" s="16" t="s">
+      <c r="A20" s="22"/>
+      <c r="B20" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="17"/>
+      <c r="D20" s="16"/>
     </row>
     <row r="21" ht="14.25">
       <c r="C21" s="1"/>
@@ -1765,20 +1752,20 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8.00390625"/>
-    <col customWidth="1" min="2" max="2" style="24" width="53.8515625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="25" width="63.11328125"/>
-    <col customWidth="1" min="4" max="4" style="25" width="84.140625"/>
+    <col customWidth="1" min="2" max="2" style="23" width="53.8515625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="24" width="63.11328125"/>
+    <col customWidth="1" min="4" max="4" style="24" width="84.140625"/>
     <col customWidth="1" min="5" max="27" width="8.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2"/>
@@ -1806,484 +1793,484 @@
       <c r="AA1" s="2"/>
     </row>
     <row r="2" ht="28.5">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="30">
+      <c r="C2" s="29">
         <v>1</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="29" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" ht="28.5">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29" t="s">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3" s="29">
         <v>3</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="29" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29" t="s">
+      <c r="A4" s="27"/>
+      <c r="B4" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="29" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" ht="28.5">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29" t="s">
+      <c r="A5" s="27"/>
+      <c r="B5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>15</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="29" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" ht="28.5">
-      <c r="A6" s="28"/>
-      <c r="B6" s="29" t="s">
+      <c r="A6" s="27"/>
+      <c r="B6" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>2</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="29" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" s="31" customFormat="1" ht="17.399999999999999" customHeight="1">
+    <row r="7" s="30" customFormat="1" ht="17.399999999999999" customHeight="1">
       <c r="A7" s="5"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
     </row>
     <row r="8" ht="39.75" customHeight="1">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="34">
         <v>30000</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="9" ht="39.75" customHeight="1">
-      <c r="A9" s="36"/>
-      <c r="B9" s="16" t="s">
+      <c r="A9" s="35"/>
+      <c r="B9" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="34">
         <v>20000</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="36"/>
-      <c r="B10" s="16" t="s">
+      <c r="A10" s="35"/>
+      <c r="B10" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="34">
         <v>0</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="16" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="36"/>
-      <c r="B11" s="16" t="s">
+      <c r="A11" s="35"/>
+      <c r="B11" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="34">
         <v>0</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" ht="17.399999999999999" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
     </row>
     <row r="13" ht="22.800000000000001" customHeight="1">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="29" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="14" ht="28.199999999999999" customHeight="1">
-      <c r="A14" s="37"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="36"/>
+      <c r="B14" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="30"/>
+      <c r="D14" s="29"/>
     </row>
     <row r="15" ht="28.199999999999999" customHeight="1">
-      <c r="A15" s="37"/>
-      <c r="B15" s="38" t="s">
+      <c r="A15" s="36"/>
+      <c r="B15" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="30"/>
+      <c r="D15" s="29"/>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="37"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
+      <c r="A16" s="36"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="37"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
     </row>
     <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="37"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
+      <c r="A18" s="36"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
     </row>
     <row r="19" ht="17.399999999999999" customHeight="1">
-      <c r="A19" s="40"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="29" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="41"/>
-      <c r="B21" s="29" t="s">
+      <c r="A21" s="38"/>
+      <c r="B21" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="29" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="22" ht="33.75" customHeight="1">
-      <c r="A22" s="41"/>
-      <c r="B22" s="30" t="s">
+      <c r="A22" s="38"/>
+      <c r="B22" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="30"/>
+      <c r="D22" s="29"/>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="41"/>
-      <c r="B23" s="29" t="s">
+      <c r="A23" s="38"/>
+      <c r="B23" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C23" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="30"/>
+      <c r="D23" s="29"/>
     </row>
     <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="41"/>
-      <c r="B24" s="29" t="s">
+      <c r="A24" s="38"/>
+      <c r="B24" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="30"/>
+      <c r="D24" s="29"/>
     </row>
     <row r="25" ht="27" customHeight="1">
-      <c r="A25" s="41"/>
-      <c r="B25" s="29" t="s">
+      <c r="A25" s="38"/>
+      <c r="B25" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="30"/>
+      <c r="D25" s="29"/>
     </row>
     <row r="26" ht="28.5">
-      <c r="A26" s="41"/>
-      <c r="B26" s="38" t="s">
+      <c r="A26" s="38"/>
+      <c r="B26" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="39" t="s">
+      <c r="D26" s="29" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="27" ht="28.5">
-      <c r="A27" s="41"/>
-      <c r="B27" s="38" t="s">
+      <c r="A27" s="38"/>
+      <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="39" t="s">
+      <c r="D27" s="29" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="28" ht="42.75">
-      <c r="A28" s="41"/>
-      <c r="B28" s="38" t="s">
+      <c r="A28" s="38"/>
+      <c r="B28" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="D28" s="39" t="s">
+      <c r="D28" s="29" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="29" ht="28.800000000000001" customHeight="1">
-      <c r="A29" s="41"/>
-      <c r="B29" s="38" t="s">
+      <c r="A29" s="38"/>
+      <c r="B29" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="39"/>
+      <c r="D29" s="29"/>
     </row>
     <row r="30" ht="27.600000000000001" customHeight="1">
-      <c r="A30" s="41"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
+      <c r="A30" s="38"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
     </row>
     <row r="31" ht="26.399999999999999" customHeight="1">
-      <c r="A31" s="41"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
+      <c r="A31" s="38"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
     </row>
     <row r="32" ht="27" customHeight="1">
-      <c r="A32" s="41"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
+      <c r="A32" s="38"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
     </row>
     <row r="33" ht="17.399999999999999" customHeight="1">
       <c r="A33" s="5"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
     </row>
     <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="30" t="s">
+      <c r="C34" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="29" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="35" ht="27.75" customHeight="1">
-      <c r="A35" s="42"/>
-      <c r="B35" s="29" t="s">
+      <c r="A35" s="39"/>
+      <c r="B35" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="30" t="s">
+      <c r="D35" s="29" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="36" ht="28.5">
-      <c r="A36" s="42"/>
-      <c r="B36" s="29" t="s">
+      <c r="A36" s="39"/>
+      <c r="B36" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C36" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="30"/>
+      <c r="D36" s="29"/>
     </row>
     <row r="37" ht="28.5">
-      <c r="A37" s="42"/>
-      <c r="B37" s="29" t="s">
+      <c r="A37" s="39"/>
+      <c r="B37" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="30" t="s">
+      <c r="C37" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="30"/>
+      <c r="D37" s="29"/>
     </row>
     <row r="38" ht="27.75" customHeight="1">
-      <c r="A38" s="42"/>
-      <c r="B38" s="29" t="s">
+      <c r="A38" s="39"/>
+      <c r="B38" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="D38" s="30" t="s">
+      <c r="D38" s="29" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="39" ht="31.199999999999999" customHeight="1">
-      <c r="A39" s="42"/>
-      <c r="B39" s="29" t="s">
+      <c r="A39" s="39"/>
+      <c r="B39" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="D39" s="30"/>
+      <c r="D39" s="29"/>
     </row>
     <row r="40" ht="28.800000000000001" customHeight="1">
-      <c r="A40" s="42"/>
-      <c r="B40" s="29" t="s">
+      <c r="A40" s="39"/>
+      <c r="B40" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="30" t="s">
+      <c r="C40" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="30" t="s">
+      <c r="D40" s="29" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="41" ht="29.399999999999999" customHeight="1">
-      <c r="A41" s="42"/>
-      <c r="B41" s="29" t="s">
+      <c r="A41" s="39"/>
+      <c r="B41" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="C41" s="30" t="s">
+      <c r="C41" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="30" t="s">
+      <c r="D41" s="29" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="42" ht="42.75">
-      <c r="A42" s="42"/>
-      <c r="B42" s="29" t="s">
+      <c r="A42" s="39"/>
+      <c r="B42" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C42" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="D42" s="30" t="s">
+      <c r="D42" s="29" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="43" ht="28.800000000000001" customHeight="1">
-      <c r="A43" s="42"/>
-      <c r="B43" s="39" t="s">
+      <c r="A43" s="39"/>
+      <c r="B43" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="C43" s="30" t="s">
+      <c r="C43" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="D43" s="30"/>
+      <c r="D43" s="29"/>
     </row>
     <row r="44" ht="28.800000000000001" customHeight="1">
-      <c r="A44" s="42"/>
-      <c r="B44" s="38" t="s">
+      <c r="A44" s="39"/>
+      <c r="B44" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="C44" s="39" t="s">
+      <c r="C44" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="D44" s="30"/>
+      <c r="D44" s="29"/>
     </row>
     <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" s="42"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
+      <c r="A45" s="39"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
     </row>
     <row r="46" ht="28.5" customHeight="1">
-      <c r="A46" s="42"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
+      <c r="A46" s="39"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
     </row>
     <row r="47" ht="28.5" customHeight="1">
-      <c r="A47" s="42"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
+      <c r="A47" s="39"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
     </row>
     <row r="48" ht="28.5" customHeight="1">
-      <c r="A48" s="42"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
+      <c r="A48" s="39"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
     </row>
     <row r="49" ht="28.5" customHeight="1">
-      <c r="A49" s="42"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
+      <c r="A49" s="39"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
     </row>
     <row r="50" ht="28.5" customHeight="1">
-      <c r="B50" s="24"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="25"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
     </row>
     <row r="51" ht="28.5" customHeight="1">
-      <c r="B51" s="24"/>
-      <c r="C51" s="25"/>
-      <c r="D51" s="25"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
     </row>
     <row r="52" ht="28.5" customHeight="1"/>
     <row r="53" ht="28.5" customHeight="1"/>
@@ -2377,7 +2364,7 @@
       <c r="A3" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="42" t="s">
         <v>126</v>
       </c>
       <c r="C3" t="s">
@@ -2394,7 +2381,7 @@
       <c r="B4" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="43" t="s">
         <v>123</v>
       </c>
       <c r="D4" t="s">
@@ -2408,7 +2395,7 @@
       <c r="B5" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="43" t="s">
         <v>123</v>
       </c>
       <c r="D5" t="s">
@@ -2416,13 +2403,13 @@
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="42" t="s">
         <v>133</v>
       </c>
       <c r="B6" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="43" t="s">
         <v>123</v>
       </c>
       <c r="D6" t="s">
@@ -2430,13 +2417,13 @@
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="42" t="s">
         <v>136</v>
       </c>
       <c r="B7" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="43" t="s">
         <v>123</v>
       </c>
       <c r="D7" t="s">
@@ -3449,7 +3436,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="45" width="38.421875"/>
+    <col customWidth="1" min="2" max="2" style="44" width="38.421875"/>
     <col customWidth="1" min="3" max="3" width="55.421875"/>
     <col customWidth="1" min="4" max="4" width="75.8515625"/>
   </cols>
@@ -3458,219 +3445,219 @@
       <c r="A1" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="45" customFormat="1" ht="28.5">
-      <c r="A2" s="46"/>
-      <c r="B2" s="47" t="s">
+    <row r="2" s="44" customFormat="1" ht="28.5">
+      <c r="A2" s="45"/>
+      <c r="B2" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="47" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="47" t="s">
+    <row r="3" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A3" s="45"/>
+      <c r="B3" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="48"/>
-    </row>
-    <row r="4" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-    </row>
-    <row r="5" s="45" customFormat="1" ht="57">
-      <c r="A5" s="46"/>
-      <c r="B5" s="48" t="s">
+      <c r="D3" s="47"/>
+    </row>
+    <row r="4" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A4" s="45"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+    </row>
+    <row r="5" s="44" customFormat="1" ht="57">
+      <c r="A5" s="45"/>
+      <c r="B5" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="47" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D5" s="47" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" s="45" customFormat="1" ht="36" customHeight="1">
-      <c r="A6" s="46"/>
-      <c r="B6" s="48" t="s">
+    <row r="6" s="44" customFormat="1" ht="36" customHeight="1">
+      <c r="A6" s="45"/>
+      <c r="B6" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="47" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="45"/>
-    </row>
-    <row r="7" s="45" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="46"/>
-      <c r="B7" s="47" t="s">
+      <c r="G6" s="44"/>
+    </row>
+    <row r="7" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A7" s="45"/>
+      <c r="B7" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="47" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="8" s="45" customFormat="1" ht="28.5">
-      <c r="A8" s="46"/>
-      <c r="B8" s="50" t="s">
+    <row r="8" s="44" customFormat="1" ht="28.5">
+      <c r="A8" s="45"/>
+      <c r="B8" s="46" t="s">
         <v>154</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="47" t="s">
         <v>155</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="47" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="52"/>
+      <c r="B9" s="49"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
     </row>
     <row r="10" ht="41.25" customHeight="1">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="29" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="55"/>
-      <c r="B11" s="29" t="s">
+      <c r="A11" s="52"/>
+      <c r="B11" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>60000</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="29" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="55"/>
-      <c r="B12" s="29" t="s">
+      <c r="A12" s="52"/>
+      <c r="B12" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="29">
         <v>3000</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="29" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="13" ht="36.75" customHeight="1">
-      <c r="A13" s="55"/>
-      <c r="B13" s="29" t="s">
+      <c r="A13" s="52"/>
+      <c r="B13" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="29" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="55"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="52"/>
+      <c r="B14" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="53" t="s">
         <v>169</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="29" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="15" ht="63.600000000000001" customHeight="1">
-      <c r="A15" s="55"/>
-      <c r="B15" s="29" t="s">
+      <c r="A15" s="52"/>
+      <c r="B15" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="53" t="s">
         <v>172</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="29" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="52"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="57" t="s">
+      <c r="A17" s="54" t="s">
         <v>174</v>
       </c>
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="55" t="s">
         <v>175</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="C17" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="D17" s="60" t="s">
+      <c r="D17" s="57" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="57"/>
-      <c r="B18" s="61" t="s">
+      <c r="A18" s="54"/>
+      <c r="B18" s="55" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="62">
+      <c r="C18" s="56">
         <v>5000</v>
       </c>
-      <c r="D18" s="62" t="s">
+      <c r="D18" s="56" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="57"/>
-      <c r="B19" s="58" t="s">
+      <c r="A19" s="54"/>
+      <c r="B19" s="55" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C19" s="56" t="s">
         <v>166</v>
       </c>
-      <c r="D19" s="62" t="s">
+      <c r="D19" s="56" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="20" ht="28.199999999999999" customHeight="1">
-      <c r="B20" s="45"/>
+      <c r="B20" s="44"/>
     </row>
     <row r="21" ht="28.199999999999999" customHeight="1"/>
     <row r="22" ht="28.199999999999999" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
   <si>
     <t>Name</t>
   </si>
@@ -548,16 +548,13 @@
     <t>especificDebitAccount</t>
   </si>
   <si>
-    <t>2055,1055,2074,5572</t>
-  </si>
-  <si>
     <t xml:space="preserve">O Domínio pode apresentar erro de acordo com a quantidade de despesas inseridas em um determinado arquivo de importação. Por isso, existem as contas de débito específicas que devem estar separadas por arquivo de importação.Deve estar no fomraco "contaDeDebito,contaDeDebito,contaDeDebito"</t>
   </si>
   <si>
     <t>especificExceptDebitAccounts</t>
   </si>
   <si>
-    <t>2110,2074,1204,2103,2112,2055</t>
+    <t>2110,2074,1204,2103,2112,6</t>
   </si>
   <si>
     <t xml:space="preserve">Contas de débito que não devem ser importadas para o Domínio.</t>
@@ -805,7 +802,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -845,6 +842,7 @@
     <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -906,12 +904,6 @@
     <xf fontId="4" fillId="11" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
@@ -928,12 +920,21 @@
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="2" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
@@ -942,6 +943,9 @@
     </xf>
     <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1587,7 +1591,7 @@
       <c r="B10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="17" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="15" t="s">
@@ -1599,7 +1603,7 @@
       <c r="B11" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="18" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="16" t="s">
@@ -1611,7 +1615,7 @@
       <c r="B12" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="16" t="s">
@@ -1640,21 +1644,21 @@
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="14"/>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="21" t="s">
+      <c r="C15" s="21"/>
+      <c r="D15" s="22" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" ht="34.799999999999997" customHeight="1">
       <c r="A16" s="14"/>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="15"/>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="22" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1665,7 +1669,7 @@
       <c r="D17" s="5"/>
     </row>
     <row r="18" ht="46.799999999999997" customHeight="1">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="23" t="s">
         <v>28</v>
       </c>
       <c r="B18" s="12" t="s">
@@ -1679,7 +1683,7 @@
       </c>
     </row>
     <row r="19" ht="46.799999999999997" customHeight="1">
-      <c r="A19" s="22"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="15" t="s">
         <v>32</v>
       </c>
@@ -1689,11 +1693,11 @@
       <c r="D19" s="15"/>
     </row>
     <row r="20" ht="43.200000000000003" customHeight="1">
-      <c r="A20" s="22"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="18" t="s">
         <v>35</v>
       </c>
       <c r="D20" s="16"/>
@@ -1752,20 +1756,20 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8.00390625"/>
-    <col customWidth="1" min="2" max="2" style="23" width="53.8515625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="24" width="63.11328125"/>
-    <col customWidth="1" min="4" max="4" style="24" width="84.140625"/>
+    <col customWidth="1" min="2" max="2" style="24" width="53.8515625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="25" width="63.11328125"/>
+    <col customWidth="1" min="4" max="4" style="25" width="84.140625"/>
     <col customWidth="1" min="5" max="27" width="8.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="27" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2"/>
@@ -1793,79 +1797,79 @@
       <c r="AA1" s="2"/>
     </row>
     <row r="2" ht="28.5">
-      <c r="A2" s="27"/>
-      <c r="B2" s="28" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="30">
         <v>1</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="30" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" ht="28.5">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28" t="s">
+      <c r="A3" s="28"/>
+      <c r="B3" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="30">
         <v>3</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="30" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="27"/>
-      <c r="B4" s="28" t="s">
+      <c r="A4" s="28"/>
+      <c r="B4" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="30" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" ht="28.5">
-      <c r="A5" s="27"/>
-      <c r="B5" s="28" t="s">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>15</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="30" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" ht="28.5">
-      <c r="A6" s="27"/>
-      <c r="B6" s="28" t="s">
+      <c r="A6" s="28"/>
+      <c r="B6" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>2</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="30" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" s="30" customFormat="1" ht="17.399999999999999" customHeight="1">
+    <row r="7" s="31" customFormat="1" ht="17.399999999999999" customHeight="1">
       <c r="A7" s="5"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
     </row>
     <row r="8" ht="39.75" customHeight="1">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="35">
         <v>30000</v>
       </c>
       <c r="D8" s="16" t="s">
@@ -1873,11 +1877,11 @@
       </c>
     </row>
     <row r="9" ht="39.75" customHeight="1">
-      <c r="A9" s="35"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="35">
         <v>20000</v>
       </c>
       <c r="D9" s="16" t="s">
@@ -1885,11 +1889,11 @@
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="35"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <v>0</v>
       </c>
       <c r="D10" s="16" t="s">
@@ -1897,11 +1901,11 @@
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="35"/>
+      <c r="A11" s="36"/>
       <c r="B11" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="35">
         <v>0</v>
       </c>
       <c r="D11" s="16" t="s">
@@ -1910,367 +1914,367 @@
     </row>
     <row r="12" ht="17.399999999999999" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
     </row>
     <row r="13" ht="22.800000000000001" customHeight="1">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="30" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="14" ht="28.199999999999999" customHeight="1">
-      <c r="A14" s="36"/>
-      <c r="B14" s="28" t="s">
+      <c r="A14" s="37"/>
+      <c r="B14" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="29"/>
+      <c r="D14" s="30"/>
     </row>
     <row r="15" ht="28.199999999999999" customHeight="1">
-      <c r="A15" s="36"/>
-      <c r="B15" s="28" t="s">
+      <c r="A15" s="37"/>
+      <c r="B15" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="29"/>
+      <c r="D15" s="30"/>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="36"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="36"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
     </row>
     <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="36"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
     </row>
     <row r="19" ht="17.399999999999999" customHeight="1">
-      <c r="A19" s="37"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="30" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="38"/>
-      <c r="B21" s="28" t="s">
+      <c r="A21" s="39"/>
+      <c r="B21" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="30" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="22" ht="33.75" customHeight="1">
-      <c r="A22" s="38"/>
-      <c r="B22" s="29" t="s">
+      <c r="A22" s="39"/>
+      <c r="B22" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="29"/>
+      <c r="D22" s="30"/>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="38"/>
-      <c r="B23" s="28" t="s">
+      <c r="A23" s="39"/>
+      <c r="B23" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="29"/>
+      <c r="D23" s="30"/>
     </row>
     <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="38"/>
-      <c r="B24" s="28" t="s">
+      <c r="A24" s="39"/>
+      <c r="B24" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="29"/>
+      <c r="D24" s="30"/>
     </row>
     <row r="25" ht="27" customHeight="1">
-      <c r="A25" s="38"/>
-      <c r="B25" s="28" t="s">
+      <c r="A25" s="39"/>
+      <c r="B25" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="29"/>
+      <c r="D25" s="30"/>
     </row>
     <row r="26" ht="28.5">
-      <c r="A26" s="38"/>
-      <c r="B26" s="28" t="s">
+      <c r="A26" s="39"/>
+      <c r="B26" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="30" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="27" ht="28.5">
-      <c r="A27" s="38"/>
-      <c r="B27" s="28" t="s">
+      <c r="A27" s="39"/>
+      <c r="B27" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="30" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="28" ht="42.75">
-      <c r="A28" s="38"/>
-      <c r="B28" s="28" t="s">
+      <c r="A28" s="39"/>
+      <c r="B28" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="30" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="29" ht="28.800000000000001" customHeight="1">
-      <c r="A29" s="38"/>
-      <c r="B29" s="28" t="s">
+      <c r="A29" s="39"/>
+      <c r="B29" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="29"/>
+      <c r="D29" s="30"/>
     </row>
     <row r="30" ht="27.600000000000001" customHeight="1">
-      <c r="A30" s="38"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
+      <c r="A30" s="39"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
     </row>
     <row r="31" ht="26.399999999999999" customHeight="1">
-      <c r="A31" s="38"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
+      <c r="A31" s="39"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
     </row>
     <row r="32" ht="27" customHeight="1">
-      <c r="A32" s="38"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
+      <c r="A32" s="39"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
     </row>
     <row r="33" ht="17.399999999999999" customHeight="1">
       <c r="A33" s="5"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
     </row>
     <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="39" t="s">
+      <c r="A34" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="41" t="s">
+      <c r="C34" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="D34" s="30" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="35" ht="27.75" customHeight="1">
-      <c r="A35" s="39"/>
-      <c r="B35" s="28" t="s">
+      <c r="A35" s="40"/>
+      <c r="B35" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="29" t="s">
+      <c r="D35" s="30" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="36" ht="28.5">
-      <c r="A36" s="39"/>
-      <c r="B36" s="28" t="s">
+      <c r="A36" s="40"/>
+      <c r="B36" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="29"/>
+      <c r="D36" s="30"/>
     </row>
     <row r="37" ht="28.5">
-      <c r="A37" s="39"/>
-      <c r="B37" s="28" t="s">
+      <c r="A37" s="40"/>
+      <c r="B37" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="29"/>
+      <c r="D37" s="30"/>
     </row>
     <row r="38" ht="27.75" customHeight="1">
-      <c r="A38" s="39"/>
-      <c r="B38" s="28" t="s">
+      <c r="A38" s="40"/>
+      <c r="B38" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="D38" s="29" t="s">
+      <c r="D38" s="30" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="39" ht="31.199999999999999" customHeight="1">
-      <c r="A39" s="39"/>
-      <c r="B39" s="28" t="s">
+      <c r="A39" s="40"/>
+      <c r="B39" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="D39" s="29"/>
+      <c r="D39" s="30"/>
     </row>
     <row r="40" ht="28.800000000000001" customHeight="1">
-      <c r="A40" s="39"/>
-      <c r="B40" s="28" t="s">
+      <c r="A40" s="40"/>
+      <c r="B40" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="29" t="s">
+      <c r="D40" s="30" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="41" ht="29.399999999999999" customHeight="1">
-      <c r="A41" s="39"/>
-      <c r="B41" s="28" t="s">
+      <c r="A41" s="40"/>
+      <c r="B41" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="29" t="s">
+      <c r="D41" s="30" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="42" ht="42.75">
-      <c r="A42" s="39"/>
-      <c r="B42" s="28" t="s">
+      <c r="A42" s="40"/>
+      <c r="B42" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="D42" s="29" t="s">
+      <c r="D42" s="30" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="43" ht="28.800000000000001" customHeight="1">
-      <c r="A43" s="39"/>
-      <c r="B43" s="29" t="s">
+      <c r="A43" s="40"/>
+      <c r="B43" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="D43" s="29"/>
+      <c r="D43" s="30"/>
     </row>
     <row r="44" ht="28.800000000000001" customHeight="1">
-      <c r="A44" s="39"/>
-      <c r="B44" s="28" t="s">
+      <c r="A44" s="40"/>
+      <c r="B44" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="D44" s="29"/>
+      <c r="D44" s="30"/>
     </row>
     <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" s="39"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
+      <c r="A45" s="40"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
     </row>
     <row r="46" ht="28.5" customHeight="1">
-      <c r="A46" s="39"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
+      <c r="A46" s="40"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
     </row>
     <row r="47" ht="28.5" customHeight="1">
-      <c r="A47" s="39"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
+      <c r="A47" s="40"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
     </row>
     <row r="48" ht="28.5" customHeight="1">
-      <c r="A48" s="39"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
+      <c r="A48" s="40"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
     </row>
     <row r="49" ht="28.5" customHeight="1">
-      <c r="A49" s="39"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
+      <c r="A49" s="40"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
     </row>
     <row r="50" ht="28.5" customHeight="1">
-      <c r="B50" s="23"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="24"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
     </row>
     <row r="51" ht="28.5" customHeight="1">
-      <c r="B51" s="23"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
     </row>
     <row r="52" ht="28.5" customHeight="1"/>
     <row r="53" ht="28.5" customHeight="1"/>
@@ -2364,7 +2368,7 @@
       <c r="A3" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="41" t="s">
         <v>126</v>
       </c>
       <c r="C3" t="s">
@@ -2381,7 +2385,7 @@
       <c r="B4" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="42" t="s">
         <v>123</v>
       </c>
       <c r="D4" t="s">
@@ -2395,7 +2399,7 @@
       <c r="B5" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="42" t="s">
         <v>123</v>
       </c>
       <c r="D5" t="s">
@@ -2403,13 +2407,13 @@
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="41" t="s">
         <v>133</v>
       </c>
       <c r="B6" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="42" t="s">
         <v>123</v>
       </c>
       <c r="D6" t="s">
@@ -2417,13 +2421,13 @@
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="41" t="s">
         <v>136</v>
       </c>
       <c r="B7" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="42" t="s">
         <v>123</v>
       </c>
       <c r="D7" t="s">
@@ -3436,228 +3440,228 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="44" width="38.421875"/>
-    <col customWidth="1" min="3" max="3" width="55.421875"/>
-    <col customWidth="1" min="4" max="4" width="75.8515625"/>
+    <col customWidth="1" min="2" max="2" style="43" width="38.421875"/>
+    <col customWidth="1" min="3" max="3" style="43" width="49.00390625"/>
+    <col customWidth="1" min="4" max="4" style="43" width="92.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
       <c r="A1" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="27" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="44" customFormat="1" ht="28.5">
-      <c r="A2" s="45"/>
-      <c r="B2" s="46" t="s">
+    <row r="2" s="43" customFormat="1" ht="28.5">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="46" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="46" t="s">
+    <row r="3" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A3" s="44"/>
+      <c r="B3" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="47"/>
-    </row>
-    <row r="4" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="45"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-    </row>
-    <row r="5" s="44" customFormat="1" ht="57">
-      <c r="A5" s="45"/>
-      <c r="B5" s="47" t="s">
+      <c r="D3" s="46"/>
+    </row>
+    <row r="4" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A4" s="44"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+    </row>
+    <row r="5" s="43" customFormat="1" ht="42.75">
+      <c r="A5" s="44"/>
+      <c r="B5" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="47">
+        <v>2055</v>
+      </c>
+      <c r="D5" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="47" t="s">
+    </row>
+    <row r="6" s="43" customFormat="1" ht="36" customHeight="1">
+      <c r="A6" s="44"/>
+      <c r="B6" s="46" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="6" s="44" customFormat="1" ht="36" customHeight="1">
-      <c r="A6" s="45"/>
-      <c r="B6" s="47" t="s">
+      <c r="C6" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="D6" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="G6" s="43"/>
+    </row>
+    <row r="7" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A7" s="44"/>
+      <c r="B7" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="44"/>
-    </row>
-    <row r="7" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="45"/>
-      <c r="B7" s="46" t="s">
+      <c r="C7" s="49" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="D7" s="46" t="s">
         <v>152</v>
       </c>
-      <c r="D7" s="47" t="s">
+    </row>
+    <row r="8" s="43" customFormat="1" ht="28.5">
+      <c r="A8" s="44"/>
+      <c r="B8" s="45" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="8" s="44" customFormat="1" ht="28.5">
-      <c r="A8" s="45"/>
-      <c r="B8" s="46" t="s">
+      <c r="C8" s="46" t="s">
         <v>154</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="D8" s="46" t="s">
         <v>155</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="49"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
     </row>
     <row r="10" ht="41.25" customHeight="1">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="52" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="C10" s="53" t="s">
         <v>158</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="D10" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="D10" s="29" t="s">
+    </row>
+    <row r="11" ht="39.75" customHeight="1">
+      <c r="A11" s="54"/>
+      <c r="B11" s="29" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="52"/>
-      <c r="B11" s="28" t="s">
+      <c r="C11" s="30">
+        <v>60000</v>
+      </c>
+      <c r="D11" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="C11" s="29">
-        <v>60000</v>
-      </c>
-      <c r="D11" s="29" t="s">
+    </row>
+    <row r="12" ht="36.75" customHeight="1">
+      <c r="A12" s="54"/>
+      <c r="B12" s="29" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="52"/>
-      <c r="B12" s="28" t="s">
+      <c r="C12" s="30">
+        <v>3000</v>
+      </c>
+      <c r="D12" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="C12" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D12" s="29" t="s">
+    </row>
+    <row r="13" ht="36.75" customHeight="1">
+      <c r="A13" s="54"/>
+      <c r="B13" s="29" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="13" ht="36.75" customHeight="1">
-      <c r="A13" s="52"/>
-      <c r="B13" s="28" t="s">
+      <c r="C13" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="D13" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="D13" s="29" t="s">
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="54"/>
+      <c r="B14" s="29" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="52"/>
-      <c r="B14" s="28" t="s">
+      <c r="C14" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="D14" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="D14" s="29" t="s">
+    </row>
+    <row r="15" ht="63.600000000000001" customHeight="1">
+      <c r="A15" s="54"/>
+      <c r="B15" s="29" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="15" ht="63.600000000000001" customHeight="1">
-      <c r="A15" s="52"/>
-      <c r="B15" s="28" t="s">
+      <c r="C15" s="56" t="s">
         <v>171</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="D15" s="30" t="s">
         <v>172</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="57" t="s">
+        <v>173</v>
+      </c>
+      <c r="B17" s="58" t="s">
         <v>174</v>
       </c>
-      <c r="B17" s="55" t="s">
+      <c r="C17" s="59" t="s">
         <v>175</v>
       </c>
-      <c r="C17" s="56" t="s">
+      <c r="D17" s="60" t="s">
         <v>176</v>
       </c>
-      <c r="D17" s="57" t="s">
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="57"/>
+      <c r="B18" s="58" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="54"/>
-      <c r="B18" s="55" t="s">
+      <c r="C18" s="59">
+        <v>5000</v>
+      </c>
+      <c r="D18" s="59" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="56">
-        <v>5000</v>
-      </c>
-      <c r="D18" s="56" t="s">
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="57"/>
+      <c r="B19" s="58" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="54"/>
-      <c r="B19" s="55" t="s">
+      <c r="C19" s="59" t="s">
+        <v>165</v>
+      </c>
+      <c r="D19" s="59" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="56" t="s">
-        <v>166</v>
-      </c>
-      <c r="D19" s="56" t="s">
-        <v>181</v>
-      </c>
     </row>
     <row r="20" ht="28.199999999999999" customHeight="1">
-      <c r="B20" s="44"/>
+      <c r="B20" s="43"/>
     </row>
     <row r="21" ht="28.199999999999999" customHeight="1"/>
     <row r="22" ht="28.199999999999999" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>Name</t>
   </si>
@@ -614,16 +614,10 @@
     <t>getExpenses_dateStart</t>
   </si>
   <si>
-    <t>01/01/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Inicio do range de datas que abrange a data de vencimento das despesas que irão ser importadas. Deve estar no formato "dd/MM/yyyy" e só deve existir caso o getExpenses_dateEnd existir também.</t>
   </si>
   <si>
     <t>getExpenses_dateEnd</t>
-  </si>
-  <si>
-    <t>01/02/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Fim do range de datas que abrange a data de vencimento das despesas que irão ser importadas. Deve estar no formato "dd/MM/yyyy" e só deve existir caso o getExpenses_dateStart existir também. Deve ser posterior ao getExpenses_dateStart</t>
@@ -802,7 +796,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="58">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -842,7 +836,6 @@
     <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -923,9 +916,6 @@
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -943,9 +933,6 @@
     </xf>
     <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1591,7 +1578,7 @@
       <c r="B10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="15" t="s">
@@ -1603,7 +1590,7 @@
       <c r="B11" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="16" t="s">
@@ -1615,7 +1602,7 @@
       <c r="B12" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="16" t="s">
@@ -1644,21 +1631,21 @@
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="14"/>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="22" t="s">
+      <c r="C15" s="20"/>
+      <c r="D15" s="21" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" ht="34.799999999999997" customHeight="1">
       <c r="A16" s="14"/>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="19" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="15"/>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="21" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1669,7 +1656,7 @@
       <c r="D17" s="5"/>
     </row>
     <row r="18" ht="46.799999999999997" customHeight="1">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="22" t="s">
         <v>28</v>
       </c>
       <c r="B18" s="12" t="s">
@@ -1683,7 +1670,7 @@
       </c>
     </row>
     <row r="19" ht="46.799999999999997" customHeight="1">
-      <c r="A19" s="23"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="15" t="s">
         <v>32</v>
       </c>
@@ -1693,11 +1680,11 @@
       <c r="D19" s="15"/>
     </row>
     <row r="20" ht="43.200000000000003" customHeight="1">
-      <c r="A20" s="23"/>
+      <c r="A20" s="22"/>
       <c r="B20" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D20" s="16"/>
@@ -1756,20 +1743,20 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8.00390625"/>
-    <col customWidth="1" min="2" max="2" style="24" width="53.8515625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="25" width="63.11328125"/>
-    <col customWidth="1" min="4" max="4" style="25" width="84.140625"/>
+    <col customWidth="1" min="2" max="2" style="23" width="53.8515625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="24" width="63.11328125"/>
+    <col customWidth="1" min="4" max="4" style="24" width="84.140625"/>
     <col customWidth="1" min="5" max="27" width="8.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2"/>
@@ -1797,79 +1784,79 @@
       <c r="AA1" s="2"/>
     </row>
     <row r="2" ht="28.5">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="30">
+      <c r="C2" s="29">
         <v>1</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="29" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" ht="28.5">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29" t="s">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3" s="29">
         <v>3</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="29" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29" t="s">
+      <c r="A4" s="27"/>
+      <c r="B4" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="29" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" ht="28.5">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29" t="s">
+      <c r="A5" s="27"/>
+      <c r="B5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>15</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="29" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" ht="28.5">
-      <c r="A6" s="28"/>
-      <c r="B6" s="29" t="s">
+      <c r="A6" s="27"/>
+      <c r="B6" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>2</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="29" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" s="31" customFormat="1" ht="17.399999999999999" customHeight="1">
+    <row r="7" s="30" customFormat="1" ht="17.399999999999999" customHeight="1">
       <c r="A7" s="5"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
     </row>
     <row r="8" ht="39.75" customHeight="1">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="33" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="34">
         <v>30000</v>
       </c>
       <c r="D8" s="16" t="s">
@@ -1877,11 +1864,11 @@
       </c>
     </row>
     <row r="9" ht="39.75" customHeight="1">
-      <c r="A9" s="36"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="34">
         <v>20000</v>
       </c>
       <c r="D9" s="16" t="s">
@@ -1889,11 +1876,11 @@
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="36"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="34">
         <v>0</v>
       </c>
       <c r="D10" s="16" t="s">
@@ -1901,11 +1888,11 @@
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="36"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="34">
         <v>0</v>
       </c>
       <c r="D11" s="16" t="s">
@@ -1914,367 +1901,367 @@
     </row>
     <row r="12" ht="17.399999999999999" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
     </row>
     <row r="13" ht="22.800000000000001" customHeight="1">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="29" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="14" ht="28.199999999999999" customHeight="1">
-      <c r="A14" s="37"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="36"/>
+      <c r="B14" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="30"/>
+      <c r="D14" s="29"/>
     </row>
     <row r="15" ht="28.199999999999999" customHeight="1">
-      <c r="A15" s="37"/>
-      <c r="B15" s="29" t="s">
+      <c r="A15" s="36"/>
+      <c r="B15" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="30"/>
+      <c r="D15" s="29"/>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="37"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
+      <c r="A16" s="36"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="37"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
     </row>
     <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="37"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
+      <c r="A18" s="36"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
     </row>
     <row r="19" ht="17.399999999999999" customHeight="1">
-      <c r="A19" s="38"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="29" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="39"/>
-      <c r="B21" s="29" t="s">
+      <c r="A21" s="38"/>
+      <c r="B21" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="29" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="22" ht="33.75" customHeight="1">
-      <c r="A22" s="39"/>
-      <c r="B22" s="30" t="s">
+      <c r="A22" s="38"/>
+      <c r="B22" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="30"/>
+      <c r="D22" s="29"/>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="39"/>
-      <c r="B23" s="29" t="s">
+      <c r="A23" s="38"/>
+      <c r="B23" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C23" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="30"/>
+      <c r="D23" s="29"/>
     </row>
     <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="39"/>
-      <c r="B24" s="29" t="s">
+      <c r="A24" s="38"/>
+      <c r="B24" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="30"/>
+      <c r="D24" s="29"/>
     </row>
     <row r="25" ht="27" customHeight="1">
-      <c r="A25" s="39"/>
-      <c r="B25" s="29" t="s">
+      <c r="A25" s="38"/>
+      <c r="B25" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="30"/>
+      <c r="D25" s="29"/>
     </row>
     <row r="26" ht="28.5">
-      <c r="A26" s="39"/>
-      <c r="B26" s="29" t="s">
+      <c r="A26" s="38"/>
+      <c r="B26" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="29" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="27" ht="28.5">
-      <c r="A27" s="39"/>
-      <c r="B27" s="29" t="s">
+      <c r="A27" s="38"/>
+      <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C27" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="29" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="28" ht="42.75">
-      <c r="A28" s="39"/>
-      <c r="B28" s="29" t="s">
+      <c r="A28" s="38"/>
+      <c r="B28" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="D28" s="30" t="s">
+      <c r="D28" s="29" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="29" ht="28.800000000000001" customHeight="1">
-      <c r="A29" s="39"/>
-      <c r="B29" s="29" t="s">
+      <c r="A29" s="38"/>
+      <c r="B29" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="C29" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="30"/>
+      <c r="D29" s="29"/>
     </row>
     <row r="30" ht="27.600000000000001" customHeight="1">
-      <c r="A30" s="39"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
+      <c r="A30" s="38"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
     </row>
     <row r="31" ht="26.399999999999999" customHeight="1">
-      <c r="A31" s="39"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
+      <c r="A31" s="38"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
     </row>
     <row r="32" ht="27" customHeight="1">
-      <c r="A32" s="39"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
+      <c r="A32" s="38"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
     </row>
     <row r="33" ht="17.399999999999999" customHeight="1">
       <c r="A33" s="5"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
     </row>
     <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="40" t="s">
+      <c r="A34" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="30" t="s">
+      <c r="C34" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="29" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="35" ht="27.75" customHeight="1">
-      <c r="A35" s="40"/>
-      <c r="B35" s="29" t="s">
+      <c r="A35" s="39"/>
+      <c r="B35" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="30" t="s">
+      <c r="D35" s="29" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="36" ht="28.5">
-      <c r="A36" s="40"/>
-      <c r="B36" s="29" t="s">
+      <c r="A36" s="39"/>
+      <c r="B36" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C36" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="30"/>
+      <c r="D36" s="29"/>
     </row>
     <row r="37" ht="28.5">
-      <c r="A37" s="40"/>
-      <c r="B37" s="29" t="s">
+      <c r="A37" s="39"/>
+      <c r="B37" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="30" t="s">
+      <c r="C37" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="30"/>
+      <c r="D37" s="29"/>
     </row>
     <row r="38" ht="27.75" customHeight="1">
-      <c r="A38" s="40"/>
-      <c r="B38" s="29" t="s">
+      <c r="A38" s="39"/>
+      <c r="B38" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="D38" s="30" t="s">
+      <c r="D38" s="29" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="39" ht="31.199999999999999" customHeight="1">
-      <c r="A39" s="40"/>
-      <c r="B39" s="29" t="s">
+      <c r="A39" s="39"/>
+      <c r="B39" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="D39" s="30"/>
+      <c r="D39" s="29"/>
     </row>
     <row r="40" ht="28.800000000000001" customHeight="1">
-      <c r="A40" s="40"/>
-      <c r="B40" s="29" t="s">
+      <c r="A40" s="39"/>
+      <c r="B40" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="30" t="s">
+      <c r="C40" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="30" t="s">
+      <c r="D40" s="29" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="41" ht="29.399999999999999" customHeight="1">
-      <c r="A41" s="40"/>
-      <c r="B41" s="29" t="s">
+      <c r="A41" s="39"/>
+      <c r="B41" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="C41" s="30" t="s">
+      <c r="C41" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="30" t="s">
+      <c r="D41" s="29" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="42" ht="42.75">
-      <c r="A42" s="40"/>
-      <c r="B42" s="29" t="s">
+      <c r="A42" s="39"/>
+      <c r="B42" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C42" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="D42" s="30" t="s">
+      <c r="D42" s="29" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="43" ht="28.800000000000001" customHeight="1">
-      <c r="A43" s="40"/>
-      <c r="B43" s="30" t="s">
+      <c r="A43" s="39"/>
+      <c r="B43" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="C43" s="30" t="s">
+      <c r="C43" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="D43" s="30"/>
+      <c r="D43" s="29"/>
     </row>
     <row r="44" ht="28.800000000000001" customHeight="1">
-      <c r="A44" s="40"/>
-      <c r="B44" s="29" t="s">
+      <c r="A44" s="39"/>
+      <c r="B44" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="C44" s="30" t="s">
+      <c r="C44" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="D44" s="30"/>
+      <c r="D44" s="29"/>
     </row>
     <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" s="40"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
+      <c r="A45" s="39"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
     </row>
     <row r="46" ht="28.5" customHeight="1">
-      <c r="A46" s="40"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
+      <c r="A46" s="39"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
     </row>
     <row r="47" ht="28.5" customHeight="1">
-      <c r="A47" s="40"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
+      <c r="A47" s="39"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
     </row>
     <row r="48" ht="28.5" customHeight="1">
-      <c r="A48" s="40"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
+      <c r="A48" s="39"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
     </row>
     <row r="49" ht="28.5" customHeight="1">
-      <c r="A49" s="40"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
+      <c r="A49" s="39"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
     </row>
     <row r="50" ht="28.5" customHeight="1">
-      <c r="B50" s="24"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="25"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
     </row>
     <row r="51" ht="28.5" customHeight="1">
-      <c r="B51" s="24"/>
-      <c r="C51" s="25"/>
-      <c r="D51" s="25"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
     </row>
     <row r="52" ht="28.5" customHeight="1"/>
     <row r="53" ht="28.5" customHeight="1"/>
@@ -2368,7 +2355,7 @@
       <c r="A3" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>126</v>
       </c>
       <c r="C3" t="s">
@@ -2385,7 +2372,7 @@
       <c r="B4" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="41" t="s">
         <v>123</v>
       </c>
       <c r="D4" t="s">
@@ -2399,7 +2386,7 @@
       <c r="B5" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="41" t="s">
         <v>123</v>
       </c>
       <c r="D5" t="s">
@@ -2407,13 +2394,13 @@
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="40" t="s">
         <v>133</v>
       </c>
       <c r="B6" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="41" t="s">
         <v>123</v>
       </c>
       <c r="D6" t="s">
@@ -2421,13 +2408,13 @@
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="40" t="s">
         <v>136</v>
       </c>
       <c r="B7" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="41" t="s">
         <v>123</v>
       </c>
       <c r="D7" t="s">
@@ -3440,228 +3427,224 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="43" width="38.421875"/>
-    <col customWidth="1" min="3" max="3" style="43" width="49.00390625"/>
-    <col customWidth="1" min="4" max="4" style="43" width="92.7109375"/>
+    <col customWidth="1" min="2" max="2" style="42" width="38.421875"/>
+    <col customWidth="1" min="3" max="3" style="42" width="49.00390625"/>
+    <col customWidth="1" min="4" max="4" style="42" width="92.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
       <c r="A1" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="43" customFormat="1" ht="28.5">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45" t="s">
+    <row r="2" s="42" customFormat="1" ht="28.5">
+      <c r="A2" s="43"/>
+      <c r="B2" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="45" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="44"/>
-      <c r="B3" s="45" t="s">
+    <row r="3" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A3" s="43"/>
+      <c r="B3" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="46"/>
-    </row>
-    <row r="4" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-    </row>
-    <row r="5" s="43" customFormat="1" ht="42.75">
-      <c r="A5" s="44"/>
-      <c r="B5" s="46" t="s">
+      <c r="D3" s="45"/>
+    </row>
+    <row r="4" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+    </row>
+    <row r="5" s="42" customFormat="1" ht="42.75">
+      <c r="A5" s="43"/>
+      <c r="B5" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="46">
         <v>2055</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="45" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="6" s="43" customFormat="1" ht="36" customHeight="1">
-      <c r="A6" s="44"/>
-      <c r="B6" s="46" t="s">
+    <row r="6" s="42" customFormat="1" ht="36" customHeight="1">
+      <c r="A6" s="43"/>
+      <c r="B6" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="43"/>
-    </row>
-    <row r="7" s="43" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="44"/>
-      <c r="B7" s="45" t="s">
+      <c r="G6" s="42"/>
+    </row>
+    <row r="7" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A7" s="43"/>
+      <c r="B7" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="45" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="8" s="43" customFormat="1" ht="28.5">
-      <c r="A8" s="44"/>
-      <c r="B8" s="45" t="s">
+    <row r="8" s="42" customFormat="1" ht="28.5">
+      <c r="A8" s="43"/>
+      <c r="B8" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="45" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
     </row>
     <row r="10" ht="41.25" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="29" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="54"/>
-      <c r="B11" s="29" t="s">
+      <c r="A11" s="52"/>
+      <c r="B11" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>60000</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="29" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="54"/>
-      <c r="B12" s="29" t="s">
+      <c r="A12" s="52"/>
+      <c r="B12" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="29">
         <v>3000</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="29" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="13" ht="36.75" customHeight="1">
-      <c r="A13" s="54"/>
-      <c r="B13" s="29" t="s">
+      <c r="A13" s="52"/>
+      <c r="B13" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="29" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="54"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="52"/>
+      <c r="B14" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="53"/>
+      <c r="D14" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="D14" s="30" t="s">
+    </row>
+    <row r="15" ht="63.600000000000001" customHeight="1">
+      <c r="A15" s="52"/>
+      <c r="B15" s="28" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="15" ht="63.600000000000001" customHeight="1">
-      <c r="A15" s="54"/>
-      <c r="B15" s="29" t="s">
+      <c r="C15" s="53"/>
+      <c r="D15" s="29" t="s">
         <v>170</v>
-      </c>
-      <c r="C15" s="56" t="s">
-        <v>171</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="57" t="s">
+      <c r="A17" s="54" t="s">
+        <v>171</v>
+      </c>
+      <c r="B17" s="55" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" s="56" t="s">
         <v>173</v>
       </c>
-      <c r="B17" s="58" t="s">
+      <c r="D17" s="57" t="s">
         <v>174</v>
       </c>
-      <c r="C17" s="59" t="s">
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="54"/>
+      <c r="B18" s="55" t="s">
         <v>175</v>
       </c>
-      <c r="D17" s="60" t="s">
+      <c r="C18" s="56">
+        <v>5000</v>
+      </c>
+      <c r="D18" s="56" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="57"/>
-      <c r="B18" s="58" t="s">
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="54"/>
+      <c r="B19" s="55" t="s">
         <v>177</v>
       </c>
-      <c r="C18" s="59">
-        <v>5000</v>
-      </c>
-      <c r="D18" s="59" t="s">
+      <c r="C19" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="D19" s="56" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="57"/>
-      <c r="B19" s="58" t="s">
-        <v>179</v>
-      </c>
-      <c r="C19" s="59" t="s">
-        <v>165</v>
-      </c>
-      <c r="D19" s="59" t="s">
-        <v>180</v>
-      </c>
-    </row>
     <row r="20" ht="28.199999999999999" customHeight="1">
-      <c r="B20" s="43"/>
+      <c r="B20" s="42"/>
     </row>
     <row r="21" ht="28.199999999999999" customHeight="1"/>
     <row r="22" ht="28.199999999999999" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -113,16 +113,10 @@
     <t>obligationDateStart</t>
   </si>
   <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data inicial do range de datas que deve abranger a data de vencimento da obrigação em questão, se não estiver definida nenhuma data nessa variável, o processo define o primeiro e o ultimo dia do mês como as datas de inicio e fim do range.</t>
   </si>
   <si>
     <t>obligationDateEnd</t>
-  </si>
-  <si>
-    <t>05/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Data final do range de datas que deve abranger a data de vencimento da obrigação em questão, se não estiver definida nenhuma data nessa variável, o processo define o primeiro e o ultimo dia do mês como as datas de inicio e fim do range.</t>
@@ -462,6 +456,12 @@
   </si>
   <si>
     <t xml:space="preserve">O relatorio de importações do Domínio não foi apresentado.</t>
+  </si>
+  <si>
+    <t>ExceptionMessage_QueryDominioDatesLimitsError</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houve um erro na consulta das datas de limite de importação no domínio. Data de fechamento, inicio e fim do periodo de trabalho.</t>
   </si>
   <si>
     <t>Asset</t>
@@ -796,7 +796,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -896,6 +896,12 @@
     </xf>
     <xf fontId="4" fillId="11" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
@@ -1590,39 +1596,35 @@
       <c r="B11" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="17"/>
+      <c r="D11" s="16" t="s">
         <v>17</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="12" ht="61.200000000000003" customHeight="1">
       <c r="A12" s="14"/>
       <c r="B12" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="16" t="s">
         <v>19</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" ht="28.800000000000001" customHeight="1">
       <c r="A13" s="14"/>
       <c r="B13" s="15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C13" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="15"/>
     </row>
     <row r="14" ht="28.800000000000001" customHeight="1">
       <c r="A14" s="14"/>
       <c r="B14" s="15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14" s="15" t="b">
         <v>0</v>
@@ -1632,21 +1634,21 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="14"/>
       <c r="B15" s="19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="34.799999999999997" customHeight="1">
       <c r="A16" s="14"/>
       <c r="B16" s="19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" ht="17.399999999999999" customHeight="1">
@@ -1657,35 +1659,35 @@
     </row>
     <row r="18" ht="46.799999999999997" customHeight="1">
       <c r="A18" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="D18" s="16" t="s">
         <v>29</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="19" ht="46.799999999999997" customHeight="1">
       <c r="A19" s="22"/>
       <c r="B19" s="15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D19" s="15"/>
     </row>
     <row r="20" ht="43.200000000000003" customHeight="1">
       <c r="A20" s="22"/>
       <c r="B20" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D20" s="16"/>
     </row>
@@ -1786,61 +1788,61 @@
     <row r="2" ht="28.5">
       <c r="A2" s="27"/>
       <c r="B2" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" s="29">
         <v>1</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" ht="28.5">
       <c r="A3" s="27"/>
       <c r="B3" s="28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C3" s="29">
         <v>3</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1">
       <c r="A4" s="27"/>
       <c r="B4" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="29" t="s">
         <v>40</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" ht="28.5">
       <c r="A5" s="27"/>
       <c r="B5" s="28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="29">
         <v>15</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" ht="28.5">
       <c r="A6" s="27"/>
       <c r="B6" s="28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C6" s="29">
         <v>2</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" s="30" customFormat="1" ht="17.399999999999999" customHeight="1">
@@ -1851,52 +1853,52 @@
     </row>
     <row r="8" ht="39.75" customHeight="1">
       <c r="A8" s="33" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C8" s="34">
         <v>30000</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" ht="39.75" customHeight="1">
       <c r="A9" s="35"/>
       <c r="B9" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" s="34">
         <v>20000</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" ht="39.75" customHeight="1">
       <c r="A10" s="35"/>
       <c r="B10" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" s="34">
         <v>0</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
       <c r="A11" s="35"/>
       <c r="B11" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C11" s="34">
         <v>0</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" ht="17.399999999999999" customHeight="1">
@@ -1907,35 +1909,35 @@
     </row>
     <row r="13" ht="22.800000000000001" customHeight="1">
       <c r="A13" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="D13" s="29" t="s">
         <v>57</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="14" ht="28.199999999999999" customHeight="1">
       <c r="A14" s="36"/>
       <c r="B14" s="28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D14" s="29"/>
     </row>
     <row r="15" ht="28.199999999999999" customHeight="1">
       <c r="A15" s="36"/>
       <c r="B15" s="28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D15" s="29"/>
     </row>
@@ -1965,113 +1967,113 @@
     </row>
     <row r="20" ht="27" customHeight="1">
       <c r="A20" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="D20" s="29" t="s">
         <v>65</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="21" ht="27" customHeight="1">
       <c r="A21" s="38"/>
       <c r="B21" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="29" t="s">
         <v>68</v>
-      </c>
-      <c r="C21" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="29" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="22" ht="33.75" customHeight="1">
       <c r="A22" s="38"/>
       <c r="B22" s="29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D22" s="29"/>
     </row>
     <row r="23" ht="27" customHeight="1">
       <c r="A23" s="38"/>
       <c r="B23" s="28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D23" s="29"/>
     </row>
     <row r="24" ht="27" customHeight="1">
       <c r="A24" s="38"/>
       <c r="B24" s="28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D24" s="29"/>
     </row>
     <row r="25" ht="27" customHeight="1">
       <c r="A25" s="38"/>
       <c r="B25" s="28" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D25" s="29"/>
     </row>
     <row r="26" ht="28.5">
       <c r="A26" s="38"/>
       <c r="B26" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="29" t="s">
         <v>79</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="27" ht="28.5">
       <c r="A27" s="38"/>
       <c r="B27" s="28" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" ht="42.75">
       <c r="A28" s="38"/>
       <c r="B28" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="29" t="s">
         <v>84</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="29" ht="28.800000000000001" customHeight="1">
       <c r="A29" s="38"/>
       <c r="B29" s="28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D29" s="29"/>
     </row>
@@ -2101,132 +2103,136 @@
     </row>
     <row r="34" ht="27.75" customHeight="1">
       <c r="A34" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="D34" s="29" t="s">
         <v>90</v>
-      </c>
-      <c r="C34" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D34" s="29" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="35" ht="27.75" customHeight="1">
       <c r="A35" s="39"/>
       <c r="B35" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="29" t="s">
         <v>93</v>
-      </c>
-      <c r="C35" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" s="29" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="36" ht="28.5">
       <c r="A36" s="39"/>
       <c r="B36" s="28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D36" s="29"/>
     </row>
     <row r="37" ht="28.5">
       <c r="A37" s="39"/>
       <c r="B37" s="28" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D37" s="29"/>
     </row>
     <row r="38" ht="27.75" customHeight="1">
       <c r="A38" s="39"/>
       <c r="B38" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" s="29" t="s">
         <v>100</v>
-      </c>
-      <c r="C38" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="D38" s="29" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="39" ht="31.199999999999999" customHeight="1">
       <c r="A39" s="39"/>
       <c r="B39" s="28" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D39" s="29"/>
     </row>
     <row r="40" ht="28.800000000000001" customHeight="1">
       <c r="A40" s="39"/>
       <c r="B40" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D40" s="29" t="s">
         <v>105</v>
-      </c>
-      <c r="C40" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" s="29" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="41" ht="29.399999999999999" customHeight="1">
       <c r="A41" s="39"/>
       <c r="B41" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D41" s="29" t="s">
         <v>108</v>
-      </c>
-      <c r="C41" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="D41" s="29" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="42" ht="42.75">
       <c r="A42" s="39"/>
       <c r="B42" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D42" s="29" t="s">
         <v>111</v>
-      </c>
-      <c r="C42" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="D42" s="29" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="43" ht="28.800000000000001" customHeight="1">
       <c r="A43" s="39"/>
       <c r="B43" s="29" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D43" s="29"/>
     </row>
     <row r="44" ht="28.800000000000001" customHeight="1">
       <c r="A44" s="39"/>
       <c r="B44" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" s="29"/>
+    </row>
+    <row r="45" ht="28.5">
+      <c r="A45" s="39"/>
+      <c r="B45" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C45" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="D44" s="29"/>
-    </row>
-    <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" s="39"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="29"/>
       <c r="D45" s="29"/>
     </row>
     <row r="46" ht="28.5" customHeight="1">
@@ -2355,7 +2361,7 @@
       <c r="A3" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="42" t="s">
         <v>126</v>
       </c>
       <c r="C3" t="s">
@@ -2372,7 +2378,7 @@
       <c r="B4" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="43" t="s">
         <v>123</v>
       </c>
       <c r="D4" t="s">
@@ -2386,7 +2392,7 @@
       <c r="B5" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="43" t="s">
         <v>123</v>
       </c>
       <c r="D5" t="s">
@@ -2394,13 +2400,13 @@
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="42" t="s">
         <v>133</v>
       </c>
       <c r="B6" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="43" t="s">
         <v>123</v>
       </c>
       <c r="D6" t="s">
@@ -2408,13 +2414,13 @@
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="42" t="s">
         <v>136</v>
       </c>
       <c r="B7" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="43" t="s">
         <v>123</v>
       </c>
       <c r="D7" t="s">
@@ -3427,9 +3433,9 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="5.57421875"/>
-    <col customWidth="1" min="2" max="2" style="42" width="38.421875"/>
-    <col customWidth="1" min="3" max="3" style="42" width="49.00390625"/>
-    <col customWidth="1" min="4" max="4" style="42" width="92.7109375"/>
+    <col customWidth="1" min="2" max="2" style="44" width="38.421875"/>
+    <col customWidth="1" min="3" max="3" style="44" width="49.00390625"/>
+    <col customWidth="1" min="4" max="4" style="44" width="92.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75">
@@ -3446,97 +3452,97 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="42" customFormat="1" ht="28.5">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44" t="s">
+    <row r="2" s="44" customFormat="1" ht="28.5">
+      <c r="A2" s="45"/>
+      <c r="B2" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="47" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A3" s="43"/>
-      <c r="B3" s="44" t="s">
+    <row r="3" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A3" s="45"/>
+      <c r="B3" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="45"/>
-    </row>
-    <row r="4" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A4" s="43"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-    </row>
-    <row r="5" s="42" customFormat="1" ht="42.75">
-      <c r="A5" s="43"/>
-      <c r="B5" s="45" t="s">
+      <c r="D3" s="47"/>
+    </row>
+    <row r="4" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A4" s="45"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+    </row>
+    <row r="5" s="44" customFormat="1" ht="42.75">
+      <c r="A5" s="45"/>
+      <c r="B5" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="46">
+      <c r="C5" s="48">
         <v>2055</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="47" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="6" s="42" customFormat="1" ht="36" customHeight="1">
-      <c r="A6" s="43"/>
-      <c r="B6" s="45" t="s">
+    <row r="6" s="44" customFormat="1" ht="36" customHeight="1">
+      <c r="A6" s="45"/>
+      <c r="B6" s="47" t="s">
         <v>147</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="42"/>
-    </row>
-    <row r="7" s="42" customFormat="1" ht="21.600000000000001" customHeight="1">
-      <c r="A7" s="43"/>
-      <c r="B7" s="44" t="s">
+      <c r="G6" s="44"/>
+    </row>
+    <row r="7" s="44" customFormat="1" ht="21.600000000000001" customHeight="1">
+      <c r="A7" s="45"/>
+      <c r="B7" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="49" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="45" t="s">
+      <c r="D7" s="47" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="8" s="42" customFormat="1" ht="28.5">
-      <c r="A8" s="43"/>
-      <c r="B8" s="44" t="s">
+    <row r="8" s="44" customFormat="1" ht="28.5">
+      <c r="A8" s="45"/>
+      <c r="B8" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="47" t="s">
         <v>154</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="D8" s="47" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
     </row>
     <row r="10" ht="41.25" customHeight="1">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="52" t="s">
         <v>156</v>
       </c>
       <c r="B10" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="53" t="s">
         <v>158</v>
       </c>
       <c r="D10" s="29" t="s">
@@ -3544,7 +3550,7 @@
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="52"/>
+      <c r="A11" s="54"/>
       <c r="B11" s="28" t="s">
         <v>160</v>
       </c>
@@ -3556,7 +3562,7 @@
       </c>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="52"/>
+      <c r="A12" s="54"/>
       <c r="B12" s="28" t="s">
         <v>162</v>
       </c>
@@ -3568,7 +3574,7 @@
       </c>
     </row>
     <row r="13" ht="36.75" customHeight="1">
-      <c r="A13" s="52"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="28" t="s">
         <v>164</v>
       </c>
@@ -3580,71 +3586,71 @@
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="52"/>
+      <c r="A14" s="54"/>
       <c r="B14" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="C14" s="53"/>
+      <c r="C14" s="55"/>
       <c r="D14" s="29" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="15" ht="63.600000000000001" customHeight="1">
-      <c r="A15" s="52"/>
+      <c r="A15" s="54"/>
       <c r="B15" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="53"/>
+      <c r="C15" s="55"/>
       <c r="D15" s="29" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="56" t="s">
         <v>171</v>
       </c>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="57" t="s">
         <v>172</v>
       </c>
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="58" t="s">
         <v>173</v>
       </c>
-      <c r="D17" s="57" t="s">
+      <c r="D17" s="59" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="54"/>
-      <c r="B18" s="55" t="s">
+      <c r="A18" s="56"/>
+      <c r="B18" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="C18" s="56">
+      <c r="C18" s="58">
         <v>5000</v>
       </c>
-      <c r="D18" s="56" t="s">
+      <c r="D18" s="58" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="54"/>
-      <c r="B19" s="55" t="s">
+      <c r="A19" s="56"/>
+      <c r="B19" s="57" t="s">
         <v>177</v>
       </c>
-      <c r="C19" s="56" t="s">
+      <c r="C19" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="D19" s="56" t="s">
+      <c r="D19" s="58" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="20" ht="28.199999999999999" customHeight="1">
-      <c r="B20" s="42"/>
+      <c r="B20" s="44"/>
     </row>
     <row r="21" ht="28.199999999999999" customHeight="1"/>
     <row r="22" ht="28.199999999999999" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robot\Documents\UiPath\LancamentoDeDespesas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28D3E922-682E-4D04-8C0D-3F373FECF9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB35F1E-3E83-42C8-A488-137E1869678E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="ProcessVariables" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -373,9 +372,6 @@
     <t>LogMessage_EnableExpensesIntegration</t>
   </si>
   <si>
-    <t>Opção 'enableExpensesIntegration' está desabilitada, o processo não irá integrar as obrigações.</t>
-  </si>
-  <si>
     <t>EXCEPTION LOG MESSAGES</t>
   </si>
   <si>
@@ -650,13 +646,16 @@
   </si>
   <si>
     <t>unavailable</t>
+  </si>
+  <si>
+    <t>Opção 'enableExpensesIntegration' está desabilitada, o processo não irá integrar as despesas.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -690,6 +689,12 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="13">
@@ -802,7 +807,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -911,6 +916,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1179,17 +1187,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA20"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" customWidth="1"/>
-    <col min="2" max="2" width="45.109375" customWidth="1"/>
-    <col min="3" max="3" width="60.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="84.5546875" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="45.140625" customWidth="1"/>
+    <col min="3" max="3" width="60.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="84.5703125" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="27" width="8.6640625" customWidth="1"/>
+    <col min="6" max="27" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1223,7 +1231,7 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>3</v>
       </c>
@@ -1234,14 +1242,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6"/>
       <c r="D3" s="7"/>
     </row>
-    <row r="4" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="49" t="s">
+    <row r="4" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -1254,8 +1262,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="49"/>
+    <row r="5" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="50"/>
       <c r="B5" s="11" t="s">
         <v>9</v>
       </c>
@@ -1264,26 +1272,26 @@
       </c>
       <c r="D5" s="10"/>
     </row>
-    <row r="6" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="49"/>
+    <row r="6" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="50"/>
       <c r="B6" s="11"/>
       <c r="C6" s="12"/>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="49"/>
+    <row r="7" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="50"/>
       <c r="B7" s="11"/>
       <c r="C7" s="12"/>
       <c r="D7" s="10"/>
     </row>
-    <row r="8" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
       <c r="D8" s="7"/>
     </row>
-    <row r="9" spans="1:27" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="50" t="s">
+    <row r="9" spans="1:27" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="51" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="11" t="s">
@@ -1294,8 +1302,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="50"/>
+    <row r="10" spans="1:27" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="51"/>
       <c r="B10" s="13" t="s">
         <v>13</v>
       </c>
@@ -1306,8 +1314,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="50"/>
+    <row r="11" spans="1:27" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="51"/>
       <c r="B11" s="13" t="s">
         <v>16</v>
       </c>
@@ -1316,8 +1324,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="50"/>
+    <row r="12" spans="1:27" ht="61.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="51"/>
       <c r="B12" s="13" t="s">
         <v>18</v>
       </c>
@@ -1326,8 +1334,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="50"/>
+    <row r="13" spans="1:27" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="51"/>
       <c r="B13" s="13" t="s">
         <v>20</v>
       </c>
@@ -1336,8 +1344,8 @@
       </c>
       <c r="D13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="50"/>
+    <row r="14" spans="1:27" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="51"/>
       <c r="B14" s="13" t="s">
         <v>21</v>
       </c>
@@ -1346,8 +1354,8 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="50"/>
+    <row r="15" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="51"/>
       <c r="B15" s="17" t="s">
         <v>22</v>
       </c>
@@ -1356,24 +1364,24 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="50"/>
+    <row r="16" spans="1:27" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="51"/>
       <c r="B16" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="13"/>
+      <c r="C16" s="43"/>
       <c r="D16" s="19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
       <c r="D17" s="5"/>
     </row>
-    <row r="18" spans="1:4" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="51" t="s">
+    <row r="18" spans="1:4" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="52" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -1386,8 +1394,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="51"/>
+    <row r="19" spans="1:4" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="52"/>
       <c r="B19" s="13" t="s">
         <v>30</v>
       </c>
@@ -1396,8 +1404,8 @@
       </c>
       <c r="D19" s="13"/>
     </row>
-    <row r="20" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="51"/>
+    <row r="20" spans="1:4" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="52"/>
       <c r="B20" s="13" t="s">
         <v>32</v>
       </c>
@@ -1423,16 +1431,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AA64"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="53.88671875" style="20" customWidth="1"/>
-    <col min="3" max="3" width="63.109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="84.109375" style="21" customWidth="1"/>
-    <col min="5" max="27" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="53.85546875" style="20" customWidth="1"/>
+    <col min="3" max="3" width="63.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="84.140625" style="21" customWidth="1"/>
+    <col min="5" max="27" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1466,8 +1474,8 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
     </row>
-    <row r="2" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="43"/>
+    <row r="2" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="44"/>
       <c r="B2" s="24" t="s">
         <v>34</v>
       </c>
@@ -1478,8 +1486,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="43"/>
+    <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="44"/>
       <c r="B3" s="24" t="s">
         <v>36</v>
       </c>
@@ -1490,8 +1498,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="43"/>
+    <row r="4" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="44"/>
       <c r="B4" s="24" t="s">
         <v>38</v>
       </c>
@@ -1502,8 +1510,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="43"/>
+    <row r="5" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="44"/>
       <c r="B5" s="24" t="s">
         <v>41</v>
       </c>
@@ -1514,8 +1522,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="43"/>
+    <row r="6" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="44"/>
       <c r="B6" s="24" t="s">
         <v>43</v>
       </c>
@@ -1526,14 +1534,14 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:27" s="26" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" s="26" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="27"/>
       <c r="C7" s="28"/>
       <c r="D7" s="28"/>
     </row>
-    <row r="8" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="44" t="s">
+    <row r="8" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="45" t="s">
         <v>45</v>
       </c>
       <c r="B8" s="13" t="s">
@@ -1546,8 +1554,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="45"/>
+    <row r="9" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="46"/>
       <c r="B9" s="13" t="s">
         <v>48</v>
       </c>
@@ -1558,8 +1566,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
+    <row r="10" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="46"/>
       <c r="B10" s="13" t="s">
         <v>50</v>
       </c>
@@ -1570,8 +1578,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="45"/>
+    <row r="11" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="46"/>
       <c r="B11" s="13" t="s">
         <v>52</v>
       </c>
@@ -1582,14 +1590,14 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="27"/>
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
     </row>
-    <row r="13" spans="1:27" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="46" t="s">
+    <row r="13" spans="1:27" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="47" t="s">
         <v>54</v>
       </c>
       <c r="B13" s="24" t="s">
@@ -1602,8 +1610,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="46"/>
+    <row r="14" spans="1:27" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="47"/>
       <c r="B14" s="24" t="s">
         <v>58</v>
       </c>
@@ -1612,8 +1620,8 @@
       </c>
       <c r="D14" s="25"/>
     </row>
-    <row r="15" spans="1:27" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="46"/>
+    <row r="15" spans="1:27" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="47"/>
       <c r="B15" s="24" t="s">
         <v>60</v>
       </c>
@@ -1622,32 +1630,32 @@
       </c>
       <c r="D15" s="25"/>
     </row>
-    <row r="16" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="46"/>
+    <row r="16" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="47"/>
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
     </row>
-    <row r="17" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="46"/>
+    <row r="17" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="47"/>
       <c r="B17" s="24"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
     </row>
-    <row r="18" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="46"/>
+    <row r="18" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="47"/>
       <c r="B18" s="24"/>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
     </row>
-    <row r="19" spans="1:4" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="30"/>
       <c r="B19" s="27"/>
       <c r="C19" s="28"/>
       <c r="D19" s="28"/>
     </row>
-    <row r="20" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="47" t="s">
+    <row r="20" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="48" t="s">
         <v>62</v>
       </c>
       <c r="B20" s="24" t="s">
@@ -1660,8 +1668,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="47"/>
+    <row r="21" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="48"/>
       <c r="B21" s="24" t="s">
         <v>66</v>
       </c>
@@ -1672,8 +1680,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47"/>
+    <row r="22" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
       <c r="B22" s="25" t="s">
         <v>69</v>
       </c>
@@ -1682,8 +1690,8 @@
       </c>
       <c r="D22" s="25"/>
     </row>
-    <row r="23" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="47"/>
+    <row r="23" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="48"/>
       <c r="B23" s="24" t="s">
         <v>71</v>
       </c>
@@ -1692,8 +1700,8 @@
       </c>
       <c r="D23" s="25"/>
     </row>
-    <row r="24" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="47"/>
+    <row r="24" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="48"/>
       <c r="B24" s="24" t="s">
         <v>73</v>
       </c>
@@ -1702,8 +1710,8 @@
       </c>
       <c r="D24" s="25"/>
     </row>
-    <row r="25" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="47"/>
+    <row r="25" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="48"/>
       <c r="B25" s="24" t="s">
         <v>75</v>
       </c>
@@ -1712,8 +1720,8 @@
       </c>
       <c r="D25" s="25"/>
     </row>
-    <row r="26" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="47"/>
+    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="48"/>
       <c r="B26" s="24" t="s">
         <v>77</v>
       </c>
@@ -1724,8 +1732,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="47"/>
+    <row r="27" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
       <c r="B27" s="24" t="s">
         <v>80</v>
       </c>
@@ -1736,8 +1744,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="47"/>
+    <row r="28" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="48"/>
       <c r="B28" s="24" t="s">
         <v>82</v>
       </c>
@@ -1748,213 +1756,213 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="47"/>
+    <row r="29" spans="1:4" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="48"/>
       <c r="B29" s="24" t="s">
         <v>85</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="D29" s="25"/>
     </row>
-    <row r="30" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="47"/>
+    <row r="30" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="48"/>
       <c r="B30" s="24"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
     </row>
-    <row r="31" spans="1:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="47"/>
+    <row r="31" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
       <c r="B31" s="24"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
     </row>
-    <row r="32" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="47"/>
+    <row r="32" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="48"/>
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
     </row>
-    <row r="33" spans="1:4" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="27"/>
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
     </row>
-    <row r="34" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="48" t="s">
+    <row r="34" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="C34" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="D34" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="25" t="s">
+    </row>
+    <row r="35" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="49"/>
+      <c r="B35" s="24" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="48"/>
-      <c r="B35" s="24" t="s">
+      <c r="C35" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="D35" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="25" t="s">
+    </row>
+    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="49"/>
+      <c r="B36" s="24" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
-      <c r="B36" s="24" t="s">
+      <c r="C36" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="D36" s="25"/>
+    </row>
+    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="49"/>
+      <c r="B37" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="25"/>
-    </row>
-    <row r="37" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="48"/>
-      <c r="B37" s="24" t="s">
+      <c r="C37" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="25" t="s">
+      <c r="D37" s="25"/>
+    </row>
+    <row r="38" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="49"/>
+      <c r="B38" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="D37" s="25"/>
-    </row>
-    <row r="38" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48"/>
-      <c r="B38" s="24" t="s">
+      <c r="C38" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="D38" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="D38" s="25" t="s">
+    </row>
+    <row r="39" spans="1:4" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="49"/>
+      <c r="B39" s="24" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="48"/>
-      <c r="B39" s="24" t="s">
+      <c r="C39" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="D39" s="25"/>
+    </row>
+    <row r="40" spans="1:4" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="49"/>
+      <c r="B40" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="D39" s="25"/>
-    </row>
-    <row r="40" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48"/>
-      <c r="B40" s="24" t="s">
+      <c r="C40" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="D40" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="25" t="s">
+    </row>
+    <row r="41" spans="1:4" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="49"/>
+      <c r="B41" s="24" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="48"/>
-      <c r="B41" s="24" t="s">
+      <c r="C41" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="D41" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="D41" s="25" t="s">
+    </row>
+    <row r="42" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="49"/>
+      <c r="B42" s="24" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="48"/>
-      <c r="B42" s="24" t="s">
+      <c r="C42" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="D42" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="D42" s="25" t="s">
+    </row>
+    <row r="43" spans="1:4" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="49"/>
+      <c r="B43" s="25" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="48"/>
-      <c r="B43" s="25" t="s">
+      <c r="C43" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="C43" s="25" t="s">
+      <c r="D43" s="25"/>
+    </row>
+    <row r="44" spans="1:4" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="49"/>
+      <c r="B44" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="D43" s="25"/>
-    </row>
-    <row r="44" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="48"/>
-      <c r="B44" s="24" t="s">
+      <c r="C44" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="25" t="s">
+      <c r="D44" s="25"/>
+    </row>
+    <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="49"/>
+      <c r="B45" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="D44" s="25"/>
-    </row>
-    <row r="45" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="48"/>
-      <c r="B45" s="24" t="s">
+      <c r="C45" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="C45" s="25" t="s">
-        <v>117</v>
-      </c>
       <c r="D45" s="25"/>
     </row>
-    <row r="46" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="48"/>
+    <row r="46" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="49"/>
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
     </row>
-    <row r="47" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="48"/>
+    <row r="47" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="49"/>
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
     </row>
-    <row r="48" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="48"/>
+    <row r="48" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="49"/>
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
     </row>
-    <row r="49" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="48"/>
+    <row r="49" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="49"/>
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
     </row>
-    <row r="50" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="53" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="54" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:A6"/>
@@ -1971,26 +1979,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.88671875" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" customWidth="1"/>
-    <col min="3" max="3" width="60.33203125" customWidth="1"/>
-    <col min="4" max="26" width="65.44140625" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="60.28515625" customWidth="1"/>
+    <col min="4" max="26" width="65.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2015,1083 +2023,1083 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" t="s">
         <v>121</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>122</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>123</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>125</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
         <v>126</v>
       </c>
-      <c r="C3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" t="s">
         <v>128</v>
       </c>
-      <c r="B4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>130</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" t="s">
         <v>131</v>
       </c>
-      <c r="C5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>133</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" t="s">
         <v>134</v>
       </c>
-      <c r="C6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" t="s">
+    </row>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>136</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" t="s">
         <v>137</v>
       </c>
-      <c r="C7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    </row>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3101,17 +3109,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D107"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" customWidth="1"/>
-    <col min="2" max="2" width="38.44140625" style="31" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" style="31" customWidth="1"/>
     <col min="3" max="3" width="49" style="31" customWidth="1"/>
-    <col min="4" max="4" width="92.6640625" style="31" customWidth="1"/>
+    <col min="4" max="4" width="92.7109375" style="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>0</v>
@@ -3123,290 +3131,290 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="31" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="52"/>
+    <row r="2" spans="1:4" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="53"/>
       <c r="B2" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="D2" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="D2" s="33" t="s">
+    </row>
+    <row r="3" spans="1:4" s="31" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="53"/>
+      <c r="B3" s="32" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" s="31" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="52"/>
-      <c r="B3" s="32" t="s">
+      <c r="C3" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="33" t="s">
-        <v>144</v>
-      </c>
       <c r="D3" s="33"/>
     </row>
-    <row r="4" spans="1:4" s="31" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="52"/>
+    <row r="4" spans="1:4" s="31" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="53"/>
       <c r="B4" s="32"/>
       <c r="C4" s="33"/>
       <c r="D4" s="33"/>
     </row>
-    <row r="5" spans="1:4" s="31" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="52"/>
+    <row r="5" spans="1:4" s="31" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="53"/>
       <c r="B5" s="33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="34">
         <v>2055</v>
       </c>
       <c r="D5" s="33" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="31" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="53"/>
+      <c r="B6" s="33" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" s="31" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="52"/>
-      <c r="B6" s="33" t="s">
+      <c r="C6" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="D6" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="D6" s="33" t="s">
+    </row>
+    <row r="7" spans="1:4" s="31" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="53"/>
+      <c r="B7" s="32" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" s="31" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="52"/>
-      <c r="B7" s="32" t="s">
+      <c r="C7" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="D7" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="33" t="s">
+    </row>
+    <row r="8" spans="1:4" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="53"/>
+      <c r="B8" s="32" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" s="31" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="52"/>
-      <c r="B8" s="32" t="s">
+      <c r="C8" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="36"/>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
     </row>
-    <row r="10" spans="1:4" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="53" t="s">
+    <row r="10" spans="1:4" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="C10" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="D10" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="D10" s="25" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="55"/>
+      <c r="B11" s="24" t="s">
         <v>158</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="54"/>
-      <c r="B11" s="24" t="s">
-        <v>159</v>
       </c>
       <c r="C11" s="25">
         <v>60000</v>
       </c>
       <c r="D11" s="25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="55"/>
+      <c r="B12" s="24" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
-      <c r="B12" s="24" t="s">
-        <v>161</v>
       </c>
       <c r="C12" s="25">
         <v>3000</v>
       </c>
       <c r="D12" s="25" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="55"/>
+      <c r="B13" s="24" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="54"/>
-      <c r="B13" s="24" t="s">
+      <c r="C13" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="D13" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="D13" s="25" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="55"/>
+      <c r="B14" s="24" t="s">
         <v>165</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="54"/>
-      <c r="B14" s="24" t="s">
-        <v>166</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="63.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="55"/>
+      <c r="B15" s="24" t="s">
         <v>167</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="54"/>
-      <c r="B15" s="24" t="s">
-        <v>168</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="36"/>
       <c r="C16" s="36"/>
       <c r="D16" s="36"/>
     </row>
-    <row r="17" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="55" t="s">
+    <row r="17" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="56" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="C17" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="D17" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="42" t="s">
+    </row>
+    <row r="18" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="56"/>
+      <c r="B18" s="40" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="55"/>
-      <c r="B18" s="40" t="s">
-        <v>174</v>
       </c>
       <c r="C18" s="41">
         <v>5000</v>
       </c>
       <c r="D18" s="41" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="56"/>
+      <c r="B19" s="40" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="55"/>
-      <c r="B19" s="40" t="s">
+      <c r="C19" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="D19" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="50" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="53" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="54" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="28.15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:A8"/>
